--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="G2" t="n">
         <v>1000</v>
@@ -766,10 +766,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="K2" t="n">
         <v>950</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H4" t="n">
         <v>2.26</v>
       </c>
       <c r="I4" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
         <v>3.1</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q4" t="n">
         <v>2.12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="G5" t="n">
         <v>1.35</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>12.5</v>
       </c>
       <c r="I5" t="n">
         <v>15</v>
@@ -1354,7 +1354,7 @@
         <v>5.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
         <v>2.46</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
         <v>2.1</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="K7" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1.08</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="G8" t="n">
         <v>1000</v>
@@ -1930,10 +1930,10 @@
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.38</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="G11" t="n">
         <v>1000</v>
@@ -2512,10 +2512,10 @@
         <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>2.06</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.94</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>2.66</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.89</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3697,22 +3697,22 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
         <v>1.01</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="U17" t="n">
         <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.26</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -3864,25 +3864,25 @@
         <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
       </c>
       <c r="J18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>1.03</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>1.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4061,10 +4061,10 @@
         <v>2.34</v>
       </c>
       <c r="H19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
         <v>3.15</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q19" t="n">
         <v>2.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
         <v>1.97</v>
@@ -4261,7 +4261,7 @@
         <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
         <v>3.8</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
         <v>2.4</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="G21" t="n">
         <v>2.04</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="G26" t="n">
         <v>2.9</v>
@@ -5422,7 +5422,7 @@
         <v>2.56</v>
       </c>
       <c r="I26" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G27" t="n">
         <v>2.68</v>
@@ -5616,10 +5616,10 @@
         <v>2.88</v>
       </c>
       <c r="I27" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
         <v>3.55</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.71</v>
       </c>
       <c r="G29" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="H29" t="n">
         <v>5.4</v>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q29" t="n">
         <v>2.12</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -6192,13 +6192,13 @@
         <v>3.45</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I30" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="J30" t="n">
         <v>3.2</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 01:09:21</t>
+          <t>2026-03-26 03:15:41</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.96</v>
+        <v>2.92</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>770</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="I3" t="n">
         <v>890</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>1.81</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -984,7 +984,7 @@
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="H4" t="n">
         <v>2.26</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4" t="n">
         <v>2.12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="G5" t="n">
         <v>1.35</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G6" t="n">
         <v>2.34</v>
       </c>
-      <c r="G6" t="n">
-        <v>2.46</v>
-      </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="J6" t="n">
         <v>3.35</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q6" t="n">
         <v>2.1</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="J7" t="n">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.08</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
         <v>1.03</v>
@@ -1850,7 +1850,7 @@
         <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
         <v>1.03</v>
@@ -1883,14 +1883,14 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.38</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.83</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.94</v>
+        <v>2.78</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="I11" t="n">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="J11" t="n">
-        <v>1.94</v>
+        <v>2.92</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.97</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="H12" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>2.62</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
         <v>950</v>
@@ -2730,7 +2730,7 @@
         <v>1.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>710</v>
+        <v>1.92</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>820</v>
+        <v>5.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3667,28 +3667,28 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>2.56</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3709,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,58 +3721,58 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP17" t="n">
         <v>1.03</v>
@@ -3823,14 +3823,14 @@
         <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -3861,28 +3861,28 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>1.97</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.98</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -4017,14 +4017,14 @@
         <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
         <v>3.15</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
         <v>2.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4261,10 +4261,10 @@
         <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q20" t="n">
         <v>2.4</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G21" t="n">
         <v>2.04</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.31</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>2.62</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="H26" t="n">
         <v>2.56</v>
       </c>
       <c r="I26" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
@@ -5446,7 +5446,7 @@
         <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>2.72</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>2.92</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>1.71</v>
       </c>
       <c r="G29" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="H29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I29" t="n">
         <v>6.6</v>
@@ -6028,7 +6028,7 @@
         <v>1.73</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -6192,13 +6192,13 @@
         <v>3.45</v>
       </c>
       <c r="G30" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I30" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="J30" t="n">
         <v>3.2</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 03:15:41</t>
+          <t>2026-03-26 05:22:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="G2" t="n">
         <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
         <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>3.25</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="H4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="I4" t="n">
         <v>2.5</v>
@@ -1160,7 +1160,7 @@
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
         <v>2.12</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="G5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="H5" t="n">
         <v>12.5</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="J5" t="n">
         <v>5.6</v>
       </c>
       <c r="K5" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q6" t="n">
         <v>2.1</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G7" t="n">
         <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I7" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1844,13 +1844,13 @@
         <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AT7" t="n">
         <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
         <v>1.03</v>
@@ -1883,14 +1883,14 @@
         <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
         <v>11</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="G8" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I8" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2315,13 +2315,13 @@
         <v>2.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="K10" t="n">
         <v>950</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>2.78</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I11" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="J11" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="K11" t="n">
         <v>3.9</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>1.94</v>
       </c>
       <c r="I12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
@@ -2730,7 +2730,7 @@
         <v>1.04</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>2.08</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
         <v>5.2</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q14" t="n">
         <v>2.16</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
         <v>2.54</v>
       </c>
       <c r="I15" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J15" t="n">
         <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H16" t="n">
         <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J16" t="n">
         <v>3.75</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>1.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
         <v>2.26</v>
@@ -3727,13 +3727,13 @@
         <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
         <v>55</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC17" t="n">
         <v>10.5</v>
@@ -3757,10 +3757,10 @@
         <v>46</v>
       </c>
       <c r="AJ17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL17" t="n">
         <v>44</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="I18" t="n">
         <v>4.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>2.12</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.28</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="BF18" t="n">
-        <v>9.6</v>
+        <v>4.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>23</v>
+        <v>1.45</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G19" t="n">
         <v>2.34</v>
@@ -4064,13 +4064,13 @@
         <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J19" t="n">
         <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>1.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4252,10 @@
         <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
         <v>6.2</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G21" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H21" t="n">
         <v>4.2</v>
@@ -4455,7 +4455,7 @@
         <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>3.75</v>
@@ -4476,7 +4476,7 @@
         <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
         <v>3.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.74</v>
+        <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
         <v>2.46</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I23" t="n">
         <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.66</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
         <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K25" t="n">
         <v>4.4</v>
@@ -5252,7 +5252,7 @@
         <v>1.97</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>2.74</v>
       </c>
       <c r="G26" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H26" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="I26" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q26" t="n">
         <v>1.72</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5610,16 +5610,16 @@
         <v>2.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H27" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I27" t="n">
         <v>2.98</v>
       </c>
       <c r="J27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
         <v>3.55</v>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q27" t="n">
         <v>2.08</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>2.72</v>
       </c>
       <c r="G28" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="H28" t="n">
         <v>2.88</v>
       </c>
       <c r="I28" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="J28" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
         <v>3.3</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G29" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q29" t="n">
         <v>2.22</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>3.45</v>
       </c>
       <c r="G30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H30" t="n">
         <v>2.16</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J31" t="n">
         <v>4.5</v>
@@ -6416,7 +6416,7 @@
         <v>1.76</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 05:22:04</t>
+          <t>2026-03-26 07:28:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G2" t="n">
         <v>3.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="I2" t="n">
         <v>2.42</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
@@ -799,7 +799,7 @@
         <v>2.54</v>
       </c>
       <c r="T2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="n">
         <v>2.3</v>
@@ -811,46 +811,46 @@
         <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AB2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AG2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ2" t="n">
         <v>65</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AL2" t="n">
         <v>46</v>
@@ -859,10 +859,10 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO2" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AP2" t="n">
         <v>1.03</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>09:30:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Haverfordwest County</t>
+          <t>Ishoj IF</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Briton Ferry Llansawel</t>
+          <t>VSK Aarhus FC</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N3" t="n">
         <v>1.75</v>
       </c>
-      <c r="G3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="I3" t="n">
-        <v>890</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K3" t="n">
-        <v>950</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scottish Championship</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>09:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Morton</t>
+          <t>Haverfordwest County</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Briton Ferry Llansawel</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.25</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
-        <v>2.24</v>
+        <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -1330,31 +1330,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>St Johnstone</t>
+          <t>Morton</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Queens Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>3.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.34</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>12.5</v>
+        <v>2.26</v>
       </c>
       <c r="I5" t="n">
-        <v>15.5</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>5.6</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>1.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.65</v>
+        <v>2.12</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Scottish Championship</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AD Ceuta FC</t>
+          <t>St Johnstone</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Queens Park</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>1.27</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>1.34</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>12.5</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>5.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,42 +1713,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>East Fife</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Cadiz</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.5</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>3.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1769,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1781,123 +1781,123 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,37 +1912,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MSK Povazska Bystrica</t>
+          <t>East Fife</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Slavia TU Kosice</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>1.77</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>1.98</v>
       </c>
       <c r="J8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.5</v>
+        <v>1.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.47</v>
+        <v>1.97</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1963,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1975,116 +1975,116 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MSK Zilina II</t>
+          <t>MSK Povazska Bystrica</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Inter Bratislava</t>
+          <t>Slavia TU Kosice</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.26</v>
+        <v>1.9</v>
       </c>
       <c r="G9" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="H9" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="K9" t="n">
-        <v>7.4</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.89</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Samorin</t>
+          <t>MSK Zilina II</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>OFK Banik Lehota</t>
+          <t>Inter Bratislava</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.66</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.87</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.89</v>
+        <v>2.98</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lokomotiva Zvolen</t>
+          <t>Samorin</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dukla Banska Bystrica</t>
+          <t>OFK Banik Lehota</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.78</v>
+        <v>1.76</v>
       </c>
       <c r="G11" t="n">
-        <v>3.7</v>
+        <v>1.96</v>
       </c>
       <c r="H11" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>2.52</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MFK Stara Lubovna</t>
+          <t>Lokomotiva Zvolen</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FC Petrzalka</t>
+          <t>Dukla Banska Bystrica</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="G12" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.94</v>
+        <v>2.18</v>
       </c>
       <c r="I12" t="n">
-        <v>2.64</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.04</v>
+        <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Beltinci</t>
+          <t>MFK Stara Lubovna</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dravinja Kostroj</t>
+          <t>FC Petrzalka</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cardiff Metropolitan</t>
+          <t>Beltinci</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Dravinja Kostroj</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>1.02</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Penybont FC</t>
+          <t>Cardiff Metropolitan</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>1.88</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>2.08</v>
       </c>
       <c r="H15" t="n">
-        <v>2.54</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Penybont FC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kelty Hearts</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.79</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>2.38</v>
       </c>
       <c r="I16" t="n">
-        <v>5.8</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q16" t="n">
         <v>1.87</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3658,37 +3658,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Kelty Hearts</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>1.79</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>1.92</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>2.56</v>
+        <v>3.75</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.63</v>
+        <v>1.89</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3709,10 +3709,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,116 +3721,116 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="G18" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="H18" t="n">
-        <v>3.45</v>
+        <v>2.6</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -3903,10 +3903,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP18" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.55</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.61</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.28</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.38</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.62</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.6</v>
+        <v>14</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.45</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,184 +4041,184 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12:15:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>1.97</v>
       </c>
       <c r="G19" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="H19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC19" t="n">
         <v>3.75</v>
       </c>
-      <c r="I19" t="n">
+      <c r="BD19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG19" t="n">
         <v>3.95</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -4240,32 +4240,32 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>3.75</v>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="J20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.3</v>
       </c>
-      <c r="K20" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,36 +4623,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.99</v>
       </c>
       <c r="G22" t="n">
-        <v>3.6</v>
+        <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2.44</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Colon FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>CA Rentistas</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>2.64</v>
+        <v>3.05</v>
       </c>
       <c r="H23" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="J23" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="K23" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Wanderers (Uru)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cerro</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Irish Division 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino (W)</t>
+          <t>Longford</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EC Bahia (W)</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.97</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,31 +5404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Red Bull Bragantino (W)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>EC Bahia (W)</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.74</v>
+        <v>1.65</v>
       </c>
       <c r="G26" t="n">
-        <v>2.9</v>
+        <v>1.92</v>
       </c>
       <c r="H26" t="n">
-        <v>2.54</v>
+        <v>3.95</v>
       </c>
       <c r="I26" t="n">
-        <v>2.7</v>
+        <v>7.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>CD Castellon</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="G27" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="H27" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="I27" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.78</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>1.72</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,36 +5787,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Deportivo</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="G28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J28" t="n">
         <v>3.4</v>
       </c>
-      <c r="H28" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2.6</v>
-      </c>
       <c r="K28" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.56</v>
+        <v>1.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.68</v>
+        <v>2.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1.79</v>
+        <v>3.05</v>
       </c>
       <c r="H29" t="n">
-        <v>5.8</v>
+        <v>2.88</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>3.25</v>
       </c>
       <c r="J29" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,36 +6175,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.45</v>
+        <v>1.68</v>
       </c>
       <c r="G30" t="n">
-        <v>4.4</v>
+        <v>1.79</v>
       </c>
       <c r="H30" t="n">
-        <v>2.16</v>
+        <v>5.8</v>
       </c>
       <c r="I30" t="n">
-        <v>2.42</v>
+        <v>7.8</v>
       </c>
       <c r="J30" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.9</v>
+        <v>2.22</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,36 +6369,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Club 2 de Mayo de PJC</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.76</v>
+        <v>1.07</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,201 +6546,589 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 07:28:39</t>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-26 09:35:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H33" t="n">
+        <v>11</v>
+      </c>
+      <c r="I33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-26 09:35:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Sportivo San Lorenzo</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q34" t="n">
         <v>1.01</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-26 07:28:39</t>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-26 09:35:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="G2" t="n">
         <v>3.6</v>
@@ -766,7 +766,7 @@
         <v>2.12</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>3.5</v>
@@ -781,7 +781,7 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.23</v>
@@ -793,10 +793,10 @@
         <v>1.61</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="T2" t="n">
         <v>1.6</v>
@@ -805,10 +805,10 @@
         <v>2.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
         <v>23</v>
@@ -865,46 +865,46 @@
         <v>16</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
         <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BD2" t="n">
         <v>1.03</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G3" t="n">
         <v>3.45</v>
       </c>
       <c r="H3" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I3" t="n">
         <v>3.15</v>
       </c>
       <c r="J3" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>3.25</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q3" t="n">
         <v>1.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W3" t="n">
         <v>1.4</v>
       </c>
       <c r="X3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1074,7 +1074,7 @@
         <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
         <v>1.03</v>
@@ -1107,14 +1107,14 @@
         <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1163,16 +1163,16 @@
         <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P4" t="n">
         <v>2.14</v>
@@ -1181,134 +1181,134 @@
         <v>1.71</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1357,16 +1357,16 @@
         <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P5" t="n">
         <v>1.74</v>
@@ -1375,134 +1375,134 @@
         <v>2.12</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>12.5</v>
       </c>
       <c r="I6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
         <v>5.6</v>
@@ -1551,16 +1551,16 @@
         <v>6.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
         <v>2.2</v>
@@ -1569,134 +1569,134 @@
         <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -1727,34 +1727,34 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
         <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
         <v>3.35</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
         <v>1.81</v>
@@ -1763,141 +1763,141 @@
         <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,72 +1907,72 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>East Fife</t>
+          <t>AC Ospitaletto</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I8" t="n">
         <v>4.5</v>
       </c>
-      <c r="G8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.98</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>2.22</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2029,69 +2029,69 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MSK Povazska Bystrica</t>
+          <t>US Latina Calcio</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Slavia TU Kosice</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1.72</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Slovakian 2 Liga</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MSK Zilina II</t>
+          <t>Beltinci</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Inter Bratislava</t>
+          <t>Dravinja Kostroj</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>2.98</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.19</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Samorin</t>
+          <t>MFK Stara Lubovna</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OFK Banik Lehota</t>
+          <t>FC Petrzalka</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.76</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>2.04</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>2.44</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2715,152 +2715,152 @@
         <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P12" t="n">
         <v>1.97</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MFK Stara Lubovna</t>
+          <t>Samorin</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FC Petrzalka</t>
+          <t>OFK Banik Lehota</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>3.8</v>
+        <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>2.12</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Beltinci</t>
+          <t>MSK Povazska Bystrica</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dravinja Kostroj</t>
+          <t>Slavia TU Kosice</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
         <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cardiff Metropolitan</t>
+          <t>Dumbarton</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Forfar</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.98</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Welsh Premiership</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Penybont FC</t>
+          <t>East Fife</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>2.38</v>
+        <v>1.77</v>
       </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>1.98</v>
       </c>
       <c r="J16" t="n">
         <v>3.1</v>
       </c>
       <c r="K16" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Slovakian 2 Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>MSK Zilina II</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kelty Hearts</t>
+          <t>Inter Bratislava</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.79</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>1.92</v>
+        <v>2.78</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>2.66</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Cardiff Metropolitan</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>1.84</v>
       </c>
       <c r="G18" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.35</v>
       </c>
-      <c r="J18" t="n">
-        <v>2.56</v>
-      </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Scottish League One</t>
+          <t>Welsh Premiership</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Penybont FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>2.28</v>
+        <v>3.25</v>
       </c>
       <c r="H19" t="n">
-        <v>3.45</v>
+        <v>2.54</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P19" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.63</v>
+        <v>1.87</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4163,69 +4163,69 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>12:15:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Elgin City FC</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Clyde</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
-        <v>2.34</v>
+        <v>3.1</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="I20" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="J20" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.52</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>12:15:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Spartans</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>East Kilbride</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.81</v>
+        <v>2.38</v>
       </c>
       <c r="G21" t="n">
-        <v>1.98</v>
+        <v>2.76</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2</v>
+        <v>2.58</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6</v>
+        <v>2.34</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.42</v>
+        <v>1.59</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,36 +4623,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Stirling</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Leganes</t>
+          <t>Edinburgh City</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G22" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>1.59</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Scottish League Two</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Colon FC</t>
+          <t>Annan</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CA Rentistas</t>
+          <t>Stranraer</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I23" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J23" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.45</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.5</v>
+        <v>1.68</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wanderers (Uru)</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cerro</t>
+          <t>Kelty Hearts</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="G24" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="H24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J24" t="n">
         <v>3.75</v>
       </c>
-      <c r="I24" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.86</v>
-      </c>
       <c r="K24" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>1.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.68</v>
+        <v>1.89</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Irish Division 1</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,42 +5205,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Longford</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5261,10 +5261,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,123 +5273,123 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Scottish League One</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino (W)</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>EC Bahia (W)</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.65</v>
+        <v>1.97</v>
       </c>
       <c r="G26" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="H26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR26" t="n">
         <v>3.95</v>
       </c>
-      <c r="I26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="AS26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF26" t="n">
         <v>3.4</v>
       </c>
-      <c r="K26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -5593,36 +5593,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CD Castellon</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.76</v>
+        <v>2.24</v>
       </c>
       <c r="G27" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="H27" t="n">
-        <v>2.54</v>
+        <v>3.75</v>
       </c>
       <c r="I27" t="n">
-        <v>2.72</v>
+        <v>3.95</v>
       </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.72</v>
+        <v>2.58</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
@@ -5787,36 +5787,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>12:15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Deportivo</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>1.81</v>
       </c>
       <c r="G28" t="n">
-        <v>2.7</v>
+        <v>1.96</v>
       </c>
       <c r="H28" t="n">
-        <v>2.92</v>
+        <v>5.2</v>
       </c>
       <c r="I28" t="n">
-        <v>2.98</v>
+        <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>ASD Alcione</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,36 +6175,36 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Arzignanochiampo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,17 +6369,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club 2 de Mayo de PJC</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -6413,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
         <v>1.01</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,36 +6563,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nacional (Uru)</t>
+          <t>Aurora Pro Patria 1919</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.76</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,36 +6757,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tolima</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.35</v>
+        <v>1.99</v>
       </c>
       <c r="G33" t="n">
-        <v>1.51</v>
+        <v>2.02</v>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="I33" t="n">
-        <v>16.5</v>
+        <v>4.6</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,201 +6934,2335 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 09:35:26</t>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Colon FC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>CA Rentistas</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Wanderers (Uru)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cerro</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Irish Division 1</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>16:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Longford</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Finn Harps</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Brazilian Campeonato Women</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Red Bull Bragantino (W)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>EC Bahia (W)</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CD Castellon</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H38" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I38" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Spanish Segunda Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sporting Gijon</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Deportivo</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Boyaca Chico</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Uruguayan Segunda Division</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>18:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plaza Colonia</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>River Plate (Uru)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Olimpia</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Club 2 de Mayo de PJC</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Nacional (Uru)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="G43" t="n">
+        <v>4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I43" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>20:10:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I44" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Cerro Porteno</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Sportivo San Lorenzo</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-03-26 09:35:26</t>
+      <c r="Q45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-03-26 11:44:06</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -868,59 +868,59 @@
         <v>15</v>
       </c>
       <c r="AQ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV2" t="n">
         <v>9.6</v>
       </c>
-      <c r="AR2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AW2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY2" t="n">
         <v>12</v>
       </c>
-      <c r="AU2" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>11</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
         <v>20</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
         <v>1.4</v>
       </c>
       <c r="X3" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU3" t="n">
         <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>23</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>16</v>
+        <v>3.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="n">
         <v>3.8</v>
@@ -1178,7 +1178,7 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>3.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I5" t="n">
         <v>2.78</v>
@@ -1363,28 +1363,28 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="O5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
         <v>3.95</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U5" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
         <v>1.56</v>
@@ -1393,7 +1393,7 @@
         <v>1.4</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
         <v>11</v>
@@ -1417,7 +1417,7 @@
         <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG5" t="n">
         <v>16.5</v>
@@ -1456,7 +1456,7 @@
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT5" t="n">
         <v>8.6</v>
@@ -1480,29 +1480,29 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
         <v>18</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
         <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V6" t="n">
         <v>1.06</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
         <v>2.44</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H8" t="n">
         <v>2.84</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J8" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="O8" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>2.42</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J9" t="n">
-        <v>2.62</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
         <v>5.3</v>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
         <v>2.08</v>
@@ -2154,7 +2154,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W9" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2315,13 +2315,13 @@
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I10" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J10" t="n">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="K10" t="n">
         <v>5.5</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>1.61</v>
       </c>
       <c r="O10" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,10 +2357,10 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K11" t="n">
         <v>5.8</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="I12" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="J12" t="n">
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -2745,10 +2745,10 @@
         <v>1.59</v>
       </c>
       <c r="V12" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="W12" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
         <v>9.199999999999999</v>
@@ -2775,10 +2775,10 @@
         <v>30</v>
       </c>
       <c r="AF12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AG12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AH12" t="n">
         <v>34</v>
@@ -2805,13 +2805,13 @@
         <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AS12" t="n">
         <v>16.5</v>
@@ -2823,19 +2823,19 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW12" t="n">
         <v>19.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
       </c>
       <c r="AZ12" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
         <v>1.03</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H15" t="n">
         <v>2.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
@@ -3327,10 +3327,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J16" t="n">
         <v>3.45</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="H17" t="n">
         <v>2.66</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K17" t="n">
         <v>4.1</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4163,16 +4163,16 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -4184,7 +4184,7 @@
         <v>8.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -4196,29 +4196,29 @@
         <v>10.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.95</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H20" t="n">
         <v>1.79</v>
       </c>
       <c r="I20" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J20" t="n">
         <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
@@ -4282,7 +4282,7 @@
         <v>1.71</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R20" t="n">
         <v>1.23</v>
@@ -4300,7 +4300,7 @@
         <v>2</v>
       </c>
       <c r="W20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AQ20" t="n">
         <v>5.7</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>2.86</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>2.96</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BG20" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H21" t="n">
         <v>4.4</v>
@@ -4464,13 +4464,13 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="O21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="P21" t="n">
         <v>1.76</v>
@@ -4479,43 +4479,43 @@
         <v>2.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V21" t="n">
         <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
         <v>21</v>
       </c>
       <c r="Z21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
         <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
@@ -4551,28 +4551,28 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
         <v>9.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU21" t="n">
         <v>5.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
         <v>7.4</v>
@@ -4584,7 +4584,7 @@
         <v>13</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
         <v>14</v>
@@ -4593,10 +4593,10 @@
         <v>14</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G22" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H22" t="n">
         <v>2.54</v>
       </c>
       <c r="I22" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>3.3</v>
@@ -4658,46 +4658,46 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="O22" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="P22" t="n">
         <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U22" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="V22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
         <v>1.47</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
         <v>16</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4718,7 +4718,7 @@
         <v>28</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH22" t="n">
         <v>23</v>
@@ -4730,10 +4730,10 @@
         <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
@@ -4742,19 +4742,19 @@
         <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>7.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
         <v>8</v>
@@ -4772,35 +4772,35 @@
         <v>12.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
         <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
         <v>19</v>
       </c>
       <c r="BD22" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
         <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -4873,10 +4873,10 @@
         <v>2.44</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
         <v>1.46</v>
@@ -4939,52 +4939,52 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5136,13 +5136,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AR24" t="n">
         <v>15.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="AT24" t="n">
         <v>11</v>
@@ -5166,29 +5166,29 @@
         <v>11</v>
       </c>
       <c r="BA24" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BB24" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BC24" t="n">
         <v>17.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BE24" t="n">
-        <v>48</v>
+        <v>1.03</v>
       </c>
       <c r="BF24" t="n">
         <v>10.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5261,10 +5261,10 @@
         <v>2.36</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V25" t="n">
         <v>1.33</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>3.15</v>
       </c>
       <c r="I26" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J26" t="n">
         <v>3.4</v>
@@ -5455,16 +5455,16 @@
         <v>2.32</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V26" t="n">
         <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5521,62 +5521,62 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
         <v>5.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ26" t="n">
         <v>10</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G27" t="n">
         <v>1.91</v>
@@ -5625,46 +5625,46 @@
         <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
         <v>1.96</v>
       </c>
       <c r="O27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P27" t="n">
         <v>1.96</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U27" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V27" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W27" t="n">
         <v>2.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z27" t="n">
         <v>1000</v>
@@ -5673,34 +5673,34 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL27" t="n">
         <v>1000</v>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5909,62 +5909,62 @@
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>14</v>
+        <v>3.7</v>
       </c>
       <c r="BG28" t="n">
-        <v>15.5</v>
+        <v>3.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -5995,25 +5995,25 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H29" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I29" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="J29" t="n">
         <v>3.25</v>
       </c>
       <c r="K29" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M29" t="n">
         <v>1.05</v>
@@ -6025,16 +6025,16 @@
         <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="T29" t="n">
         <v>1.64</v>
@@ -6046,7 +6046,7 @@
         <v>1.31</v>
       </c>
       <c r="W29" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV29" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR29" t="n">
+      <c r="AW29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC29" t="n">
         <v>3.95</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="BD29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG29" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>4</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6425,10 +6425,10 @@
         <v>2.72</v>
       </c>
       <c r="T31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U31" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V31" t="n">
         <v>1.48</v>
@@ -6500,7 +6500,7 @@
         <v>15.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
         <v>9.800000000000001</v>
@@ -6536,7 +6536,7 @@
         <v>1.03</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
         <v>11.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6709,7 +6709,7 @@
         <v>12.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AY32" t="n">
         <v>14.5</v>
@@ -6721,26 +6721,26 @@
         <v>21</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="BG32" t="n">
         <v>6.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AQ34" t="n">
         <v>11</v>
@@ -7082,7 +7082,7 @@
         <v>18</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AT34" t="n">
         <v>7.8</v>
@@ -7094,7 +7094,7 @@
         <v>10</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="AX34" t="n">
         <v>9.199999999999999</v>
@@ -7106,7 +7106,7 @@
         <v>10.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BB34" t="n">
         <v>15</v>
@@ -7118,17 +7118,17 @@
         <v>18</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
         <v>20</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF35" t="n">
         <v>25</v>
@@ -7288,7 +7288,7 @@
         <v>8.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AX35" t="n">
         <v>10.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>7.6</v>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J37" t="n">
         <v>5.3</v>
@@ -7586,7 +7586,7 @@
         <v>1.72</v>
       </c>
       <c r="S37" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T37" t="n">
         <v>1.73</v>
@@ -7604,7 +7604,7 @@
         <v>38</v>
       </c>
       <c r="Y37" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z37" t="n">
         <v>110</v>
@@ -7613,10 +7613,10 @@
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AC37" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AD37" t="n">
         <v>38</v>
@@ -7625,10 +7625,10 @@
         <v>150</v>
       </c>
       <c r="AF37" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
         <v>24</v>
@@ -7637,10 +7637,10 @@
         <v>120</v>
       </c>
       <c r="AJ37" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AK37" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AL37" t="n">
         <v>30</v>
@@ -7655,62 +7655,62 @@
         <v>140</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB37" t="n">
         <v>9</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG37" t="n">
-        <v>80</v>
+        <v>6.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>2.58</v>
       </c>
       <c r="I38" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J38" t="n">
         <v>3.6</v>
@@ -7768,7 +7768,7 @@
         <v>6.6</v>
       </c>
       <c r="O38" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P38" t="n">
         <v>2.9</v>
@@ -7789,7 +7789,7 @@
         <v>2.84</v>
       </c>
       <c r="V38" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W38" t="n">
         <v>1.62</v>
@@ -7819,7 +7819,7 @@
         <v>30</v>
       </c>
       <c r="AF38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG38" t="n">
         <v>16</v>
@@ -7852,16 +7852,16 @@
         <v>1.03</v>
       </c>
       <c r="AQ38" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU38" t="n">
         <v>8.4</v>
@@ -7873,7 +7873,7 @@
         <v>18</v>
       </c>
       <c r="AX38" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY38" t="n">
         <v>9.6</v>
@@ -7885,7 +7885,7 @@
         <v>1.03</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
         <v>16</v>
@@ -7894,17 +7894,17 @@
         <v>1.03</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
         <v>7.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8237,52 +8237,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
         <v>2.14</v>
       </c>
       <c r="U41" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="V41" t="n">
         <v>1.33</v>
@@ -8395,7 +8395,7 @@
         <v>7.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE41" t="n">
         <v>65</v>
@@ -8440,7 +8440,7 @@
         <v>22</v>
       </c>
       <c r="AS41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT41" t="n">
         <v>6.6</v>
@@ -8464,7 +8464,7 @@
         <v>21</v>
       </c>
       <c r="BA41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB41" t="n">
         <v>28</v>
@@ -8476,17 +8476,17 @@
         <v>10.5</v>
       </c>
       <c r="BE41" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF41" t="n">
         <v>27</v>
       </c>
       <c r="BG41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8520,10 +8520,10 @@
         <v>1.81</v>
       </c>
       <c r="G42" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H42" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I42" t="n">
         <v>6.2</v>
@@ -8535,13 +8535,13 @@
         <v>3.65</v>
       </c>
       <c r="L42" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N42" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O42" t="n">
         <v>1.48</v>
@@ -8568,7 +8568,7 @@
         <v>1.19</v>
       </c>
       <c r="W42" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X42" t="n">
         <v>10.5</v>
@@ -8598,7 +8598,7 @@
         <v>10.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH42" t="n">
         <v>27</v>
@@ -8613,13 +8613,13 @@
         <v>26</v>
       </c>
       <c r="AL42" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM42" t="n">
         <v>230</v>
       </c>
       <c r="AN42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
@@ -8634,10 +8634,10 @@
         <v>34</v>
       </c>
       <c r="AS42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT42" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU42" t="n">
         <v>7</v>
@@ -8646,7 +8646,7 @@
         <v>19</v>
       </c>
       <c r="AW42" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX42" t="n">
         <v>8.6</v>
@@ -8658,7 +8658,7 @@
         <v>21</v>
       </c>
       <c r="BA42" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BB42" t="n">
         <v>18</v>
@@ -8667,20 +8667,20 @@
         <v>20</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF42" t="n">
         <v>15</v>
       </c>
       <c r="BG42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -8929,22 +8929,22 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="O44" t="n">
         <v>1.3</v>
       </c>
       <c r="P44" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="R44" t="n">
         <v>1.18</v>
       </c>
       <c r="S44" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="T44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -9520,13 +9520,13 @@
         <v>1.48</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R47" t="n">
         <v>1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G48" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H48" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I48" t="n">
         <v>4.3</v>
       </c>
       <c r="J48" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K48" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="L48" t="n">
         <v>1.43</v>
@@ -9705,13 +9705,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="O48" t="n">
         <v>1.36</v>
       </c>
       <c r="P48" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q48" t="n">
         <v>2.14</v>
@@ -9723,16 +9723,16 @@
         <v>3.9</v>
       </c>
       <c r="T48" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V48" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W48" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X48" t="n">
         <v>13.5</v>
@@ -9765,7 +9765,7 @@
         <v>12.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI48" t="n">
         <v>75</v>
@@ -9804,7 +9804,7 @@
         <v>7.6</v>
       </c>
       <c r="AU48" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV48" t="n">
         <v>13.5</v>
@@ -9840,11 +9840,11 @@
         <v>15</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.5</v>
+        <v>42</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
         <v>30</v>
       </c>
       <c r="AC49" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AD49" t="n">
         <v>21</v>
@@ -9956,7 +9956,7 @@
         <v>32</v>
       </c>
       <c r="AG49" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AH49" t="n">
         <v>20</v>
@@ -9983,31 +9983,31 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="AT49" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AU49" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AV49" t="n">
         <v>10</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="AY49" t="n">
         <v>9.4</v>
@@ -10016,29 +10016,29 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.94</v>
+        <v>2.32</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="BD49" t="n">
-        <v>1.92</v>
+        <v>2.3</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.97</v>
+        <v>2.36</v>
       </c>
       <c r="BF49" t="n">
-        <v>2.04</v>
+        <v>5.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -10069,19 +10069,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G50" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I50" t="n">
         <v>3.95</v>
       </c>
       <c r="J50" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K50" t="n">
         <v>3.2</v>
@@ -10102,13 +10102,13 @@
         <v>1.45</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="R50" t="n">
         <v>1.14</v>
       </c>
       <c r="S50" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T50" t="n">
         <v>1.01</v>
@@ -10117,10 +10117,10 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W50" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10177,52 +10177,52 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF50" t="n">
         <v>1.01</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -10281,16 +10281,16 @@
         <v>3.35</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P51" t="n">
         <v>1.48</v>
@@ -10299,134 +10299,134 @@
         <v>2.68</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO51" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -10457,170 +10457,170 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P52" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO52" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG52" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -10669,16 +10669,16 @@
         <v>4.1</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P53" t="n">
         <v>1.9</v>
@@ -10687,134 +10687,134 @@
         <v>1.92</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG53" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G54" t="n">
         <v>2.38</v>
@@ -10863,16 +10863,16 @@
         <v>4.4</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P54" t="n">
         <v>2.48</v>
@@ -10881,134 +10881,134 @@
         <v>1.58</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG54" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -11048,25 +11048,25 @@
         <v>2.58</v>
       </c>
       <c r="I55" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J55" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K55" t="n">
         <v>3.85</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P55" t="n">
         <v>2.16</v>
@@ -11075,134 +11075,134 @@
         <v>1.72</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -11233,170 +11233,170 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G56" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H56" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J56" t="n">
         <v>3.1</v>
       </c>
-      <c r="I56" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K56" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P56" t="n">
         <v>1.65</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -11427,37 +11427,37 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G57" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="H57" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="I57" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J57" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L57" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M57" t="n">
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="O57" t="n">
         <v>1.38</v>
       </c>
       <c r="P57" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q57" t="n">
         <v>1.92</v>
@@ -11475,10 +11475,10 @@
         <v>1.01</v>
       </c>
       <c r="V57" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W57" t="n">
-        <v>1.74</v>
+        <v>1.83</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -11633,22 +11633,22 @@
         <v>7.8</v>
       </c>
       <c r="J58" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K58" t="n">
         <v>4.1</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P58" t="n">
         <v>1.74</v>
@@ -11657,134 +11657,134 @@
         <v>2.22</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -11818,16 +11818,16 @@
         <v>2.72</v>
       </c>
       <c r="G59" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H59" t="n">
         <v>2.88</v>
       </c>
       <c r="I59" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="J59" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="K59" t="n">
         <v>3.3</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -12206,13 +12206,13 @@
         <v>3.4</v>
       </c>
       <c r="G61" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H61" t="n">
         <v>2.18</v>
       </c>
       <c r="I61" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="J61" t="n">
         <v>3.2</v>
@@ -12233,7 +12233,7 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q61" t="n">
         <v>2.06</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -12427,10 +12427,10 @@
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -12591,22 +12591,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G63" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H63" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I63" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J63" t="n">
         <v>2.88</v>
       </c>
       <c r="K63" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -12624,13 +12624,13 @@
         <v>1.53</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R63" t="n">
         <v>1.18</v>
       </c>
       <c r="S63" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="T63" t="n">
         <v>1.01</v>
@@ -12639,7 +12639,7 @@
         <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W63" t="n">
         <v>1.53</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-26 16:06:19</t>
+          <t>2026-03-26 18:18:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="J5" t="n">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
         <v>3.4</v>
@@ -1363,13 +1363,13 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P5" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
         <v>2.24</v>
@@ -1378,19 +1378,19 @@
         <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U5" t="n">
         <v>1.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
         <v>12.5</v>
@@ -1405,10 +1405,10 @@
         <v>42</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
@@ -1420,7 +1420,7 @@
         <v>23</v>
       </c>
       <c r="AG5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH5" t="n">
         <v>21</v>
@@ -1462,13 +1462,13 @@
         <v>8.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1486,23 +1486,23 @@
         <v>5.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>36</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G6" t="n">
         <v>1.34</v>
@@ -1548,31 +1548,31 @@
         <v>5.6</v>
       </c>
       <c r="K6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
         <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
         <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.47</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
         <v>2.18</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G7" t="n">
         <v>2.44</v>
@@ -1745,7 +1745,7 @@
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -1757,13 +1757,13 @@
         <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
         <v>3.85</v>
@@ -1784,7 +1784,7 @@
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
         <v>25</v>
@@ -1796,7 +1796,7 @@
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
         <v>14.5</v>
@@ -1823,7 +1823,7 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
         <v>140</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
         <v>11</v>
@@ -1841,10 +1841,10 @@
         <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
@@ -1856,7 +1856,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -1868,29 +1868,29 @@
         <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD7" t="n">
         <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
         <v>34</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
         <v>2.72</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="I10" t="n">
         <v>2.54</v>
@@ -2324,7 +2324,7 @@
         <v>2.84</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -2697,25 +2697,25 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="G12" t="n">
         <v>7</v>
       </c>
       <c r="H12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I12" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
         <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
@@ -2724,7 +2724,7 @@
         <v>2.46</v>
       </c>
       <c r="O12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
         <v>1.5</v>
@@ -2745,7 +2745,7 @@
         <v>1.59</v>
       </c>
       <c r="V12" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="W12" t="n">
         <v>1.16</v>
@@ -2763,7 +2763,7 @@
         <v>23</v>
       </c>
       <c r="AB12" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.6</v>
@@ -2805,7 +2805,7 @@
         <v>24</v>
       </c>
       <c r="AP12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2820,7 +2820,7 @@
         <v>11.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV12" t="n">
         <v>9.6</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H14" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3115,16 +3115,16 @@
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
         <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>2.42</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
@@ -3327,7 +3327,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
         <v>1.34</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>1.96</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>5.7</v>
@@ -3524,7 +3524,7 @@
         <v>1.21</v>
       </c>
       <c r="W16" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
         <v>2.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R17" t="n">
         <v>1.63</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3927,7 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
@@ -3969,16 +3969,16 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AQ18" t="n">
         <v>7.4</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AT18" t="n">
         <v>6.6</v>
@@ -3990,7 +3990,7 @@
         <v>8.4</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AX18" t="n">
         <v>10</v>
@@ -4002,29 +4002,29 @@
         <v>10.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BB18" t="n">
         <v>6.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>6.4</v>
       </c>
       <c r="H19" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="I19" t="n">
         <v>1.98</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H21" t="n">
         <v>2.66</v>
@@ -4455,7 +4455,7 @@
         <v>2.98</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W21" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
         <v>5.3</v>
@@ -4661,16 +4661,16 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="O22" t="n">
         <v>1.05</v>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="G23" t="n">
         <v>3.25</v>
@@ -4843,7 +4843,7 @@
         <v>2.9</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>3.85</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
         <v>11</v>
       </c>
       <c r="AU26" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AV26" t="n">
         <v>9.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="H28" t="n">
         <v>3.15</v>
       </c>
       <c r="I28" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="J28" t="n">
         <v>3.4</v>
@@ -5834,13 +5834,13 @@
         <v>2.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="R28" t="n">
         <v>1.41</v>
       </c>
       <c r="S28" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T28" t="n">
         <v>1.45</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="G29" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6019,7 +6019,7 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O29" t="n">
         <v>1.29</v>
@@ -6028,7 +6028,7 @@
         <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R29" t="n">
         <v>1.26</v>
@@ -6046,16 +6046,16 @@
         <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X29" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
@@ -6064,7 +6064,7 @@
         <v>12.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD29" t="n">
         <v>28</v>
@@ -6130,7 +6130,7 @@
         <v>7.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
         <v>12</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6237,10 +6237,10 @@
         <v>2.26</v>
       </c>
       <c r="V30" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W30" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="X30" t="n">
         <v>22</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="G31" t="n">
         <v>5.3</v>
@@ -6392,10 +6392,10 @@
         <v>1.86</v>
       </c>
       <c r="I31" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="J31" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K31" t="n">
         <v>4.5</v>
@@ -6404,13 +6404,13 @@
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N31" t="n">
         <v>3.95</v>
       </c>
       <c r="O31" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P31" t="n">
         <v>2.02</v>
@@ -6419,19 +6419,19 @@
         <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U31" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="V31" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="W31" t="n">
         <v>1.25</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.96</v>
+        <v>5.4</v>
       </c>
       <c r="AQ31" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>8.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.88</v>
+        <v>4.8</v>
       </c>
       <c r="AT31" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="AV31" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.87</v>
+        <v>4.7</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.92</v>
+        <v>3.9</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.96</v>
+        <v>6.2</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.96</v>
+        <v>2.92</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.96</v>
+        <v>3.85</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.96</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
         <v>4.1</v>
       </c>
       <c r="K35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,22 +7183,22 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O35" t="n">
         <v>1.12</v>
       </c>
       <c r="P35" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q35" t="n">
         <v>1.36</v>
       </c>
       <c r="R35" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S35" t="n">
         <v>1.89</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.93</v>
       </c>
       <c r="T35" t="n">
         <v>1.37</v>
@@ -7216,13 +7216,13 @@
         <v>46</v>
       </c>
       <c r="Y35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z35" t="n">
         <v>34</v>
       </c>
       <c r="AA35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB35" t="n">
         <v>27</v>
@@ -7243,7 +7243,7 @@
         <v>16</v>
       </c>
       <c r="AH35" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AI35" t="n">
         <v>32</v>
@@ -7258,7 +7258,7 @@
         <v>26</v>
       </c>
       <c r="AM35" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AN35" t="n">
         <v>970</v>
@@ -7288,7 +7288,7 @@
         <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.18</v>
       </c>
       <c r="G38" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H38" t="n">
         <v>3.1</v>
@@ -7765,10 +7765,10 @@
         <v>1.02</v>
       </c>
       <c r="N38" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P38" t="n">
         <v>2.24</v>
@@ -7789,10 +7789,10 @@
         <v>2.38</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W38" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8526,13 +8526,13 @@
         <v>3.65</v>
       </c>
       <c r="I42" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J42" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K42" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L42" t="n">
         <v>1.5</v>
@@ -8574,7 +8574,7 @@
         <v>8.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z42" t="n">
         <v>26</v>
@@ -8604,7 +8604,7 @@
         <v>24</v>
       </c>
       <c r="AI42" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ42" t="n">
         <v>34</v>
@@ -8634,7 +8634,7 @@
         <v>21</v>
       </c>
       <c r="AS42" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT42" t="n">
         <v>6.6</v>
@@ -8652,13 +8652,13 @@
         <v>11.5</v>
       </c>
       <c r="AY42" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ42" t="n">
         <v>21</v>
       </c>
       <c r="BA42" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB42" t="n">
         <v>28</v>
@@ -8667,20 +8667,20 @@
         <v>28</v>
       </c>
       <c r="BD42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE42" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF42" t="n">
         <v>27</v>
       </c>
       <c r="BG42" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8717,31 +8717,31 @@
         <v>2.02</v>
       </c>
       <c r="H43" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I43" t="n">
         <v>5.7</v>
       </c>
       <c r="J43" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L43" t="n">
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O43" t="n">
         <v>1.48</v>
       </c>
       <c r="P43" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q43" t="n">
         <v>2.4</v>
@@ -8777,7 +8777,7 @@
         <v>180</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC43" t="n">
         <v>8.4</v>
@@ -8819,16 +8819,16 @@
         <v>1000</v>
       </c>
       <c r="AP43" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AQ43" t="n">
         <v>11</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT43" t="n">
         <v>6.2</v>
@@ -8837,10 +8837,10 @@
         <v>6.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX43" t="n">
         <v>9</v>
@@ -8852,7 +8852,7 @@
         <v>21</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB43" t="n">
         <v>18</v>
@@ -8864,17 +8864,17 @@
         <v>44</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF43" t="n">
         <v>15</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -8911,16 +8911,16 @@
         <v>2.16</v>
       </c>
       <c r="H44" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
         <v>7.2</v>
       </c>
       <c r="J44" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K44" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8929,13 +8929,13 @@
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="O44" t="n">
         <v>1.02</v>
       </c>
       <c r="P44" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q44" t="n">
         <v>2.16</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="G46" t="n">
-        <v>2.24</v>
+        <v>2.54</v>
       </c>
       <c r="H46" t="n">
         <v>3.4</v>
       </c>
       <c r="I46" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="J46" t="n">
         <v>3</v>
       </c>
       <c r="K46" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9317,7 +9317,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="O46" t="n">
         <v>1.3</v>
@@ -9326,13 +9326,13 @@
         <v>1.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R46" t="n">
         <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
@@ -9341,10 +9341,10 @@
         <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="W46" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -9511,7 +9511,7 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="O47" t="n">
         <v>1.02</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G48" t="n">
         <v>3</v>
@@ -9705,13 +9705,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="O48" t="n">
         <v>1.01</v>
       </c>
       <c r="P48" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q48" t="n">
         <v>2.32</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W48" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
         <v>3.7</v>
       </c>
       <c r="I49" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J49" t="n">
         <v>3.45</v>
@@ -9893,22 +9893,22 @@
         <v>3.65</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>1.81</v>
+        <v>3.3</v>
       </c>
       <c r="O49" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P49" t="n">
         <v>1.81</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R49" t="n">
         <v>1.29</v>
@@ -9917,10 +9917,10 @@
         <v>3.9</v>
       </c>
       <c r="T49" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="U49" t="n">
-        <v>1.84</v>
+        <v>1.99</v>
       </c>
       <c r="V49" t="n">
         <v>1.32</v>
@@ -9929,116 +9929,116 @@
         <v>1.84</v>
       </c>
       <c r="X49" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y49" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA49" t="n">
         <v>85</v>
       </c>
       <c r="AB49" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC49" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD49" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AE49" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF49" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG49" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH49" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AI49" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ49" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AK49" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL49" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM49" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO49" t="n">
         <v>65</v>
       </c>
       <c r="AP49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ49" t="n">
         <v>11</v>
       </c>
       <c r="AR49" t="n">
-        <v>5.1</v>
+        <v>23</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="AT49" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU49" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV49" t="n">
         <v>13.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.6</v>
+        <v>12.5</v>
       </c>
       <c r="AX49" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ49" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BB49" t="n">
-        <v>5.1</v>
+        <v>24</v>
       </c>
       <c r="BC49" t="n">
-        <v>5.1</v>
+        <v>22</v>
       </c>
       <c r="BD49" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="BF49" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BG49" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10266,7 @@
         <v>2.58</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="H51" t="n">
         <v>3.05</v>
@@ -10275,7 +10275,7 @@
         <v>3.95</v>
       </c>
       <c r="J51" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="K51" t="n">
         <v>3.2</v>
@@ -10290,19 +10290,19 @@
         <v>1.46</v>
       </c>
       <c r="O51" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P51" t="n">
         <v>1.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R51" t="n">
         <v>1.14</v>
       </c>
       <c r="S51" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -10499,10 +10499,10 @@
         <v>4.8</v>
       </c>
       <c r="T52" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U52" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V52" t="n">
         <v>1.28</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -10654,13 +10654,13 @@
         <v>2.46</v>
       </c>
       <c r="G53" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H53" t="n">
         <v>2.36</v>
       </c>
       <c r="I53" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J53" t="n">
         <v>3</v>
@@ -10690,7 +10690,7 @@
         <v>1.21</v>
       </c>
       <c r="S53" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="T53" t="n">
         <v>1.01</v>
@@ -10699,10 +10699,10 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W53" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -11233,10 +11233,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G56" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H56" t="n">
         <v>2.58</v>
@@ -11245,7 +11245,7 @@
         <v>2.62</v>
       </c>
       <c r="J56" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K56" t="n">
         <v>3.9</v>
@@ -11266,7 +11266,7 @@
         <v>2.18</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R56" t="n">
         <v>1.46</v>
@@ -11281,10 +11281,10 @@
         <v>2.14</v>
       </c>
       <c r="V56" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W56" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X56" t="n">
         <v>18</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -11427,19 +11427,19 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G57" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="H57" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I57" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J57" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K57" t="n">
         <v>3.2</v>
@@ -11475,10 +11475,10 @@
         <v>1.93</v>
       </c>
       <c r="V57" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W57" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X57" t="n">
         <v>10.5</v>
@@ -11502,7 +11502,7 @@
         <v>14.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF57" t="n">
         <v>17</v>
@@ -11520,25 +11520,25 @@
         <v>42</v>
       </c>
       <c r="AK57" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL57" t="n">
         <v>60</v>
       </c>
       <c r="AM57" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN57" t="n">
         <v>36</v>
       </c>
       <c r="AO57" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP57" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AQ57" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR57" t="n">
         <v>17.5</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -11857,10 +11857,10 @@
         <v>3.55</v>
       </c>
       <c r="T59" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U59" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V59" t="n">
         <v>1.16</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -12400,13 +12400,13 @@
         <v>3.4</v>
       </c>
       <c r="G62" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="H62" t="n">
         <v>2.18</v>
       </c>
       <c r="I62" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="J62" t="n">
         <v>3.2</v>
@@ -12415,7 +12415,7 @@
         <v>3.7</v>
       </c>
       <c r="L62" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M62" t="n">
         <v>1.01</v>
@@ -12430,7 +12430,7 @@
         <v>1.76</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="R62" t="n">
         <v>1.24</v>
@@ -12439,16 +12439,16 @@
         <v>3.2</v>
       </c>
       <c r="T62" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U62" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V62" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="W62" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="X62" t="n">
         <v>17</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -12633,10 +12633,10 @@
         <v>2.88</v>
       </c>
       <c r="T63" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U63" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V63" t="n">
         <v>1.5</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -12794,7 +12794,7 @@
         <v>4.9</v>
       </c>
       <c r="I64" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J64" t="n">
         <v>3.4</v>
@@ -12809,16 +12809,16 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O64" t="n">
         <v>1.37</v>
       </c>
       <c r="P64" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="R64" t="n">
         <v>1.19</v>
@@ -12833,7 +12833,7 @@
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W64" t="n">
         <v>2.16</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -12982,13 +12982,13 @@
         <v>1.35</v>
       </c>
       <c r="G65" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H65" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="J65" t="n">
         <v>4.5</v>
@@ -12997,16 +12997,16 @@
         <v>5.4</v>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P65" t="n">
         <v>1.76</v>
@@ -13015,134 +13015,134 @@
         <v>2.1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO65" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AR65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AV65" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AW65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX65" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AY65" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BA65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BC65" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD65" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BG65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -13197,10 +13197,10 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O66" t="n">
-        <v>1.43</v>
+        <v>1.02</v>
       </c>
       <c r="P66" t="n">
         <v>1.53</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -13385,152 +13385,152 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O67" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P67" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO67" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE67" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>
@@ -13579,16 +13579,16 @@
         <v>4.9</v>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P68" t="n">
         <v>2.08</v>
@@ -13597,134 +13597,134 @@
         <v>1.76</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO68" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-26 20:30:11</t>
+          <t>2026-03-26 22:41:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH68"/>
+  <dimension ref="A1:BH72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.89</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="H4" t="n">
         <v>3.8</v>
@@ -1196,7 +1196,7 @@
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G5" t="n">
         <v>3.4</v>
@@ -1354,7 +1354,7 @@
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1372,7 +1372,7 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1381,13 +1381,13 @@
         <v>4.2</v>
       </c>
       <c r="T5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.91</v>
       </c>
-      <c r="U5" t="n">
-        <v>1.92</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W5" t="n">
         <v>1.41</v>
@@ -1408,7 +1408,7 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
         <v>14</v>
@@ -1456,7 +1456,7 @@
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>8.6</v>
@@ -1468,7 +1468,7 @@
         <v>11</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX5" t="n">
         <v>17.5</v>
@@ -1480,29 +1480,29 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>38</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
         <v>36</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
         <v>10</v>
       </c>
       <c r="AV6" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
         <v>1.03</v>
@@ -1683,7 +1683,7 @@
         <v>11</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
         <v>1.03</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
         <v>3.4</v>
@@ -1745,7 +1745,7 @@
         <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
         <v>1.08</v>
@@ -1760,28 +1760,28 @@
         <v>1.83</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
         <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U7" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
         <v>12</v>
@@ -1841,56 +1841,56 @@
         <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
         <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>16</v>
       </c>
       <c r="BA7" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC7" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6.2</v>
       </c>
       <c r="BD7" t="n">
         <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
         <v>34</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="n">
         <v>3</v>
@@ -1972,7 +1972,7 @@
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>5.1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>2.54</v>
@@ -2333,13 +2333,13 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q10" t="n">
         <v>2.06</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G11" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
@@ -2518,7 +2518,7 @@
         <v>2.84</v>
       </c>
       <c r="K11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,13 +2527,13 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="O11" t="n">
         <v>1.02</v>
       </c>
       <c r="P11" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q11" t="n">
         <v>2.02</v>
@@ -2554,7 +2554,7 @@
         <v>1.21</v>
       </c>
       <c r="W11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -2754,13 +2754,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
         <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
         <v>15.5</v>
@@ -2769,7 +2769,7 @@
         <v>8.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
         <v>30</v>
@@ -2802,7 +2802,7 @@
         <v>330</v>
       </c>
       <c r="AO12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP12" t="n">
         <v>6.8</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3118,13 +3118,13 @@
         <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R14" t="n">
         <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3133,7 +3133,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W14" t="n">
         <v>1.39</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3476,10 @@
         <v>1.76</v>
       </c>
       <c r="G16" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
         <v>5.7</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -3691,22 +3691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R17" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -3903,10 +3903,10 @@
         <v>2.72</v>
       </c>
       <c r="T18" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V18" t="n">
         <v>1.35</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4085,10 +4085,10 @@
         <v>1.36</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="R19" t="n">
         <v>1.23</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4273,7 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O20" t="n">
         <v>1.16</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4643,10 +4643,10 @@
         <v>2.02</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
@@ -4661,16 +4661,16 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="O22" t="n">
         <v>1.05</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
@@ -4685,7 +4685,7 @@
         <v>1.65</v>
       </c>
       <c r="V22" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
         <v>1.98</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G23" t="n">
         <v>3.25</v>
@@ -4840,10 +4840,10 @@
         <v>2.54</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
         <v>3.85</v>
@@ -4879,7 +4879,7 @@
         <v>1.89</v>
       </c>
       <c r="V23" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W23" t="n">
         <v>1.47</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="G24" t="n">
         <v>2.64</v>
       </c>
       <c r="H24" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
@@ -5040,7 +5040,7 @@
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5058,7 +5058,7 @@
         <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R24" t="n">
         <v>1.48</v>
@@ -5076,7 +5076,7 @@
         <v>1.49</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X24" t="n">
         <v>21</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
         <v>1.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X26" t="n">
         <v>28</v>
@@ -5524,7 +5524,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR26" t="n">
         <v>15.5</v>
@@ -5536,7 +5536,7 @@
         <v>11</v>
       </c>
       <c r="AU26" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>9.6</v>
@@ -5566,17 +5566,17 @@
         <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
         <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
         <v>3.15</v>
       </c>
       <c r="I28" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J28" t="n">
         <v>3.4</v>
@@ -5849,10 +5849,10 @@
         <v>1.96</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W28" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -5986,28 +5986,28 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hamilton</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kelty Hearts</t>
+          <t>Cove Rangers</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="G29" t="n">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>2.6</v>
       </c>
       <c r="I29" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="J29" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
         <v>4.1</v>
@@ -6019,146 +6019,146 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="O29" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="T29" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U29" t="n">
-        <v>1.74</v>
+        <v>2.26</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN29" t="n">
         <v>24</v>
       </c>
-      <c r="Z29" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>3.45</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>5.6</v>
+        <v>3.05</v>
       </c>
       <c r="AV29" t="n">
-        <v>11.5</v>
+        <v>3.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.2</v>
+        <v>3.65</v>
       </c>
       <c r="AY29" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="AZ29" t="n">
-        <v>12</v>
+        <v>3.55</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB29" t="n">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="BC29" t="n">
-        <v>12</v>
+        <v>3.85</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Alloa</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Cove Rangers</t>
+          <t>Peterhead</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="G30" t="n">
-        <v>2.88</v>
+        <v>2.28</v>
       </c>
       <c r="H30" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="I30" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="J30" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>1.24</v>
       </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
         <v>1.64</v>
       </c>
       <c r="R30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V30" t="n">
         <v>1.34</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.48</v>
-      </c>
       <c r="W30" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="X30" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AR30" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AV30" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AW30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>3.75</v>
       </c>
-      <c r="AX30" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BA30" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF30" t="n">
-        <v>3.55</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>4.2</v>
       </c>
       <c r="G31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H31" t="n">
         <v>1.86</v>
       </c>
       <c r="I31" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
         <v>4.5</v>
@@ -6422,16 +6422,16 @@
         <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T31" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U31" t="n">
         <v>2.18</v>
       </c>
       <c r="V31" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W31" t="n">
         <v>1.25</v>
@@ -6491,31 +6491,31 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR31" t="n">
         <v>4.8</v>
       </c>
       <c r="AS31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW31" t="n">
         <v>4.8</v>
       </c>
-      <c r="AT31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AX31" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AY31" t="n">
         <v>4.9</v>
@@ -6527,26 +6527,26 @@
         <v>6.2</v>
       </c>
       <c r="BB31" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE31" t="n">
-        <v>3.85</v>
+        <v>3.05</v>
       </c>
       <c r="BF31" t="n">
         <v>4</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6568,179 +6568,179 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Alloa</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Peterhead</t>
+          <t>Kelty Hearts</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="G32" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="H32" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="I32" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
         <v>3.75</v>
       </c>
       <c r="O32" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="U32" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="V32" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.77</v>
+        <v>2.04</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL32" t="n">
         <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO32" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.75</v>
+        <v>14.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT32" t="n">
-        <v>3.45</v>
+        <v>8</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.7</v>
+        <v>16</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY32" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.75</v>
+        <v>16.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB32" t="n">
-        <v>4</v>
+        <v>18.5</v>
       </c>
       <c r="BC32" t="n">
-        <v>3.95</v>
+        <v>17.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.2</v>
+        <v>46</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>4.7</v>
       </c>
       <c r="G33" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H33" t="n">
         <v>1.67</v>
@@ -6798,10 +6798,10 @@
         <v>4.5</v>
       </c>
       <c r="O33" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q33" t="n">
         <v>1.66</v>
@@ -6810,13 +6810,13 @@
         <v>1.49</v>
       </c>
       <c r="S33" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T33" t="n">
         <v>1.69</v>
       </c>
       <c r="U33" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V33" t="n">
         <v>2.2</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -6956,179 +6956,179 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tamworth FC</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.78</v>
+        <v>1.97</v>
       </c>
       <c r="G34" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="H34" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="I34" t="n">
-        <v>2.74</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="K34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N34" t="n">
         <v>3.95</v>
       </c>
-      <c r="L34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4.1</v>
-      </c>
       <c r="O34" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="P34" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="R34" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="T34" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="U34" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="X34" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="Z34" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="AA34" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
         <v>16.5</v>
       </c>
       <c r="AC34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="BA34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BB34" t="n">
         <v>15</v>
       </c>
-      <c r="AE34" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BC34" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.4</v>
+        <v>18</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.7</v>
+        <v>2.08</v>
       </c>
       <c r="BF34" t="n">
-        <v>17</v>
+        <v>2.08</v>
       </c>
       <c r="BG34" t="n">
-        <v>14</v>
+        <v>2.08</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7150,179 +7150,179 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Morecambe</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aldershot</t>
+          <t>Yeovil</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="G35" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="H35" t="n">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N35" t="n">
         <v>4.1</v>
       </c>
-      <c r="K35" t="n">
-        <v>5</v>
-      </c>
-      <c r="L35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N35" t="n">
-        <v>7.6</v>
-      </c>
       <c r="O35" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="P35" t="n">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="R35" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="S35" t="n">
-        <v>1.89</v>
+        <v>2.48</v>
       </c>
       <c r="T35" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="V35" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W35" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="X35" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Z35" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA35" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>27</v>
+        <v>18.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AE35" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK35" t="n">
         <v>30</v>
       </c>
-      <c r="AF35" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>27</v>
-      </c>
       <c r="AL35" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="AM35" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>2</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7344,31 +7344,31 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>York City</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.34</v>
+        <v>4.6</v>
       </c>
       <c r="G36" t="n">
-        <v>1.42</v>
+        <v>5.5</v>
       </c>
       <c r="H36" t="n">
-        <v>7.8</v>
+        <v>1.67</v>
       </c>
       <c r="I36" t="n">
-        <v>12.5</v>
+        <v>1.8</v>
       </c>
       <c r="J36" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="K36" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,153 +7377,153 @@
         <v>1.02</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="R36" t="n">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="S36" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="T36" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="U36" t="n">
         <v>2.08</v>
       </c>
       <c r="V36" t="n">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="W36" t="n">
-        <v>3.35</v>
+        <v>1.22</v>
       </c>
       <c r="X36" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="Z36" t="n">
-        <v>110</v>
+        <v>18</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB36" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AC36" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AD36" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="AE36" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="AF36" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AH36" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI36" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="AJ36" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ36" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU36" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AV36" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW36" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AX36" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="AZ36" t="n">
-        <v>5.2</v>
+        <v>10.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.2</v>
+        <v>16.5</v>
       </c>
       <c r="BB36" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC36" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF36" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,179 +7538,179 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>2.62</v>
+        <v>1.56</v>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>1.66</v>
       </c>
       <c r="J37" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="K37" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.96</v>
+        <v>1.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7732,31 +7732,31 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>York City</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yeovil</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.18</v>
+        <v>1.33</v>
       </c>
       <c r="G38" t="n">
-        <v>2.32</v>
+        <v>1.4</v>
       </c>
       <c r="H38" t="n">
-        <v>3.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>3.65</v>
+        <v>12.5</v>
       </c>
       <c r="J38" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="K38" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7765,146 +7765,146 @@
         <v>1.02</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="P38" t="n">
-        <v>2.24</v>
+        <v>2.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.64</v>
+        <v>1.42</v>
       </c>
       <c r="R38" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="S38" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="T38" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="U38" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="V38" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="W38" t="n">
-        <v>1.75</v>
+        <v>3.5</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y38" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="Z38" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL38" t="n">
         <v>36</v>
       </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="AM38" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD38" t="n">
         <v>20</v>
       </c>
-      <c r="AE38" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU38" t="n">
+      <c r="BE38" t="n">
         <v>5.9</v>
       </c>
-      <c r="AV38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>2</v>
-      </c>
       <c r="BF38" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="BG38" t="n">
-        <v>2</v>
+        <v>5.9</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -7926,179 +7926,179 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Aldershot</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5.8</v>
+        <v>2.28</v>
       </c>
       <c r="G39" t="n">
-        <v>8.199999999999999</v>
+        <v>2.58</v>
       </c>
       <c r="H39" t="n">
-        <v>1.56</v>
+        <v>2.58</v>
       </c>
       <c r="I39" t="n">
-        <v>1.66</v>
+        <v>2.94</v>
       </c>
       <c r="J39" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P39" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -8120,186 +8120,186 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Tamworth FC</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="G40" t="n">
-        <v>2.12</v>
+        <v>3.1</v>
       </c>
       <c r="H40" t="n">
-        <v>3.55</v>
+        <v>2.46</v>
       </c>
       <c r="I40" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N40" t="n">
         <v>4.1</v>
       </c>
-      <c r="J40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3.95</v>
-      </c>
       <c r="O40" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="P40" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="R40" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W40" t="n">
         <v>1.5</v>
       </c>
-      <c r="S40" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="U40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W40" t="n">
-        <v>1.89</v>
-      </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y40" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Z40" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB40" t="n">
         <v>16.5</v>
       </c>
       <c r="AC40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR40" t="n">
         <v>13</v>
       </c>
-      <c r="AD40" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>18</v>
-      </c>
       <c r="AS40" t="n">
-        <v>2.04</v>
+        <v>4.4</v>
       </c>
       <c r="AT40" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW40" t="n">
-        <v>2.04</v>
+        <v>19</v>
       </c>
       <c r="AX40" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AY40" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ40" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>2.04</v>
+        <v>4.5</v>
       </c>
       <c r="BB40" t="n">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="BC40" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD40" t="n">
-        <v>18</v>
+        <v>4.4</v>
       </c>
       <c r="BE40" t="n">
-        <v>2.04</v>
+        <v>4.7</v>
       </c>
       <c r="BF40" t="n">
-        <v>2.04</v>
+        <v>17</v>
       </c>
       <c r="BG40" t="n">
-        <v>2.04</v>
+        <v>14</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8314,103 +8314,103 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Truro City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="G41" t="n">
-        <v>5.5</v>
+        <v>3.25</v>
       </c>
       <c r="H41" t="n">
-        <v>1.67</v>
+        <v>2.62</v>
       </c>
       <c r="I41" t="n">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="K41" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="O41" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="R41" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="S41" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="T41" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="U41" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V41" t="n">
-        <v>2.24</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z41" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AA41" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AC41" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AD41" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE41" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
         <v>1000</v>
       </c>
       <c r="AG41" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AH41" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI41" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
         <v>1000</v>
@@ -8434,37 +8434,37 @@
         <v>1.03</v>
       </c>
       <c r="AQ41" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR41" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AS41" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT41" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW41" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AX41" t="n">
         <v>1.03</v>
       </c>
       <c r="AY41" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ41" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA41" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB41" t="n">
         <v>1.03</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -8508,179 +8508,179 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.32</v>
+        <v>1.86</v>
       </c>
       <c r="G42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q42" t="n">
         <v>2.4</v>
       </c>
-      <c r="H42" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I42" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.58</v>
-      </c>
       <c r="R42" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S42" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="T42" t="n">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="U42" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="V42" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="W42" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="X42" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Z42" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK42" t="n">
         <v>26</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>34</v>
       </c>
       <c r="AL42" t="n">
         <v>60</v>
       </c>
       <c r="AM42" t="n">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="AN42" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AO42" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR42" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AS42" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="AT42" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU42" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV42" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AW42" t="n">
-        <v>50</v>
+        <v>8.4</v>
       </c>
       <c r="AX42" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AY42" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42" t="n">
         <v>21</v>
       </c>
       <c r="BA42" t="n">
-        <v>13.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="BC42" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BD42" t="n">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BE42" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="BG42" t="n">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -8702,179 +8702,179 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Valladolid</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="G43" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="H43" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="I43" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="J43" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K43" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N43" t="n">
-        <v>2.84</v>
+        <v>2.66</v>
       </c>
       <c r="O43" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="P43" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="R43" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S43" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="T43" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="U43" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="V43" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="W43" t="n">
-        <v>1.98</v>
+        <v>1.72</v>
       </c>
       <c r="X43" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y43" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y43" t="n">
-        <v>14</v>
-      </c>
       <c r="Z43" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AA43" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AB43" t="n">
         <v>7.4</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AE43" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AF43" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AG43" t="n">
         <v>12</v>
       </c>
       <c r="AH43" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AI43" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AJ43" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AK43" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AL43" t="n">
         <v>60</v>
       </c>
       <c r="AM43" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AN43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR43" t="n">
         <v>22</v>
       </c>
-      <c r="AO43" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>28</v>
-      </c>
       <c r="AS43" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT43" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU43" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV43" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ43" t="n">
         <v>21</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BB43" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BC43" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BD43" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="BF43" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -8896,127 +8896,127 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>ASD Alcione</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aurora Pro Patria 1919</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.76</v>
+        <v>2.76</v>
       </c>
       <c r="G44" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="I44" t="n">
-        <v>7.2</v>
+        <v>3.25</v>
       </c>
       <c r="J44" t="n">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="K44" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N44" t="n">
-        <v>1.51</v>
+        <v>2.66</v>
       </c>
       <c r="O44" t="n">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P44" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="R44" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S44" t="n">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="T44" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="U44" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V44" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="W44" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="X44" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB44" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC44" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK44" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL44" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM44" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO44" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP44" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR44" t="n">
         <v>1.03</v>
@@ -9028,7 +9028,7 @@
         <v>1.03</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV44" t="n">
         <v>1.03</v>
@@ -9061,14 +9061,14 @@
         <v>1.03</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BG44" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -9090,127 +9090,127 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ASD Alcione</t>
+          <t>SSD Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignanochiampo</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="G45" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="H45" t="n">
-        <v>2.78</v>
+        <v>2.36</v>
       </c>
       <c r="I45" t="n">
         <v>3.25</v>
       </c>
       <c r="J45" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="K45" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N45" t="n">
-        <v>2.66</v>
+        <v>1.54</v>
       </c>
       <c r="O45" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="P45" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.34</v>
+        <v>1.47</v>
       </c>
       <c r="R45" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S45" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="T45" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U45" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V45" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W45" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="X45" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="Y45" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z45" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA45" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD45" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE45" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF45" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG45" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AH45" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI45" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ45" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK45" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL45" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM45" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN45" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO45" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP45" t="n">
         <v>1.03</v>
       </c>
       <c r="AQ45" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR45" t="n">
         <v>1.03</v>
@@ -9222,7 +9222,7 @@
         <v>1.03</v>
       </c>
       <c r="AU45" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV45" t="n">
         <v>1.03</v>
@@ -9255,14 +9255,14 @@
         <v>1.03</v>
       </c>
       <c r="BF45" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG45" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -9284,179 +9284,179 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>SS Virtus Verona 1921</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="G46" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="H46" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I46" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="J46" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K46" t="n">
-        <v>4.6</v>
+        <v>3.25</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N46" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="O46" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="P46" t="n">
-        <v>1.75</v>
+        <v>1.47</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="R46" t="n">
         <v>1.18</v>
       </c>
       <c r="S46" t="n">
-        <v>1.9</v>
+        <v>2.36</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V46" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="W46" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="X46" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB46" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC46" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG46" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI46" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK46" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM46" t="n">
         <v>1000</v>
       </c>
       <c r="AN46" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -9478,31 +9478,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SSD Dolomiti Bellunesi</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arzignanochiampo</t>
+          <t>SS Virtus Verona 1921</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.64</v>
+        <v>2.04</v>
       </c>
       <c r="G47" t="n">
-        <v>3.75</v>
+        <v>2.54</v>
       </c>
       <c r="H47" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="I47" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="J47" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,22 +9511,22 @@
         <v>1.01</v>
       </c>
       <c r="N47" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="O47" t="n">
-        <v>1.02</v>
+        <v>1.3</v>
       </c>
       <c r="P47" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="R47" t="n">
         <v>1.18</v>
       </c>
       <c r="S47" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9535,10 +9535,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="W47" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -9672,55 +9672,55 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Aurora Pro Patria 1919</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.36</v>
+        <v>1.76</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>2.16</v>
       </c>
       <c r="H48" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="I48" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="J48" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="K48" t="n">
-        <v>3.7</v>
+        <v>5.3</v>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M48" t="n">
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="O48" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P48" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="R48" t="n">
         <v>1.18</v>
       </c>
       <c r="S48" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="W48" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -9908,7 +9908,7 @@
         <v>1.81</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R49" t="n">
         <v>1.29</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -10275,7 +10275,7 @@
         <v>3.95</v>
       </c>
       <c r="J51" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="K51" t="n">
         <v>3.2</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G52" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H52" t="n">
         <v>3.75</v>
@@ -10508,7 +10508,7 @@
         <v>1.28</v>
       </c>
       <c r="W52" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -10675,22 +10675,22 @@
         <v>1.01</v>
       </c>
       <c r="N53" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O53" t="n">
         <v>1.28</v>
       </c>
       <c r="P53" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R53" t="n">
         <v>1.21</v>
       </c>
       <c r="S53" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="T53" t="n">
         <v>1.01</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N56" t="n">
         <v>4.4</v>
@@ -11266,7 +11266,7 @@
         <v>2.18</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R56" t="n">
         <v>1.46</v>
@@ -11275,10 +11275,10 @@
         <v>2.88</v>
       </c>
       <c r="T56" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="U56" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="V56" t="n">
         <v>1.61</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
         <v>1.1</v>
       </c>
       <c r="N57" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O57" t="n">
         <v>1.44</v>
@@ -11574,7 +11574,7 @@
         <v>34</v>
       </c>
       <c r="BC57" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD57" t="n">
         <v>10</v>
@@ -11583,21 +11583,21 @@
         <v>11</v>
       </c>
       <c r="BF57" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG57" t="n">
         <v>40</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Uruguayan Segunda Division</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -11612,179 +11612,179 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Plaza Colonia</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>River Plate (Uru)</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="G58" t="n">
-        <v>3.05</v>
+        <v>2.2</v>
       </c>
       <c r="H58" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="I58" t="n">
-        <v>3.65</v>
+        <v>6.8</v>
       </c>
       <c r="J58" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K58" t="n">
-        <v>3.3</v>
+        <v>6.8</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P58" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO58" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG58" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -11836,10 +11836,10 @@
         <v>1.01</v>
       </c>
       <c r="M59" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N59" t="n">
-        <v>1.74</v>
+        <v>3.1</v>
       </c>
       <c r="O59" t="n">
         <v>1.37</v>
@@ -11851,16 +11851,16 @@
         <v>2.2</v>
       </c>
       <c r="R59" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S59" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="T59" t="n">
-        <v>1.89</v>
+        <v>2.04</v>
       </c>
       <c r="U59" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="V59" t="n">
         <v>1.16</v>
@@ -11869,123 +11869,123 @@
         <v>2.32</v>
       </c>
       <c r="X59" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y59" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z59" t="n">
         <v>60</v>
       </c>
       <c r="AA59" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB59" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS59" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC59" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF59" t="n">
+      <c r="AT59" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV59" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW59" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX59" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY59" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ59" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA59" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB59" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC59" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD59" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF59" t="n">
         <v>11</v>
       </c>
-      <c r="AG59" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH59" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO59" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP59" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS59" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AT59" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX59" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY59" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AZ59" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BA59" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB59" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BC59" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BD59" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BE59" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BF59" t="n">
-        <v>2.68</v>
-      </c>
       <c r="BG59" t="n">
-        <v>2.68</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Uruguayan Segunda Division</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12000,179 +12000,179 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Plaza Colonia</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>River Plate (Uru)</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="G60" t="n">
-        <v>2.2</v>
+        <v>3.05</v>
       </c>
       <c r="H60" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="I60" t="n">
-        <v>6.8</v>
+        <v>3.65</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="K60" t="n">
-        <v>6.8</v>
+        <v>3.3</v>
       </c>
       <c r="L60" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="R60" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO60" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AT60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AU60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AV60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AZ60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BA60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BC60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -12311,52 +12311,52 @@
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF61" t="n">
         <v>1.01</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G62" t="n">
         <v>4.5</v>
@@ -12406,7 +12406,7 @@
         <v>2.18</v>
       </c>
       <c r="I62" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J62" t="n">
         <v>3.2</v>
@@ -12415,22 +12415,22 @@
         <v>3.7</v>
       </c>
       <c r="L62" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="M62" t="n">
         <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="O62" t="n">
         <v>1.36</v>
       </c>
       <c r="P62" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R62" t="n">
         <v>1.24</v>
@@ -12439,13 +12439,13 @@
         <v>3.2</v>
       </c>
       <c r="T62" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="U62" t="n">
         <v>1.68</v>
       </c>
       <c r="V62" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W62" t="n">
         <v>1.29</v>
@@ -12508,34 +12508,34 @@
         <v>8</v>
       </c>
       <c r="AQ62" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR62" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS62" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT62" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU62" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AV62" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW62" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX62" t="n">
         <v>16.5</v>
       </c>
-      <c r="AX62" t="n">
-        <v>16</v>
-      </c>
       <c r="AY62" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ62" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BA62" t="n">
         <v>1.03</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -12633,10 +12633,10 @@
         <v>2.88</v>
       </c>
       <c r="T63" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U63" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V63" t="n">
         <v>1.5</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -12818,7 +12818,7 @@
         <v>1.71</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R64" t="n">
         <v>1.19</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -12982,13 +12982,13 @@
         <v>1.35</v>
       </c>
       <c r="G65" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H65" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I65" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="J65" t="n">
         <v>4.5</v>
@@ -13000,10 +13000,10 @@
         <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N65" t="n">
-        <v>1.76</v>
+        <v>3.25</v>
       </c>
       <c r="O65" t="n">
         <v>1.37</v>
@@ -13015,134 +13015,134 @@
         <v>2.1</v>
       </c>
       <c r="R65" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S65" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="T65" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="U65" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="V65" t="n">
         <v>1.07</v>
       </c>
       <c r="W65" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X65" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="Y65" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="Z65" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA65" t="n">
         <v>1000</v>
       </c>
       <c r="AB65" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>320</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR65" t="n">
         <v>8.4</v>
       </c>
-      <c r="AC65" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD65" t="n">
-        <v>70</v>
-      </c>
-      <c r="AE65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG65" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH65" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK65" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO65" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP65" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AS65" t="n">
-        <v>2.38</v>
+        <v>9</v>
       </c>
       <c r="AT65" t="n">
-        <v>1.86</v>
+        <v>5.4</v>
       </c>
       <c r="AU65" t="n">
-        <v>2.06</v>
+        <v>5.2</v>
       </c>
       <c r="AV65" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="AW65" t="n">
-        <v>2.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX65" t="n">
-        <v>1.9</v>
+        <v>5.9</v>
       </c>
       <c r="AY65" t="n">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ65" t="n">
-        <v>2.28</v>
+        <v>7.4</v>
       </c>
       <c r="BA65" t="n">
-        <v>2.38</v>
+        <v>8.6</v>
       </c>
       <c r="BB65" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
       </c>
       <c r="BC65" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="BD65" t="n">
-        <v>2.32</v>
+        <v>7.8</v>
       </c>
       <c r="BE65" t="n">
-        <v>2.38</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF65" t="n">
-        <v>2.38</v>
+        <v>6.4</v>
       </c>
       <c r="BG65" t="n">
-        <v>2.38</v>
+        <v>9</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -13406,7 +13406,7 @@
         <v>1.18</v>
       </c>
       <c r="S67" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="T67" t="n">
         <v>1.01</v>
@@ -13475,52 +13475,52 @@
         <v>1000</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE67" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF67" t="n">
         <v>1.01</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,783 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-26 22:41:56</t>
+          <t>2026-03-27 00:54:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks FC</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H69" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J69" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE69" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH69" t="inlineStr">
+        <is>
+          <t>2026-03-27 00:54:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Orange County Blues</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H70" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I70" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K70" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S70" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W70" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV70" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX70" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY70" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ70" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA70" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB70" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC70" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD70" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF70" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG70" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH70" t="inlineStr">
+        <is>
+          <t>2026-03-27 00:54:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>22:20:00</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I71" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R71" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S71" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W71" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X71" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>150</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>60</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>460</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>410</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>570</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV71" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW71" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX71" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY71" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ71" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA71" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB71" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC71" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD71" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE71" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF71" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG71" t="n">
+        <v>8</v>
+      </c>
+      <c r="BH71" t="inlineStr">
+        <is>
+          <t>2026-03-27 00:54:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>US United Soccer League</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>23:30:00</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights FC</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Monterey Bay FC</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G72" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H72" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I72" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K72" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S72" t="n">
+        <v>4</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W72" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE72" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG72" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH72" t="inlineStr">
+        <is>
+          <t>2026-03-27 00:54:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.74</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
         <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>1.92</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1020,7 +1020,7 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>2.98</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H4" t="n">
         <v>2.12</v>
       </c>
       <c r="I4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
         <v>3.5</v>
@@ -1193,7 +1193,7 @@
         <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W4" t="n">
         <v>1.39</v>
@@ -1253,40 +1253,40 @@
         <v>16</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.75</v>
+        <v>9.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="AS4" t="n">
         <v>4.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.65</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.2</v>
+        <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.3</v>
+        <v>21</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
         <v>4.7</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="G5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H5" t="n">
         <v>2.28</v>
       </c>
       <c r="I5" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J5" t="n">
         <v>2.98</v>
@@ -1357,7 +1357,7 @@
         <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
@@ -1375,19 +1375,19 @@
         <v>1.79</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W5" t="n">
         <v>1.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
@@ -1557,55 +1557,55 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
         <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE6" t="n">
         <v>55</v>
@@ -1617,10 +1617,10 @@
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
         <v>27</v>
@@ -1632,71 +1632,71 @@
         <v>36</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>13</v>
       </c>
-      <c r="AO6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AR6" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.72</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.58</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.9</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.15</v>
+        <v>4.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>2.82</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>2.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.35</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.15</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.05</v>
+        <v>19.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.98</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.72</v>
+        <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1760,19 +1760,19 @@
         <v>1.74</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
       </c>
       <c r="S7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
         <v>1.91</v>
       </c>
       <c r="U7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V7" t="n">
         <v>1.64</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
         <v>32</v>
@@ -1844,7 +1844,7 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
         <v>8.6</v>
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX7" t="n">
         <v>17.5</v>
@@ -1868,10 +1868,10 @@
         <v>13.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB7" t="n">
         <v>6.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7</v>
       </c>
       <c r="BC7" t="n">
         <v>32</v>
@@ -1880,17 +1880,17 @@
         <v>42</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG7" t="n">
         <v>6.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.28</v>
       </c>
       <c r="G8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="H8" t="n">
         <v>12.5</v>
@@ -1951,10 +1951,10 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
@@ -1966,19 +1966,19 @@
         <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="V8" t="n">
         <v>1.07</v>
       </c>
       <c r="W8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X8" t="n">
         <v>23</v>
       </c>
       <c r="Y8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Z8" t="n">
         <v>160</v>
@@ -1987,13 +1987,13 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AE8" t="n">
         <v>300</v>
@@ -2071,7 +2071,7 @@
         <v>11</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE8" t="n">
         <v>1.03</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I9" t="n">
         <v>3.6</v>
@@ -2133,7 +2133,7 @@
         <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
@@ -2145,7 +2145,7 @@
         <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
         <v>2.1</v>
@@ -2154,10 +2154,10 @@
         <v>1.32</v>
       </c>
       <c r="S9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
@@ -2181,7 +2181,7 @@
         <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.800000000000001</v>
@@ -2232,7 +2232,7 @@
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
         <v>8.4</v>
@@ -2244,7 +2244,7 @@
         <v>12.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2259,26 +2259,26 @@
         <v>44</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I10" t="n">
         <v>1.86</v>
@@ -2327,19 +2327,19 @@
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O10" t="n">
         <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q10" t="n">
         <v>2.64</v>
@@ -2360,13 +2360,13 @@
         <v>2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X10" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z10" t="n">
         <v>10.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>1.58</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.02</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,22 +2569,22 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
         <v>1000</v>
@@ -2611,7 +2611,7 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.03</v>
@@ -2623,10 +2623,10 @@
         <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AV11" t="n">
         <v>1.03</v>
@@ -2659,14 +2659,14 @@
         <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2697,91 +2697,91 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>1.47</v>
+        <v>2.64</v>
       </c>
       <c r="O12" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
         <v>1.51</v>
       </c>
       <c r="O13" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
         <v>1.51</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3088,167 +3088,167 @@
         <v>3.55</v>
       </c>
       <c r="G14" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
       </c>
       <c r="I14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW14" t="n">
         <v>3.75</v>
       </c>
-      <c r="L14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3282,55 +3282,55 @@
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
         <v>2.06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="J15" t="n">
         <v>3.35</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
         <v>1.93</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="R15" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W15" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3348,7 +3348,7 @@
         <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G17" t="n">
         <v>3.6</v>
@@ -3691,10 +3691,10 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
         <v>1.96</v>
@@ -3706,13 +3706,13 @@
         <v>1.37</v>
       </c>
       <c r="S17" t="n">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V17" t="n">
         <v>1.67</v>
@@ -3721,116 +3721,116 @@
         <v>1.39</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA17" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AB17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX17" t="n">
         <v>18</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AY17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>1.76</v>
+        <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.91</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.91</v>
+        <v>4.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.91</v>
+        <v>28</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.91</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.91</v>
+        <v>4.9</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.91</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.91</v>
+        <v>13.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>2.04</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
@@ -3894,7 +3894,7 @@
         <v>1.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R18" t="n">
         <v>1.25</v>
@@ -3912,7 +3912,7 @@
         <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4064,10 +4064,10 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
@@ -4076,13 +4076,13 @@
         <v>1.35</v>
       </c>
       <c r="M19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>1.74</v>
+        <v>3.5</v>
       </c>
       <c r="O19" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P19" t="n">
         <v>1.74</v>
@@ -4091,64 +4091,64 @@
         <v>1.96</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
         <v>20</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>23</v>
-      </c>
       <c r="AG19" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AK19" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.96</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.84</v>
+        <v>3.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.87</v>
+        <v>3.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.96</v>
+        <v>4.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.96</v>
+        <v>3.85</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.96</v>
+        <v>4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4252,28 +4252,28 @@
         <v>1.76</v>
       </c>
       <c r="G20" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="H20" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
         <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>5.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.14</v>
@@ -4282,25 +4282,25 @@
         <v>2.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S20" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="T20" t="n">
         <v>1.48</v>
       </c>
       <c r="U20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.47</v>
+        <v>4.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.47</v>
+        <v>4.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.47</v>
+        <v>3.85</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.38</v>
+        <v>4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.35</v>
+        <v>3.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.39</v>
+        <v>4.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.47</v>
+        <v>4.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.38</v>
+        <v>4</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.34</v>
+        <v>3.7</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.47</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.47</v>
+        <v>4.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.38</v>
+        <v>4.1</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.47</v>
+        <v>4.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.47</v>
+        <v>3.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4443,46 +4443,46 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="G21" t="n">
         <v>6.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="I21" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
         <v>2.78</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="P21" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
         <v>2.02</v>
@@ -4491,10 +4491,10 @@
         <v>1.79</v>
       </c>
       <c r="V21" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="W21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="G23" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="H23" t="n">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="I23" t="n">
         <v>2.98</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
         <v>4.1</v>
@@ -4882,7 +4882,7 @@
         <v>1.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5034,161 +5034,161 @@
         <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="J24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.05</v>
       </c>
-      <c r="K24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3</v>
-      </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="V24" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="W24" t="n">
         <v>1.96</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>11</v>
       </c>
-      <c r="AC24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AR24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV24" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AW24" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5222,22 +5222,22 @@
         <v>2.68</v>
       </c>
       <c r="G25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="H25" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -5246,7 +5246,7 @@
         <v>3.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P25" t="n">
         <v>1.94</v>
@@ -5258,131 +5258,131 @@
         <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="U25" t="n">
-        <v>1.92</v>
+        <v>2.16</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W25" t="n">
         <v>1.45</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC25" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AG25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK25" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO25" t="n">
         <v>27</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW25" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AX25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BG25" t="n">
         <v>18</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5437,13 +5437,13 @@
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O26" t="n">
         <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
         <v>1.72</v>
@@ -5455,10 +5455,10 @@
         <v>2.78</v>
       </c>
       <c r="T26" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U26" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V26" t="n">
         <v>1.49</v>
@@ -5470,10 +5470,10 @@
         <v>21</v>
       </c>
       <c r="Y26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
         <v>48</v>
@@ -5485,7 +5485,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>32</v>
@@ -5530,10 +5530,10 @@
         <v>15.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AU26" t="n">
         <v>6.6</v>
@@ -5554,19 +5554,19 @@
         <v>11.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC26" t="n">
         <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BE26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
         <v>11.5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G27" t="n">
         <v>3.1</v>
       </c>
       <c r="H27" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="I27" t="n">
         <v>3.15</v>
@@ -5625,10 +5625,10 @@
         <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="M27" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N27" t="n">
         <v>4.2</v>
@@ -5643,22 +5643,22 @@
         <v>1.72</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="T27" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="U27" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="V27" t="n">
         <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X27" t="n">
         <v>1000</v>
@@ -5676,10 +5676,10 @@
         <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
@@ -5688,10 +5688,10 @@
         <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
@@ -5718,7 +5718,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR27" t="n">
         <v>1.03</v>
@@ -5727,25 +5727,25 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW27" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AX27" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA27" t="n">
         <v>1.03</v>
@@ -5763,14 +5763,14 @@
         <v>1.03</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>2.4</v>
       </c>
       <c r="G28" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H28" t="n">
         <v>2.58</v>
@@ -5813,16 +5813,16 @@
         <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N28" t="n">
         <v>4.9</v>
@@ -5909,7 +5909,7 @@
         <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AQ28" t="n">
         <v>11.5</v>
@@ -5918,13 +5918,13 @@
         <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>9.6</v>
@@ -5942,29 +5942,29 @@
         <v>11</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="BC28" t="n">
         <v>17.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BF28" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG28" t="n">
         <v>12.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -5995,170 +5995,170 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="H29" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
         <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.06</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
         <v>1.59</v>
       </c>
       <c r="R29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR29" t="n">
         <v>1.39</v>
       </c>
-      <c r="S29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AS29" t="n">
-        <v>1.95</v>
+        <v>1.21</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.26</v>
+        <v>1.39</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.24</v>
+        <v>1.55</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="AY29" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="BB29" t="n">
         <v>17.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.44</v>
+        <v>1.23</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.95</v>
+        <v>1.49</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.95</v>
+        <v>1.21</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.38</v>
+        <v>1.75</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.72</v>
+        <v>1.48</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>2.1</v>
       </c>
       <c r="G30" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H30" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I30" t="n">
         <v>3.9</v>
@@ -6213,7 +6213,7 @@
         <v>1.03</v>
       </c>
       <c r="N30" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="O30" t="n">
         <v>1.22</v>
@@ -6222,28 +6222,28 @@
         <v>2.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R30" t="n">
         <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="T30" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="U30" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W30" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y30" t="n">
         <v>1000</v>
@@ -6297,16 +6297,16 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ30" t="n">
         <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
@@ -6318,7 +6318,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="AX30" t="n">
         <v>10</v>
@@ -6330,29 +6330,29 @@
         <v>10</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BB30" t="n">
         <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G31" t="n">
         <v>1.96</v>
@@ -6395,13 +6395,13 @@
         <v>4.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -6413,10 +6413,10 @@
         <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="R31" t="n">
         <v>1.37</v>
@@ -6428,16 +6428,16 @@
         <v>1.79</v>
       </c>
       <c r="U31" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
         <v>2.04</v>
       </c>
       <c r="X31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y31" t="n">
         <v>17</v>
@@ -6446,13 +6446,13 @@
         <v>36</v>
       </c>
       <c r="AA31" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC31" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AD31" t="n">
         <v>18.5</v>
@@ -6470,7 +6470,7 @@
         <v>19.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
         <v>22</v>
@@ -6482,22 +6482,22 @@
         <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN31" t="n">
         <v>13</v>
       </c>
       <c r="AO31" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP31" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS31" t="n">
         <v>1.03</v>
@@ -6506,10 +6506,10 @@
         <v>1.03</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV31" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
         <v>1.03</v>
@@ -6518,7 +6518,7 @@
         <v>1.03</v>
       </c>
       <c r="AY31" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ31" t="n">
         <v>13.5</v>
@@ -6542,11 +6542,11 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BG31" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>2.1</v>
       </c>
       <c r="G32" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H32" t="n">
         <v>3.3</v>
       </c>
       <c r="I32" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.24</v>
@@ -6604,31 +6604,31 @@
         <v>3.75</v>
       </c>
       <c r="O32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P32" t="n">
         <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S32" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="T32" t="n">
         <v>1.64</v>
       </c>
       <c r="U32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W32" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6685,28 +6685,28 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW32" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>4.2</v>
       </c>
       <c r="AX32" t="n">
         <v>11</v>
@@ -6715,32 +6715,32 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="BA32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC32" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB32" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD32" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="BE32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG32" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6777,19 +6777,19 @@
         <v>4.9</v>
       </c>
       <c r="H33" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="I33" t="n">
         <v>2.04</v>
       </c>
       <c r="J33" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
@@ -6879,7 +6879,7 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AQ33" t="n">
         <v>4.5</v>
@@ -6927,14 +6927,14 @@
         <v>3.1</v>
       </c>
       <c r="BF33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG33" t="n">
         <v>4.7</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -6965,170 +6965,170 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.96</v>
+        <v>2.46</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H34" t="n">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
-        <v>1.36</v>
+        <v>2.62</v>
       </c>
       <c r="K34" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O34" t="n">
         <v>1.24</v>
       </c>
       <c r="P34" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="R34" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W34" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
         <v>140</v>
       </c>
       <c r="AK35" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL35" t="n">
         <v>70</v>
@@ -7270,7 +7270,7 @@
         <v>15</v>
       </c>
       <c r="AQ35" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AR35" t="n">
         <v>8.800000000000001</v>
@@ -7291,7 +7291,7 @@
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7374,13 +7374,13 @@
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P36" t="n">
         <v>2.26</v>
@@ -7395,10 +7395,10 @@
         <v>2.72</v>
       </c>
       <c r="T36" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="U36" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V36" t="n">
         <v>1.33</v>
@@ -7407,116 +7407,116 @@
         <v>1.89</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y36" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Z36" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD36" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV36" t="n">
         <v>13</v>
       </c>
-      <c r="AD36" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>10</v>
-      </c>
       <c r="AW36" t="n">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="AX36" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY36" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="AZ36" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA36" t="n">
         <v>7.2</v>
       </c>
-      <c r="AZ36" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.08</v>
-      </c>
       <c r="BB36" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="BC36" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>18</v>
+        <v>6.6</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.08</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.08</v>
+        <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.18</v>
       </c>
       <c r="G37" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H37" t="n">
         <v>3.2</v>
@@ -7565,13 +7565,13 @@
         <v>3.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M37" t="n">
         <v>1.04</v>
       </c>
       <c r="N37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O37" t="n">
         <v>1.21</v>
@@ -7589,7 +7589,7 @@
         <v>2.58</v>
       </c>
       <c r="T37" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U37" t="n">
         <v>2.38</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="G38" t="n">
         <v>6.8</v>
@@ -7774,7 +7774,7 @@
         <v>2.34</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>4.6</v>
       </c>
       <c r="G39" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H39" t="n">
         <v>1.68</v>
@@ -7968,13 +7968,13 @@
         <v>2.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R39" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="S39" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="T39" t="n">
         <v>1.64</v>
@@ -8076,13 +8076,13 @@
         <v>14.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BD39" t="n">
         <v>38</v>
@@ -8094,11 +8094,11 @@
         <v>40</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8186,7 @@
         <v>32</v>
       </c>
       <c r="Y40" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Z40" t="n">
         <v>110</v>
@@ -8201,7 +8201,7 @@
         <v>970</v>
       </c>
       <c r="AD40" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE40" t="n">
         <v>150</v>
@@ -8210,7 +8210,7 @@
         <v>970</v>
       </c>
       <c r="AG40" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH40" t="n">
         <v>26</v>
@@ -8222,7 +8222,7 @@
         <v>970</v>
       </c>
       <c r="AK40" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AL40" t="n">
         <v>30</v>
@@ -8237,43 +8237,43 @@
         <v>140</v>
       </c>
       <c r="AP40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS40" t="n">
         <v>6.4</v>
       </c>
-      <c r="AR40" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AT40" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU40" t="n">
         <v>10.5</v>
       </c>
       <c r="AV40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW40" t="n">
         <v>6.4</v>
       </c>
-      <c r="AW40" t="n">
-        <v>7</v>
-      </c>
       <c r="AX40" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AY40" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AZ40" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA40" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB40" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC40" t="n">
         <v>9.800000000000001</v>
@@ -8282,17 +8282,17 @@
         <v>20</v>
       </c>
       <c r="BE40" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF40" t="n">
         <v>4</v>
       </c>
       <c r="BG40" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G41" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H41" t="n">
         <v>2.64</v>
@@ -8347,34 +8347,34 @@
         <v>1.02</v>
       </c>
       <c r="N41" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="O41" t="n">
         <v>1.15</v>
       </c>
       <c r="P41" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R41" t="n">
         <v>1.73</v>
       </c>
       <c r="S41" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T41" t="n">
         <v>1.44</v>
       </c>
       <c r="U41" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V41" t="n">
         <v>1.51</v>
       </c>
       <c r="W41" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X41" t="n">
         <v>36</v>
@@ -8392,13 +8392,13 @@
         <v>22</v>
       </c>
       <c r="AC41" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AD41" t="n">
         <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF41" t="n">
         <v>22</v>
@@ -8413,13 +8413,13 @@
         <v>32</v>
       </c>
       <c r="AJ41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK41" t="n">
         <v>25</v>
       </c>
       <c r="AL41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM41" t="n">
         <v>48</v>
@@ -8437,16 +8437,16 @@
         <v>14</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS41" t="n">
         <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU41" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
         <v>1.01</v>
@@ -8470,10 +8470,10 @@
         <v>1.01</v>
       </c>
       <c r="BC41" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BE41" t="n">
         <v>30</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H42" t="n">
         <v>2.46</v>
       </c>
       <c r="I42" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J42" t="n">
         <v>3.2</v>
@@ -8535,13 +8535,13 @@
         <v>3.85</v>
       </c>
       <c r="L42" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M42" t="n">
         <v>1.06</v>
       </c>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O42" t="n">
         <v>1.28</v>
@@ -8574,22 +8574,22 @@
         <v>20</v>
       </c>
       <c r="Y42" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AA42" t="n">
         <v>38</v>
       </c>
       <c r="AB42" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AC42" t="n">
         <v>10.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AE42" t="n">
         <v>27</v>
@@ -8598,10 +8598,10 @@
         <v>22</v>
       </c>
       <c r="AG42" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH42" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI42" t="n">
         <v>42</v>
@@ -8610,13 +8610,13 @@
         <v>55</v>
       </c>
       <c r="AK42" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL42" t="n">
         <v>40</v>
       </c>
       <c r="AM42" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN42" t="n">
         <v>32</v>
@@ -8625,7 +8625,7 @@
         <v>24</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ42" t="n">
         <v>9.199999999999999</v>
@@ -8634,10 +8634,10 @@
         <v>13</v>
       </c>
       <c r="AS42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT42" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU42" t="n">
         <v>6.4</v>
@@ -8658,19 +8658,19 @@
         <v>11.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC42" t="n">
         <v>6.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF42" t="n">
         <v>17</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -8905,55 +8905,55 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G44" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H44" t="n">
         <v>5.1</v>
       </c>
       <c r="I44" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J44" t="n">
         <v>3.35</v>
       </c>
       <c r="K44" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O44" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P44" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V44" t="n">
         <v>1.21</v>
-      </c>
-      <c r="S44" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.2</v>
       </c>
       <c r="W44" t="n">
         <v>2.04</v>
@@ -8971,7 +8971,7 @@
         <v>180</v>
       </c>
       <c r="AB44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC44" t="n">
         <v>8</v>
@@ -8983,7 +8983,7 @@
         <v>110</v>
       </c>
       <c r="AF44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG44" t="n">
         <v>11.5</v>
@@ -9016,37 +9016,37 @@
         <v>9</v>
       </c>
       <c r="AQ44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR44" t="n">
         <v>28</v>
       </c>
       <c r="AS44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT44" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV44" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AW44" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX44" t="n">
         <v>9</v>
       </c>
       <c r="AY44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ44" t="n">
         <v>21</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB44" t="n">
         <v>18</v>
@@ -9058,17 +9058,17 @@
         <v>44</v>
       </c>
       <c r="BE44" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF44" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         <v>2.36</v>
       </c>
       <c r="H45" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I45" t="n">
         <v>3.9</v>
@@ -9117,13 +9117,13 @@
         <v>3.3</v>
       </c>
       <c r="L45" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M45" t="n">
         <v>1.12</v>
       </c>
       <c r="N45" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O45" t="n">
         <v>1.55</v>
@@ -9144,7 +9144,7 @@
         <v>2.14</v>
       </c>
       <c r="U45" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V45" t="n">
         <v>1.34</v>
@@ -9171,7 +9171,7 @@
         <v>7.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE45" t="n">
         <v>65</v>
@@ -9228,7 +9228,7 @@
         <v>15</v>
       </c>
       <c r="AW45" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX45" t="n">
         <v>11.5</v>
@@ -9246,23 +9246,23 @@
         <v>28</v>
       </c>
       <c r="BC45" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD45" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE45" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BF45" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG45" t="n">
         <v>13</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -9317,7 +9317,7 @@
         <v>1.11</v>
       </c>
       <c r="N46" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O46" t="n">
         <v>1.49</v>
@@ -9335,10 +9335,10 @@
         <v>4.8</v>
       </c>
       <c r="T46" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U46" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="V46" t="n">
         <v>1.45</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -9487,58 +9487,58 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="G47" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="H47" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="I47" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J47" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="K47" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="L47" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M47" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N47" t="n">
-        <v>1.54</v>
+        <v>2.88</v>
       </c>
       <c r="O47" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P47" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.47</v>
+        <v>2.3</v>
       </c>
       <c r="R47" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S47" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V47" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W47" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9556,7 +9556,7 @@
         <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD47" t="n">
         <v>1000</v>
@@ -9595,62 +9595,62 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
         <v>2.52</v>
       </c>
       <c r="G48" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H48" t="n">
         <v>3.25</v>
@@ -9732,7 +9732,7 @@
         <v>1.37</v>
       </c>
       <c r="W48" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X48" t="n">
         <v>10.5</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
         <v>4.2</v>
       </c>
       <c r="J49" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K49" t="n">
         <v>3.75</v>
@@ -9896,19 +9896,19 @@
         <v>1.01</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>1.76</v>
+        <v>3.45</v>
       </c>
       <c r="O49" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="P49" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R49" t="n">
         <v>1.32</v>
@@ -9917,10 +9917,10 @@
         <v>3.65</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V49" t="n">
         <v>1.32</v>
@@ -9929,7 +9929,7 @@
         <v>1.78</v>
       </c>
       <c r="X49" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y49" t="n">
         <v>15.5</v>
@@ -9944,7 +9944,7 @@
         <v>10.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD49" t="n">
         <v>18</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -10269,13 +10269,13 @@
         <v>2.18</v>
       </c>
       <c r="H51" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K51" t="n">
         <v>3.65</v>
@@ -10284,19 +10284,19 @@
         <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N51" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O51" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R51" t="n">
         <v>1.3</v>
@@ -10305,13 +10305,13 @@
         <v>4</v>
       </c>
       <c r="T51" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U51" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V51" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W51" t="n">
         <v>1.84</v>
@@ -10362,10 +10362,10 @@
         <v>44</v>
       </c>
       <c r="AM51" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN51" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO51" t="n">
         <v>65</v>
@@ -10374,7 +10374,7 @@
         <v>11</v>
       </c>
       <c r="AQ51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR51" t="n">
         <v>24</v>
@@ -10386,7 +10386,7 @@
         <v>7.8</v>
       </c>
       <c r="AU51" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV51" t="n">
         <v>13.5</v>
@@ -10395,7 +10395,7 @@
         <v>13</v>
       </c>
       <c r="AX51" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY51" t="n">
         <v>10</v>
@@ -10404,7 +10404,7 @@
         <v>17.5</v>
       </c>
       <c r="BA51" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB51" t="n">
         <v>24</v>
@@ -10416,7 +10416,7 @@
         <v>12</v>
       </c>
       <c r="BE51" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF51" t="n">
         <v>17.5</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -10460,19 +10460,19 @@
         <v>2.2</v>
       </c>
       <c r="G52" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H52" t="n">
         <v>2.76</v>
       </c>
       <c r="I52" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J52" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K52" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10481,146 +10481,146 @@
         <v>1.02</v>
       </c>
       <c r="N52" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P52" t="n">
         <v>3.3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3.25</v>
       </c>
       <c r="Q52" t="n">
         <v>1.37</v>
       </c>
       <c r="R52" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="S52" t="n">
-        <v>1.37</v>
+        <v>1.8</v>
       </c>
       <c r="T52" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="U52" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="V52" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W52" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X52" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y52" t="n">
+        <v>26</v>
+      </c>
+      <c r="Z52" t="n">
         <v>34</v>
       </c>
-      <c r="Z52" t="n">
-        <v>40</v>
-      </c>
       <c r="AA52" t="n">
         <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AC52" t="n">
         <v>970</v>
       </c>
       <c r="AD52" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE52" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="AF52" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AG52" t="n">
         <v>970</v>
       </c>
       <c r="AH52" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI52" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AJ52" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM52" t="n">
         <v>46</v>
       </c>
-      <c r="AK52" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>55</v>
-      </c>
       <c r="AN52" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.38</v>
+        <v>5.9</v>
       </c>
       <c r="AQ52" t="n">
-        <v>2.32</v>
+        <v>5.3</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.34</v>
+        <v>5.6</v>
       </c>
       <c r="AS52" t="n">
-        <v>2.48</v>
+        <v>6</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.3</v>
+        <v>16.5</v>
       </c>
       <c r="AU52" t="n">
-        <v>2.18</v>
+        <v>9.6</v>
       </c>
       <c r="AV52" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG52" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW52" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>2.48</v>
-      </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -10657,13 +10657,13 @@
         <v>3</v>
       </c>
       <c r="H53" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I53" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="J53" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="K53" t="n">
         <v>3.2</v>
@@ -10678,7 +10678,7 @@
         <v>2.36</v>
       </c>
       <c r="O53" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P53" t="n">
         <v>1.45</v>
@@ -10693,13 +10693,13 @@
         <v>5.7</v>
       </c>
       <c r="T53" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U53" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V53" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="W53" t="n">
         <v>1.5</v>
@@ -10723,10 +10723,10 @@
         <v>8.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE53" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF53" t="n">
         <v>20</v>
@@ -10735,16 +10735,16 @@
         <v>16.5</v>
       </c>
       <c r="AH53" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI53" t="n">
         <v>1000</v>
       </c>
       <c r="AJ53" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK53" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL53" t="n">
         <v>1000</v>
@@ -10753,68 +10753,68 @@
         <v>1000</v>
       </c>
       <c r="AN53" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO53" t="n">
         <v>1000</v>
       </c>
       <c r="AP53" t="n">
-        <v>1.94</v>
+        <v>5.8</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.98</v>
+        <v>6.6</v>
       </c>
       <c r="AR53" t="n">
-        <v>2.22</v>
+        <v>15</v>
       </c>
       <c r="AS53" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="AT53" t="n">
-        <v>1.93</v>
+        <v>5.8</v>
       </c>
       <c r="AU53" t="n">
-        <v>1.89</v>
+        <v>5.3</v>
       </c>
       <c r="AV53" t="n">
-        <v>2.42</v>
+        <v>11</v>
       </c>
       <c r="AW53" t="n">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="AX53" t="n">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="AY53" t="n">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="AZ53" t="n">
-        <v>2.42</v>
+        <v>17.5</v>
       </c>
       <c r="BA53" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BB53" t="n">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="BC53" t="n">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="BD53" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BE53" t="n">
-        <v>2.42</v>
+        <v>4.3</v>
       </c>
       <c r="BF53" t="n">
-        <v>2.42</v>
+        <v>4.1</v>
       </c>
       <c r="BG53" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -10857,7 +10857,7 @@
         <v>4.5</v>
       </c>
       <c r="J54" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K54" t="n">
         <v>3.35</v>
@@ -10866,28 +10866,28 @@
         <v>1.01</v>
       </c>
       <c r="M54" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N54" t="n">
         <v>1.48</v>
       </c>
       <c r="O54" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="P54" t="n">
         <v>1.48</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R54" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S54" t="n">
         <v>4.8</v>
       </c>
       <c r="T54" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U54" t="n">
         <v>1.52</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -11042,19 +11042,19 @@
         <v>2.46</v>
       </c>
       <c r="G55" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="H55" t="n">
         <v>2.36</v>
       </c>
       <c r="I55" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11063,22 +11063,22 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O55" t="n">
         <v>1.28</v>
       </c>
       <c r="P55" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.28</v>
+        <v>1.84</v>
       </c>
       <c r="R55" t="n">
         <v>1.21</v>
       </c>
       <c r="S55" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -11087,10 +11087,10 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W55" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -11245,7 +11245,7 @@
         <v>5.7</v>
       </c>
       <c r="J56" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K56" t="n">
         <v>4.1</v>
@@ -11254,13 +11254,13 @@
         <v>1.01</v>
       </c>
       <c r="M56" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N56" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="O56" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P56" t="n">
         <v>1.91</v>
@@ -11269,134 +11269,134 @@
         <v>1.92</v>
       </c>
       <c r="R56" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S56" t="n">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="T56" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U56" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V56" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W56" t="n">
         <v>2</v>
       </c>
       <c r="X56" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y56" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z56" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA56" t="n">
         <v>1000</v>
       </c>
       <c r="AB56" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC56" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD56" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE56" t="n">
         <v>1000</v>
       </c>
       <c r="AF56" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG56" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH56" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI56" t="n">
         <v>1000</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK56" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL56" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM56" t="n">
         <v>1000</v>
       </c>
       <c r="AN56" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO56" t="n">
         <v>1000</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT56" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AV56" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AZ56" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA56" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BC56" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD56" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -11430,10 +11430,10 @@
         <v>2.16</v>
       </c>
       <c r="G57" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="H57" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I57" t="n">
         <v>3.45</v>
@@ -11448,7 +11448,7 @@
         <v>1.01</v>
       </c>
       <c r="M57" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N57" t="n">
         <v>2.48</v>
@@ -11478,7 +11478,7 @@
         <v>1.41</v>
       </c>
       <c r="W57" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11636,7 @@
         <v>3.8</v>
       </c>
       <c r="K58" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
@@ -11648,19 +11648,19 @@
         <v>4.4</v>
       </c>
       <c r="O58" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P58" t="n">
         <v>2.16</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="R58" t="n">
         <v>1.46</v>
       </c>
       <c r="S58" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T58" t="n">
         <v>1.64</v>
@@ -11678,10 +11678,10 @@
         <v>18</v>
       </c>
       <c r="Y58" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z58" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA58" t="n">
         <v>46</v>
@@ -11708,7 +11708,7 @@
         <v>16</v>
       </c>
       <c r="AI58" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AJ58" t="n">
         <v>46</v>
@@ -11726,10 +11726,10 @@
         <v>23</v>
       </c>
       <c r="AO58" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP58" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ58" t="n">
         <v>11.5</v>
@@ -11762,29 +11762,29 @@
         <v>14</v>
       </c>
       <c r="BA58" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB58" t="n">
         <v>12</v>
       </c>
-      <c r="BB58" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BC58" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="BD58" t="n">
         <v>30</v>
       </c>
       <c r="BE58" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF58" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BG58" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -11815,16 +11815,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G59" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H59" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I59" t="n">
         <v>3.3</v>
-      </c>
-      <c r="I59" t="n">
-        <v>3.35</v>
       </c>
       <c r="J59" t="n">
         <v>3.15</v>
@@ -11839,25 +11839,25 @@
         <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O59" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P59" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R59" t="n">
         <v>1.24</v>
       </c>
       <c r="S59" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T59" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="U59" t="n">
         <v>1.93</v>
@@ -11866,10 +11866,10 @@
         <v>1.43</v>
       </c>
       <c r="W59" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="X59" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y59" t="n">
         <v>11</v>
@@ -11914,16 +11914,16 @@
         <v>60</v>
       </c>
       <c r="AM59" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN59" t="n">
         <v>36</v>
       </c>
       <c r="AO59" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP59" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ59" t="n">
         <v>9.4</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -12012,34 +12012,34 @@
         <v>1.7</v>
       </c>
       <c r="G60" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H60" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="I60" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K60" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="L60" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M60" t="n">
         <v>1.01</v>
       </c>
       <c r="N60" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O60" t="n">
         <v>1.37</v>
       </c>
       <c r="P60" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q60" t="n">
         <v>1.92</v>
@@ -12057,10 +12057,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W60" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -12206,16 +12206,16 @@
         <v>1.66</v>
       </c>
       <c r="G61" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H61" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I61" t="n">
         <v>7.2</v>
       </c>
       <c r="J61" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K61" t="n">
         <v>4</v>
@@ -12245,7 +12245,7 @@
         <v>4</v>
       </c>
       <c r="T61" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U61" t="n">
         <v>1.8</v>
@@ -12254,13 +12254,13 @@
         <v>1.16</v>
       </c>
       <c r="W61" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X61" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y61" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z61" t="n">
         <v>55</v>
@@ -12272,16 +12272,16 @@
         <v>7.4</v>
       </c>
       <c r="AC61" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD61" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE61" t="n">
         <v>140</v>
       </c>
       <c r="AF61" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AG61" t="n">
         <v>11</v>
@@ -12305,7 +12305,7 @@
         <v>200</v>
       </c>
       <c r="AN61" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AO61" t="n">
         <v>210</v>
@@ -12314,13 +12314,13 @@
         <v>10</v>
       </c>
       <c r="AQ61" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR61" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS61" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT61" t="n">
         <v>6.2</v>
@@ -12329,44 +12329,44 @@
         <v>7.4</v>
       </c>
       <c r="AV61" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW61" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="AX61" t="n">
         <v>8</v>
       </c>
       <c r="AY61" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ61" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA61" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="BB61" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC61" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BD61" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE61" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF61" t="n">
         <v>11</v>
       </c>
       <c r="BG61" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -12400,16 +12400,16 @@
         <v>2.72</v>
       </c>
       <c r="G62" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H62" t="n">
         <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="J62" t="n">
-        <v>2.6</v>
+        <v>2.92</v>
       </c>
       <c r="K62" t="n">
         <v>3.3</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="G64" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H64" t="n">
         <v>2.16</v>
       </c>
       <c r="I64" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J64" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K64" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L64" t="n">
         <v>1.34</v>
@@ -12809,40 +12809,40 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>2.92</v>
+        <v>1.71</v>
       </c>
       <c r="O64" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="P64" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R64" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S64" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T64" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U64" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="W64" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="X64" t="n">
         <v>17</v>
       </c>
       <c r="Y64" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z64" t="n">
         <v>19.5</v>
@@ -12851,7 +12851,7 @@
         <v>42</v>
       </c>
       <c r="AB64" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC64" t="n">
         <v>11</v>
@@ -12896,31 +12896,31 @@
         <v>7.6</v>
       </c>
       <c r="AQ64" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR64" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AS64" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT64" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU64" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV64" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AW64" t="n">
         <v>16.5</v>
       </c>
       <c r="AX64" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY64" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ64" t="n">
         <v>12</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -12982,19 +12982,19 @@
         <v>2.72</v>
       </c>
       <c r="G65" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="H65" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I65" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="J65" t="n">
         <v>3.5</v>
       </c>
       <c r="K65" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -13003,16 +13003,16 @@
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="O65" t="n">
         <v>1.29</v>
       </c>
       <c r="P65" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="R65" t="n">
         <v>1.28</v>
@@ -13027,10 +13027,10 @@
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W65" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -13173,7 +13173,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G66" t="n">
         <v>1.86</v>
@@ -13185,7 +13185,7 @@
         <v>6</v>
       </c>
       <c r="J66" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K66" t="n">
         <v>4.3</v>
@@ -13212,7 +13212,7 @@
         <v>1.26</v>
       </c>
       <c r="S66" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T66" t="n">
         <v>2.06</v>
@@ -13221,70 +13221,70 @@
         <v>1.79</v>
       </c>
       <c r="V66" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W66" t="n">
         <v>2.16</v>
       </c>
       <c r="X66" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y66" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z66" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA66" t="n">
         <v>1000</v>
       </c>
       <c r="AB66" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC66" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD66" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE66" t="n">
         <v>1000</v>
       </c>
       <c r="AF66" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG66" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH66" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI66" t="n">
         <v>1000</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK66" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL66" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM66" t="n">
         <v>1000</v>
       </c>
       <c r="AN66" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO66" t="n">
         <v>1000</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR66" t="n">
         <v>1.03</v>
@@ -13293,34 +13293,34 @@
         <v>1.03</v>
       </c>
       <c r="AT66" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AU66" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV66" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AW66" t="n">
         <v>1.03</v>
       </c>
       <c r="AX66" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY66" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BA66" t="n">
         <v>1.03</v>
       </c>
       <c r="BB66" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BC66" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BD66" t="n">
         <v>1.03</v>
@@ -13329,14 +13329,14 @@
         <v>1.03</v>
       </c>
       <c r="BF66" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG66" t="n">
-        <v>1.01</v>
+        <v>95</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
         <v>1.07</v>
       </c>
       <c r="N67" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O67" t="n">
         <v>1.37</v>
@@ -13421,7 +13421,7 @@
         <v>3.3</v>
       </c>
       <c r="X67" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y67" t="n">
         <v>30</v>
@@ -13436,7 +13436,7 @@
         <v>6.4</v>
       </c>
       <c r="AC67" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD67" t="n">
         <v>50</v>
@@ -13448,7 +13448,7 @@
         <v>7.2</v>
       </c>
       <c r="AG67" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH67" t="n">
         <v>42</v>
@@ -13457,10 +13457,10 @@
         <v>300</v>
       </c>
       <c r="AJ67" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AK67" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL67" t="n">
         <v>65</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -13561,170 +13561,170 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="G68" t="n">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="H68" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J68" t="n">
+        <v>3</v>
+      </c>
+      <c r="K68" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N68" t="n">
         <v>2.88</v>
       </c>
-      <c r="K68" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M68" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N68" t="n">
-        <v>1.53</v>
-      </c>
       <c r="O68" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P68" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="R68" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S68" t="n">
-        <v>2.06</v>
+        <v>4.2</v>
       </c>
       <c r="T68" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U68" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="V68" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W68" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="X68" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y68" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z68" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA68" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB68" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC68" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD68" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE68" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF68" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH68" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI68" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ68" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK68" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL68" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM68" t="n">
         <v>1000</v>
       </c>
       <c r="AN68" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO68" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AT68" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU68" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV68" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AX68" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY68" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AZ68" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BA68" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB68" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC68" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD68" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF68" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG68" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -14161,7 +14161,7 @@
         <v>4.4</v>
       </c>
       <c r="L71" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M71" t="n">
         <v>1.07</v>
@@ -14173,7 +14173,7 @@
         <v>1.37</v>
       </c>
       <c r="P71" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q71" t="n">
         <v>2.04</v>
@@ -14188,7 +14188,7 @@
         <v>1.97</v>
       </c>
       <c r="U71" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V71" t="n">
         <v>1.21</v>
@@ -14263,7 +14263,7 @@
         <v>1.03</v>
       </c>
       <c r="AT71" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU71" t="n">
         <v>7</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -14337,13 +14337,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G72" t="n">
         <v>1.98</v>
       </c>
       <c r="H72" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I72" t="n">
         <v>5</v>
@@ -14352,7 +14352,7 @@
         <v>3.55</v>
       </c>
       <c r="K72" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -14463,10 +14463,10 @@
         <v>7.4</v>
       </c>
       <c r="AV72" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW72" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX72" t="n">
         <v>10</v>
@@ -14490,7 +14490,7 @@
         <v>32</v>
       </c>
       <c r="BE72" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF72" t="n">
         <v>13</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -14537,16 +14537,16 @@
         <v>1.38</v>
       </c>
       <c r="H73" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="I73" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K73" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14564,7 +14564,7 @@
         <v>1.68</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R73" t="n">
         <v>1.25</v>
@@ -14582,16 +14582,16 @@
         <v>1.05</v>
       </c>
       <c r="W73" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="X73" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y73" t="n">
         <v>38</v>
       </c>
       <c r="Z73" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA73" t="n">
         <v>1000</v>
@@ -14609,7 +14609,7 @@
         <v>1000</v>
       </c>
       <c r="AF73" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AG73" t="n">
         <v>12.5</v>
@@ -14642,25 +14642,25 @@
         <v>10</v>
       </c>
       <c r="AQ73" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR73" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS73" t="n">
         <v>7.2</v>
       </c>
-      <c r="AS73" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AT73" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AU73" t="n">
         <v>11</v>
       </c>
       <c r="AV73" t="n">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="AW73" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX73" t="n">
         <v>5</v>
@@ -14669,32 +14669,32 @@
         <v>10</v>
       </c>
       <c r="AZ73" t="n">
-        <v>44</v>
+        <v>6.4</v>
       </c>
       <c r="BA73" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB73" t="n">
         <v>8.4</v>
       </c>
       <c r="BC73" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD73" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BE73" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF73" t="n">
         <v>7.4</v>
       </c>
       <c r="BG73" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-27 03:07:07</t>
+          <t>2026-03-27 05:19:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G2" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
         <v>1.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
@@ -805,16 +805,16 @@
         <v>1.95</v>
       </c>
       <c r="V2" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,13 +823,13 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
@@ -913,14 +913,14 @@
         <v>1.03</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="G3" t="n">
         <v>2.28</v>
       </c>
       <c r="H3" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="I3" t="n">
         <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L3" t="n">
         <v>1.46</v>
@@ -975,28 +975,28 @@
         <v>1.08</v>
       </c>
       <c r="N3" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="O3" t="n">
         <v>1.38</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R3" t="n">
         <v>1.28</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V3" t="n">
         <v>1.27</v>
@@ -1020,7 +1020,7 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>2.16</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>2.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>2.14</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>2.34</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="BF3" t="n">
-        <v>16</v>
+        <v>1.59</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>2.08</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1151,19 +1151,19 @@
         <v>3.55</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I4" t="n">
         <v>2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
         <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1175,10 +1175,10 @@
         <v>1.23</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.46</v>
@@ -1220,7 +1220,7 @@
         <v>13</v>
       </c>
       <c r="AE4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AF4" t="n">
         <v>29</v>
@@ -1229,7 +1229,7 @@
         <v>16.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
         <v>36</v>
@@ -1244,13 +1244,13 @@
         <v>46</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP4" t="n">
         <v>15</v>
@@ -1259,10 +1259,10 @@
         <v>9.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
@@ -1277,7 +1277,7 @@
         <v>16.5</v>
       </c>
       <c r="AX4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
@@ -1289,26 +1289,26 @@
         <v>20</v>
       </c>
       <c r="BB4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF4" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>2.66</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H5" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I5" t="n">
         <v>2.96</v>
       </c>
       <c r="J5" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1372,7 +1372,7 @@
         <v>1.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.35</v>
@@ -1387,10 +1387,10 @@
         <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X5" t="n">
         <v>970</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
         <v>4.5</v>
@@ -1560,34 +1560,34 @@
         <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
         <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
         <v>2.82</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
         <v>20</v>
@@ -1605,7 +1605,7 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
         <v>55</v>
@@ -1623,7 +1623,7 @@
         <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>23</v>
@@ -1647,10 +1647,10 @@
         <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -1662,7 +1662,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
@@ -1674,7 +1674,7 @@
         <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BB6" t="n">
         <v>19.5</v>
@@ -1683,20 +1683,20 @@
         <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
         <v>9</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1733,13 +1733,13 @@
         <v>3.35</v>
       </c>
       <c r="H7" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="I7" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
@@ -1748,7 +1748,7 @@
         <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
         <v>3.05</v>
@@ -1757,10 +1757,10 @@
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
@@ -1769,16 +1769,16 @@
         <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
         <v>1.96</v>
       </c>
       <c r="V7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W7" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>12.5</v>
@@ -1820,7 +1820,7 @@
         <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
         <v>55</v>
@@ -1841,13 +1841,13 @@
         <v>8.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS7" t="n">
         <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
@@ -1871,10 +1871,10 @@
         <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BD7" t="n">
         <v>42</v>
@@ -1883,14 +1883,14 @@
         <v>7.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG7" t="n">
         <v>6.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.28</v>
       </c>
       <c r="G8" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="H8" t="n">
         <v>12.5</v>
@@ -1951,10 +1951,10 @@
         <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R8" t="n">
         <v>1.47</v>
@@ -2047,7 +2047,7 @@
         <v>10</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="AW8" t="n">
         <v>1.03</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G9" t="n">
         <v>2.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
         <v>3.6</v>
@@ -2133,13 +2133,13 @@
         <v>3.45</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
@@ -2157,7 +2157,7 @@
         <v>3.9</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
@@ -2169,22 +2169,22 @@
         <v>1.71</v>
       </c>
       <c r="X9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
         <v>70</v>
       </c>
       <c r="AB9" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
         <v>14.5</v>
@@ -2193,22 +2193,22 @@
         <v>44</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL9" t="n">
         <v>42</v>
@@ -2217,34 +2217,34 @@
         <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP9" t="n">
         <v>11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR9" t="n">
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW9" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AX9" t="n">
         <v>13</v>
@@ -2253,32 +2253,32 @@
         <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>36</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.6</v>
+        <v>19.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="M10" t="n">
         <v>1.12</v>
@@ -2339,10 +2339,10 @@
         <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
@@ -2360,7 +2360,7 @@
         <v>2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X10" t="n">
         <v>9.199999999999999</v>
@@ -2423,7 +2423,7 @@
         <v>5</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
         <v>16.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H11" t="n">
         <v>3.95</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -2533,16 +2533,16 @@
         <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
         <v>1.9</v>
@@ -2554,7 +2554,7 @@
         <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X11" t="n">
         <v>13.5</v>
@@ -2614,10 +2614,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>1.03</v>
@@ -2629,28 +2629,28 @@
         <v>5.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
         <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
         <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BD11" t="n">
         <v>1.03</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J12" t="n">
         <v>2.92</v>
@@ -2715,7 +2715,7 @@
         <v>3.35</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -2745,7 +2745,7 @@
         <v>1.8</v>
       </c>
       <c r="V12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
         <v>1.6</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
         <v>3.45</v>
@@ -2900,16 +2900,16 @@
         <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K13" t="n">
         <v>3.95</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
@@ -2924,13 +2924,13 @@
         <v>1.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
         <v>2.08</v>
@@ -3100,10 +3100,10 @@
         <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3118,10 +3118,10 @@
         <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S14" t="n">
         <v>3.45</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H15" t="n">
         <v>2.06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>3.95</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3309,7 +3309,7 @@
         <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q15" t="n">
         <v>1.89</v>
@@ -3318,7 +3318,7 @@
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T15" t="n">
         <v>1.71</v>
@@ -3327,10 +3327,10 @@
         <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3414,7 +3414,7 @@
         <v>4.3</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="AZ15" t="n">
         <v>4.1</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
         <v>3.6</v>
@@ -3685,7 +3685,7 @@
         <v>3.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3694,7 +3694,7 @@
         <v>3.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
         <v>1.96</v>
@@ -3778,22 +3778,22 @@
         <v>11.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR17" t="n">
         <v>12</v>
       </c>
       <c r="AS17" t="n">
-        <v>23</v>
+        <v>4.5</v>
       </c>
       <c r="AT17" t="n">
         <v>10</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
         <v>18.5</v>
@@ -3802,25 +3802,25 @@
         <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
         <v>4.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>28</v>
+        <v>4.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>34</v>
+        <v>4.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
         <v>4.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="n">
         <v>3.6</v>
@@ -3879,16 +3879,16 @@
         <v>4.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>2.06</v>
+        <v>3.85</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P18" t="n">
         <v>1.98</v>
@@ -3897,22 +3897,22 @@
         <v>1.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
         <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>2.78</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4058,49 +4058,49 @@
         <v>2.4</v>
       </c>
       <c r="G19" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J19" t="n">
         <v>2.98</v>
       </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J19" t="n">
-        <v>2.92</v>
-      </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M19" t="n">
         <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
         <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V19" t="n">
         <v>1.36</v>
@@ -4112,7 +4112,7 @@
         <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
         <v>26</v>
@@ -4121,10 +4121,10 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD19" t="n">
         <v>16.5</v>
@@ -4169,10 +4169,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AT19" t="n">
         <v>7.8</v>
@@ -4184,41 +4184,41 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19" t="n">
         <v>12.5</v>
       </c>
       <c r="BA19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE19" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BG19" t="n">
         <v>3.85</v>
       </c>
-      <c r="BG19" t="n">
-        <v>4</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>1.76</v>
       </c>
       <c r="G20" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H20" t="n">
         <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.21</v>
@@ -4279,7 +4279,7 @@
         <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="Q20" t="n">
         <v>1.43</v>
@@ -4366,7 +4366,7 @@
         <v>4.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="AT20" t="n">
         <v>4</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G21" t="n">
         <v>6.4</v>
@@ -4452,13 +4452,13 @@
         <v>1.82</v>
       </c>
       <c r="I21" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.39</v>
@@ -4467,7 +4467,7 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
         <v>1.42</v>
@@ -4491,7 +4491,7 @@
         <v>1.79</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W21" t="n">
         <v>1.2</v>
@@ -4551,7 +4551,7 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AQ21" t="n">
         <v>5.7</v>
@@ -4560,7 +4560,7 @@
         <v>3.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="AT21" t="n">
         <v>4</v>
@@ -4584,7 +4584,7 @@
         <v>3.15</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BB21" t="n">
         <v>3</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G22" t="n">
         <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
         <v>1000</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="H23" t="n">
         <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
         <v>3.55</v>
@@ -4855,22 +4855,22 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O23" t="n">
         <v>1.01</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
         <v>1.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="G24" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I24" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5052,7 +5052,7 @@
         <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
         <v>1.71</v>
@@ -5067,58 +5067,58 @@
         <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG24" t="n">
         <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI24" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL24" t="n">
         <v>55</v>
@@ -5127,22 +5127,22 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR24" t="n">
         <v>4.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
         <v>6</v>
@@ -5151,13 +5151,13 @@
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
         <v>8.199999999999999</v>
@@ -5166,29 +5166,29 @@
         <v>16</v>
       </c>
       <c r="BA24" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD24" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5222,13 +5222,13 @@
         <v>2.68</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H25" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="I25" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="J25" t="n">
         <v>3.3</v>
@@ -5237,7 +5237,7 @@
         <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="M25" t="n">
         <v>1.06</v>
@@ -5246,7 +5246,7 @@
         <v>3.75</v>
       </c>
       <c r="O25" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P25" t="n">
         <v>1.94</v>
@@ -5258,19 +5258,19 @@
         <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T25" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V25" t="n">
         <v>1.52</v>
       </c>
       <c r="W25" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X25" t="n">
         <v>18</v>
@@ -5330,7 +5330,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR25" t="n">
         <v>14</v>
@@ -5342,13 +5342,13 @@
         <v>9.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>22</v>
+        <v>4.5</v>
       </c>
       <c r="AX25" t="n">
         <v>15</v>
@@ -5369,7 +5369,7 @@
         <v>4.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="BE25" t="n">
         <v>4.9</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G26" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="I26" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K26" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
@@ -5461,7 +5461,7 @@
         <v>2.38</v>
       </c>
       <c r="V26" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W26" t="n">
         <v>1.61</v>
@@ -5515,7 +5515,7 @@
         <v>70</v>
       </c>
       <c r="AN26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
@@ -5530,7 +5530,7 @@
         <v>15.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
         <v>11</v>
@@ -5563,7 +5563,7 @@
         <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="BE26" t="n">
         <v>8.4</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>3.15</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
         <v>4.1</v>
@@ -5646,7 +5646,7 @@
         <v>1.43</v>
       </c>
       <c r="S27" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T27" t="n">
         <v>1.61</v>
@@ -5679,7 +5679,7 @@
         <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
@@ -5718,7 +5718,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR27" t="n">
         <v>1.03</v>
@@ -5727,7 +5727,7 @@
         <v>1.03</v>
       </c>
       <c r="AT27" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU27" t="n">
         <v>6.8</v>
@@ -5742,7 +5742,7 @@
         <v>1.03</v>
       </c>
       <c r="AY27" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ27" t="n">
         <v>1.03</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G28" t="n">
         <v>2.74</v>
@@ -5813,7 +5813,7 @@
         <v>3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>4.4</v>
@@ -5837,7 +5837,7 @@
         <v>1.59</v>
       </c>
       <c r="R28" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S28" t="n">
         <v>2.46</v>
@@ -5909,7 +5909,7 @@
         <v>21</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AQ28" t="n">
         <v>11.5</v>
@@ -5918,7 +5918,7 @@
         <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="AT28" t="n">
         <v>11</v>
@@ -5954,17 +5954,17 @@
         <v>22</v>
       </c>
       <c r="BE28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG28" t="n">
         <v>12.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="H29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I29" t="n">
         <v>3.8</v>
@@ -6025,10 +6025,10 @@
         <v>1.23</v>
       </c>
       <c r="P29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R29" t="n">
         <v>1.48</v>
@@ -6046,7 +6046,7 @@
         <v>1.37</v>
       </c>
       <c r="W29" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6103,62 +6103,62 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AR29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.39</v>
       </c>
-      <c r="AS29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BF29" t="n">
-        <v>1.75</v>
+        <v>2.68</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.1</v>
       </c>
       <c r="G30" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H30" t="n">
         <v>3.1</v>
@@ -6210,10 +6210,10 @@
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="O30" t="n">
         <v>1.22</v>
@@ -6225,10 +6225,10 @@
         <v>1.68</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
         <v>1.47</v>
@@ -6237,13 +6237,13 @@
         <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W30" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="X30" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
         <v>1000</v>
@@ -6297,16 +6297,16 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AQ30" t="n">
         <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
@@ -6318,7 +6318,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="AX30" t="n">
         <v>10</v>
@@ -6330,29 +6330,29 @@
         <v>10</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BB30" t="n">
         <v>6.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.22</v>
+        <v>1.99</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M31" t="n">
         <v>1.06</v>
@@ -6413,13 +6413,13 @@
         <v>1.3</v>
       </c>
       <c r="P31" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="R31" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S31" t="n">
         <v>3.25</v>
@@ -6428,7 +6428,7 @@
         <v>1.79</v>
       </c>
       <c r="U31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V31" t="n">
         <v>1.26</v>
@@ -6437,7 +6437,7 @@
         <v>2.04</v>
       </c>
       <c r="X31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y31" t="n">
         <v>17</v>
@@ -6449,10 +6449,10 @@
         <v>120</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
         <v>18.5</v>
@@ -6461,31 +6461,31 @@
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG31" t="n">
         <v>12</v>
       </c>
-      <c r="AG31" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH31" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ31" t="n">
         <v>22</v>
       </c>
       <c r="AK31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM31" t="n">
         <v>120</v>
       </c>
       <c r="AN31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO31" t="n">
         <v>75</v>
@@ -6494,7 +6494,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR31" t="n">
         <v>1.03</v>
@@ -6503,10 +6503,10 @@
         <v>1.03</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV31" t="n">
         <v>13</v>
@@ -6515,16 +6515,16 @@
         <v>1.03</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ31" t="n">
         <v>13.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="BB31" t="n">
         <v>15.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6577,25 +6577,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G32" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="H32" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I32" t="n">
         <v>4.1</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
         <v>1.05</v>
@@ -6610,10 +6610,10 @@
         <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R32" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
         <v>2.58</v>
@@ -6622,13 +6622,13 @@
         <v>1.64</v>
       </c>
       <c r="U32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V32" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W32" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.6</v>
+        <v>4</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AW32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX32" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>11</v>
       </c>
       <c r="AY32" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="BB32" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="BF32" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -6774,40 +6774,40 @@
         <v>4.2</v>
       </c>
       <c r="G33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I33" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J33" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K33" t="n">
         <v>4.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O33" t="n">
         <v>1.27</v>
       </c>
       <c r="P33" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
         <v>2.96</v>
@@ -6819,7 +6819,7 @@
         <v>2.18</v>
       </c>
       <c r="V33" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="W33" t="n">
         <v>1.25</v>
@@ -6915,13 +6915,13 @@
         <v>6.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD33" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BE33" t="n">
         <v>3.1</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7001,7 +7001,7 @@
         <v>1.64</v>
       </c>
       <c r="R34" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S34" t="n">
         <v>2.36</v>
@@ -7022,7 +7022,7 @@
         <v>22</v>
       </c>
       <c r="Y34" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z34" t="n">
         <v>25</v>
@@ -7031,13 +7031,13 @@
         <v>55</v>
       </c>
       <c r="AB34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC34" t="n">
         <v>10.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE34" t="n">
         <v>36</v>
@@ -7055,13 +7055,13 @@
         <v>46</v>
       </c>
       <c r="AJ34" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL34" t="n">
         <v>44</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>42</v>
       </c>
       <c r="AM34" t="n">
         <v>90</v>
@@ -7073,62 +7073,62 @@
         <v>27</v>
       </c>
       <c r="AP34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AY34" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AS34" t="n">
+      <c r="AZ34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG34" t="n">
         <v>4</v>
       </c>
-      <c r="AT34" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7171,13 +7171,13 @@
         <v>1.82</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>4.7</v>
       </c>
       <c r="L35" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="M35" t="n">
         <v>1.04</v>
@@ -7189,7 +7189,7 @@
         <v>1.22</v>
       </c>
       <c r="P35" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q35" t="n">
         <v>1.66</v>
@@ -7216,37 +7216,37 @@
         <v>25</v>
       </c>
       <c r="Y35" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA35" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AB35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AC35" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH35" t="n">
         <v>21</v>
       </c>
-      <c r="AF35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>22</v>
-      </c>
       <c r="AI35" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ35" t="n">
         <v>140</v>
@@ -7261,10 +7261,10 @@
         <v>100</v>
       </c>
       <c r="AN35" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP35" t="n">
         <v>15</v>
@@ -7273,7 +7273,7 @@
         <v>9</v>
       </c>
       <c r="AR35" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AS35" t="n">
         <v>13</v>
@@ -7291,7 +7291,7 @@
         <v>12.5</v>
       </c>
       <c r="AX35" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="AY35" t="n">
         <v>14.5</v>
@@ -7303,26 +7303,26 @@
         <v>21</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BC35" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF35" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BG35" t="n">
         <v>6.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G36" t="n">
         <v>2.12</v>
@@ -7371,7 +7371,7 @@
         <v>4.3</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M36" t="n">
         <v>1.05</v>
@@ -7392,7 +7392,7 @@
         <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T36" t="n">
         <v>1.64</v>
@@ -7416,7 +7416,7 @@
         <v>32</v>
       </c>
       <c r="AA36" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB36" t="n">
         <v>12.5</v>
@@ -7428,7 +7428,7 @@
         <v>16.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF36" t="n">
         <v>15</v>
@@ -7452,7 +7452,7 @@
         <v>32</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN36" t="n">
         <v>11.5</v>
@@ -7467,7 +7467,7 @@
         <v>14.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS36" t="n">
         <v>7.6</v>
@@ -7503,7 +7503,7 @@
         <v>16.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE36" t="n">
         <v>7.6</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
         <v>3.9</v>
       </c>
       <c r="L37" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M37" t="n">
         <v>1.04</v>
@@ -7610,7 +7610,7 @@
         <v>28</v>
       </c>
       <c r="AA37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
         <v>13.5</v>
@@ -7643,10 +7643,10 @@
         <v>22</v>
       </c>
       <c r="AL37" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM37" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
         <v>15</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7744,19 +7744,19 @@
         <v>5.7</v>
       </c>
       <c r="G38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I38" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="J38" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K38" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G39" t="n">
         <v>5.6</v>
@@ -7971,7 +7971,7 @@
         <v>1.62</v>
       </c>
       <c r="R39" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S39" t="n">
         <v>2.52</v>
@@ -7998,16 +7998,16 @@
         <v>13</v>
       </c>
       <c r="AA39" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AB39" t="n">
         <v>25</v>
       </c>
       <c r="AC39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE39" t="n">
         <v>17</v>
@@ -8076,29 +8076,29 @@
         <v>14.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BB39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC39" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC39" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD39" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BE39" t="n">
-        <v>50</v>
+        <v>8.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>40</v>
+        <v>8.4</v>
       </c>
       <c r="BG39" t="n">
         <v>6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
         <v>9.4</v>
       </c>
       <c r="I40" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J40" t="n">
         <v>5.6</v>
@@ -8147,7 +8147,7 @@
         <v>6.8</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M40" t="n">
         <v>1.02</v>
@@ -8168,7 +8168,7 @@
         <v>1.69</v>
       </c>
       <c r="S40" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T40" t="n">
         <v>1.8</v>
@@ -8186,7 +8186,7 @@
         <v>32</v>
       </c>
       <c r="Y40" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="Z40" t="n">
         <v>110</v>
@@ -8231,22 +8231,22 @@
         <v>120</v>
       </c>
       <c r="AN40" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AO40" t="n">
         <v>140</v>
       </c>
       <c r="AP40" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ40" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS40" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT40" t="n">
         <v>9.4</v>
@@ -8255,25 +8255,25 @@
         <v>10.5</v>
       </c>
       <c r="AV40" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW40" t="n">
         <v>6.4</v>
       </c>
       <c r="AX40" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AY40" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AZ40" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB40" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC40" t="n">
         <v>9.800000000000001</v>
@@ -8282,17 +8282,17 @@
         <v>20</v>
       </c>
       <c r="BE40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF40" t="n">
         <v>4</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
         <v>1.51</v>
       </c>
       <c r="W41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X41" t="n">
         <v>36</v>
@@ -8398,7 +8398,7 @@
         <v>970</v>
       </c>
       <c r="AE41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF41" t="n">
         <v>22</v>
@@ -8410,13 +8410,13 @@
         <v>970</v>
       </c>
       <c r="AI41" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ41" t="n">
         <v>36</v>
       </c>
       <c r="AK41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL41" t="n">
         <v>27</v>
@@ -8443,7 +8443,7 @@
         <v>1.01</v>
       </c>
       <c r="AT41" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU41" t="n">
         <v>1.03</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -8526,43 +8526,43 @@
         <v>2.46</v>
       </c>
       <c r="I42" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J42" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K42" t="n">
         <v>3.85</v>
       </c>
       <c r="L42" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="M42" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N42" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O42" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="P42" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="R42" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S42" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="T42" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="U42" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="V42" t="n">
         <v>1.6</v>
@@ -8571,10 +8571,10 @@
         <v>1.5</v>
       </c>
       <c r="X42" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Y42" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z42" t="n">
         <v>970</v>
@@ -8583,10 +8583,10 @@
         <v>38</v>
       </c>
       <c r="AB42" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="AD42" t="n">
         <v>970</v>
@@ -8595,7 +8595,7 @@
         <v>27</v>
       </c>
       <c r="AF42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG42" t="n">
         <v>970</v>
@@ -8604,13 +8604,13 @@
         <v>970</v>
       </c>
       <c r="AI42" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ42" t="n">
         <v>55</v>
       </c>
       <c r="AK42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL42" t="n">
         <v>40</v>
@@ -8619,68 +8619,68 @@
         <v>90</v>
       </c>
       <c r="AN42" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AO42" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AP42" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="AQ42" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AR42" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="AS42" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT42" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AU42" t="n">
         <v>6.4</v>
       </c>
       <c r="AV42" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="AW42" t="n">
         <v>19</v>
       </c>
       <c r="AX42" t="n">
-        <v>15</v>
+        <v>5.6</v>
       </c>
       <c r="AY42" t="n">
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ42" t="n">
         <v>11.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB42" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC42" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BD42" t="n">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BE42" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG42" t="n">
         <v>5.4</v>
       </c>
-      <c r="BF42" t="n">
-        <v>17</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>14</v>
-      </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G43" t="n">
         <v>3.2</v>
@@ -8723,34 +8723,34 @@
         <v>4.2</v>
       </c>
       <c r="J43" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K43" t="n">
         <v>5.9</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M43" t="n">
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="O43" t="n">
         <v>1.38</v>
       </c>
       <c r="P43" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R43" t="n">
         <v>1.08</v>
       </c>
       <c r="S43" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T43" t="n">
         <v>1.01</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -8905,43 +8905,43 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="G44" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H44" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I44" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K44" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L44" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
         <v>1.11</v>
       </c>
       <c r="N44" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O44" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q44" t="n">
         <v>2.42</v>
       </c>
       <c r="R44" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S44" t="n">
         <v>4.9</v>
@@ -8953,16 +8953,16 @@
         <v>1.76</v>
       </c>
       <c r="V44" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X44" t="n">
         <v>10.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z44" t="n">
         <v>42</v>
@@ -8971,19 +8971,19 @@
         <v>180</v>
       </c>
       <c r="AB44" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC44" t="n">
         <v>8</v>
       </c>
       <c r="AD44" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE44" t="n">
         <v>110</v>
       </c>
       <c r="AF44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG44" t="n">
         <v>11.5</v>
@@ -8995,7 +8995,7 @@
         <v>120</v>
       </c>
       <c r="AJ44" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK44" t="n">
         <v>26</v>
@@ -9007,7 +9007,7 @@
         <v>220</v>
       </c>
       <c r="AN44" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
@@ -9016,25 +9016,25 @@
         <v>9</v>
       </c>
       <c r="AQ44" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT44" t="n">
         <v>6</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV44" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AW44" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX44" t="n">
         <v>9</v>
@@ -9055,20 +9055,20 @@
         <v>20</v>
       </c>
       <c r="BD44" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="BE44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF44" t="n">
         <v>16.5</v>
       </c>
       <c r="BG44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -9099,13 +9099,13 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G45" t="n">
         <v>2.36</v>
       </c>
       <c r="H45" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I45" t="n">
         <v>3.9</v>
@@ -9117,7 +9117,7 @@
         <v>3.3</v>
       </c>
       <c r="L45" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M45" t="n">
         <v>1.12</v>
@@ -9126,22 +9126,22 @@
         <v>2.68</v>
       </c>
       <c r="O45" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P45" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q45" t="n">
         <v>2.58</v>
       </c>
       <c r="R45" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S45" t="n">
         <v>5.3</v>
       </c>
       <c r="T45" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U45" t="n">
         <v>1.8</v>
@@ -9150,7 +9150,7 @@
         <v>1.34</v>
       </c>
       <c r="W45" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X45" t="n">
         <v>8.6</v>
@@ -9168,7 +9168,7 @@
         <v>7.4</v>
       </c>
       <c r="AC45" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD45" t="n">
         <v>16.5</v>
@@ -9207,7 +9207,7 @@
         <v>90</v>
       </c>
       <c r="AP45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ45" t="n">
         <v>9.4</v>
@@ -9216,10 +9216,10 @@
         <v>22</v>
       </c>
       <c r="AS45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT45" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU45" t="n">
         <v>6.8</v>
@@ -9228,7 +9228,7 @@
         <v>15</v>
       </c>
       <c r="AW45" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX45" t="n">
         <v>11.5</v>
@@ -9240,29 +9240,29 @@
         <v>21</v>
       </c>
       <c r="BA45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB45" t="n">
         <v>28</v>
       </c>
       <c r="BC45" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD45" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BE45" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BF45" t="n">
         <v>26</v>
       </c>
       <c r="BG45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -9293,25 +9293,25 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="G46" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H46" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="I46" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J46" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K46" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M46" t="n">
         <v>1.11</v>
@@ -9341,10 +9341,10 @@
         <v>1.7</v>
       </c>
       <c r="V46" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="W46" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="X46" t="n">
         <v>9.6</v>
@@ -9356,10 +9356,10 @@
         <v>20</v>
       </c>
       <c r="AA46" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB46" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC46" t="n">
         <v>8.6</v>
@@ -9371,10 +9371,10 @@
         <v>50</v>
       </c>
       <c r="AF46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG46" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH46" t="n">
         <v>23</v>
@@ -9386,7 +9386,7 @@
         <v>55</v>
       </c>
       <c r="AK46" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL46" t="n">
         <v>70</v>
@@ -9404,7 +9404,7 @@
         <v>1.03</v>
       </c>
       <c r="AQ46" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR46" t="n">
         <v>1.03</v>
@@ -9413,13 +9413,13 @@
         <v>1.03</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU46" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW46" t="n">
         <v>1.03</v>
@@ -9449,14 +9449,14 @@
         <v>1.03</v>
       </c>
       <c r="BF46" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BG46" t="n">
         <v>40</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9499,7 @@
         <v>3.15</v>
       </c>
       <c r="J47" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K47" t="n">
         <v>3.45</v>
@@ -9535,7 +9535,7 @@
         <v>1.87</v>
       </c>
       <c r="V47" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="W47" t="n">
         <v>1.39</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -9681,7 +9681,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="G48" t="n">
         <v>2.74</v>
@@ -9699,7 +9699,7 @@
         <v>3.25</v>
       </c>
       <c r="L48" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M48" t="n">
         <v>1.12</v>
@@ -9708,13 +9708,13 @@
         <v>2.62</v>
       </c>
       <c r="O48" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P48" t="n">
         <v>1.54</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R48" t="n">
         <v>1.19</v>
@@ -9741,10 +9741,10 @@
         <v>10.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AA48" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB48" t="n">
         <v>8.4</v>
@@ -9768,7 +9768,7 @@
         <v>23</v>
       </c>
       <c r="AI48" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AJ48" t="n">
         <v>50</v>
@@ -9777,13 +9777,13 @@
         <v>40</v>
       </c>
       <c r="AL48" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM48" t="n">
         <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AO48" t="n">
         <v>85</v>
@@ -9810,7 +9810,7 @@
         <v>13</v>
       </c>
       <c r="AW48" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AX48" t="n">
         <v>13</v>
@@ -9822,29 +9822,29 @@
         <v>18</v>
       </c>
       <c r="BA48" t="n">
-        <v>55</v>
+        <v>6.4</v>
       </c>
       <c r="BB48" t="n">
-        <v>34</v>
+        <v>6.2</v>
       </c>
       <c r="BC48" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="BD48" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE48" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF48" t="n">
         <v>6</v>
       </c>
       <c r="BG48" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -9887,13 +9887,13 @@
         <v>4.2</v>
       </c>
       <c r="J49" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K49" t="n">
         <v>3.75</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M49" t="n">
         <v>1.08</v>
@@ -9905,7 +9905,7 @@
         <v>1.35</v>
       </c>
       <c r="P49" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Q49" t="n">
         <v>2.02</v>
@@ -9914,7 +9914,7 @@
         <v>1.32</v>
       </c>
       <c r="S49" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T49" t="n">
         <v>1.81</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -10069,25 +10069,25 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G50" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H50" t="n">
         <v>4.1</v>
       </c>
       <c r="I50" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J50" t="n">
         <v>2.92</v>
       </c>
       <c r="K50" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L50" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M50" t="n">
         <v>1.01</v>
@@ -10096,13 +10096,13 @@
         <v>1.51</v>
       </c>
       <c r="O50" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P50" t="n">
         <v>1.51</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R50" t="n">
         <v>1.18</v>
@@ -10120,7 +10120,7 @@
         <v>1.16</v>
       </c>
       <c r="W50" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -10263,79 +10263,79 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G51" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H51" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I51" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J51" t="n">
         <v>3.5</v>
       </c>
       <c r="K51" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L51" t="n">
         <v>1.44</v>
       </c>
       <c r="M51" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N51" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O51" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P51" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R51" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T51" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U51" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V51" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W51" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X51" t="n">
         <v>12</v>
       </c>
       <c r="Y51" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z51" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA51" t="n">
         <v>85</v>
       </c>
       <c r="AB51" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC51" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD51" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE51" t="n">
         <v>55</v>
@@ -10347,16 +10347,16 @@
         <v>11</v>
       </c>
       <c r="AH51" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI51" t="n">
         <v>65</v>
       </c>
       <c r="AJ51" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK51" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL51" t="n">
         <v>44</v>
@@ -10380,53 +10380,53 @@
         <v>24</v>
       </c>
       <c r="AS51" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT51" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU51" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW51" t="n">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="AX51" t="n">
         <v>11.5</v>
       </c>
       <c r="AY51" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ51" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA51" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD51" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BE51" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BF51" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG51" t="n">
         <v>50</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
         <v>2.76</v>
       </c>
       <c r="I52" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J52" t="n">
         <v>4.1</v>
@@ -10475,7 +10475,7 @@
         <v>4.8</v>
       </c>
       <c r="L52" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M52" t="n">
         <v>1.02</v>
@@ -10496,7 +10496,7 @@
         <v>1.92</v>
       </c>
       <c r="S52" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="T52" t="n">
         <v>1.39</v>
@@ -10514,7 +10514,7 @@
         <v>48</v>
       </c>
       <c r="Y52" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z52" t="n">
         <v>34</v>
@@ -10523,22 +10523,22 @@
         <v>1000</v>
       </c>
       <c r="AB52" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AC52" t="n">
         <v>970</v>
       </c>
       <c r="AD52" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AE52" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AF52" t="n">
         <v>27</v>
       </c>
       <c r="AG52" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AH52" t="n">
         <v>970</v>
@@ -10547,13 +10547,13 @@
         <v>32</v>
       </c>
       <c r="AJ52" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK52" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL52" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AM52" t="n">
         <v>46</v>
@@ -10565,16 +10565,16 @@
         <v>14</v>
       </c>
       <c r="AP52" t="n">
-        <v>5.9</v>
+        <v>4.9</v>
       </c>
       <c r="AQ52" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="AR52" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AT52" t="n">
         <v>16.5</v>
@@ -10586,41 +10586,41 @@
         <v>11</v>
       </c>
       <c r="AW52" t="n">
-        <v>5.3</v>
+        <v>19.5</v>
       </c>
       <c r="AX52" t="n">
-        <v>5.3</v>
+        <v>17.5</v>
       </c>
       <c r="AY52" t="n">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AZ52" t="n">
         <v>10.5</v>
       </c>
       <c r="BA52" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB52" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC52" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD52" t="n">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE52" t="n">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF52" t="n">
-        <v>3.95</v>
+        <v>6.6</v>
       </c>
       <c r="BG52" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -10681,7 +10681,7 @@
         <v>1.59</v>
       </c>
       <c r="P53" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="Q53" t="n">
         <v>2.74</v>
@@ -10696,7 +10696,7 @@
         <v>2.12</v>
       </c>
       <c r="U53" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V53" t="n">
         <v>1.38</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -10845,10 +10845,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G54" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H54" t="n">
         <v>3.75</v>
@@ -10857,7 +10857,7 @@
         <v>4.5</v>
       </c>
       <c r="J54" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K54" t="n">
         <v>3.35</v>
@@ -10872,13 +10872,13 @@
         <v>1.48</v>
       </c>
       <c r="O54" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P54" t="n">
         <v>1.48</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R54" t="n">
         <v>1.13</v>
@@ -10896,7 +10896,7 @@
         <v>1.28</v>
       </c>
       <c r="W54" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X54" t="n">
         <v>1000</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -11039,46 +11039,46 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G55" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H55" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I55" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J55" t="n">
         <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="L55" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M55" t="n">
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="O55" t="n">
         <v>1.28</v>
       </c>
       <c r="P55" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R55" t="n">
         <v>1.21</v>
       </c>
       <c r="S55" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -11087,7 +11087,7 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W55" t="n">
         <v>1.4</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -11236,16 +11236,16 @@
         <v>1.84</v>
       </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H56" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I56" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J56" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K56" t="n">
         <v>4.1</v>
@@ -11263,7 +11263,7 @@
         <v>1.32</v>
       </c>
       <c r="P56" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q56" t="n">
         <v>1.92</v>
@@ -11281,10 +11281,10 @@
         <v>2.02</v>
       </c>
       <c r="V56" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W56" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X56" t="n">
         <v>18</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -11430,13 +11430,13 @@
         <v>2.16</v>
       </c>
       <c r="G57" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H57" t="n">
         <v>3.2</v>
       </c>
       <c r="I57" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J57" t="n">
         <v>3.9</v>
@@ -11451,10 +11451,10 @@
         <v>1.03</v>
       </c>
       <c r="N57" t="n">
-        <v>2.48</v>
+        <v>5.3</v>
       </c>
       <c r="O57" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P57" t="n">
         <v>2.48</v>
@@ -11463,134 +11463,134 @@
         <v>1.58</v>
       </c>
       <c r="R57" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="S57" t="n">
-        <v>1.58</v>
+        <v>2.26</v>
       </c>
       <c r="T57" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U57" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="V57" t="n">
         <v>1.41</v>
       </c>
       <c r="W57" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X57" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y57" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z57" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA57" t="n">
         <v>1000</v>
       </c>
       <c r="AB57" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC57" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD57" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE57" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF57" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG57" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH57" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI57" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK57" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL57" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM57" t="n">
         <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO57" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT57" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU57" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV57" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA57" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BC57" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD57" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -11621,25 +11621,25 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="G58" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H58" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I58" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K58" t="n">
         <v>3.8</v>
       </c>
-      <c r="K58" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L58" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M58" t="n">
         <v>1.05</v>
@@ -11657,22 +11657,22 @@
         <v>1.8</v>
       </c>
       <c r="R58" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S58" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T58" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U58" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V58" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W58" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X58" t="n">
         <v>18</v>
@@ -11684,10 +11684,10 @@
         <v>18</v>
       </c>
       <c r="AA58" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AB58" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC58" t="n">
         <v>8.6</v>
@@ -11711,7 +11711,7 @@
         <v>36</v>
       </c>
       <c r="AJ58" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK58" t="n">
         <v>30</v>
@@ -11723,10 +11723,10 @@
         <v>75</v>
       </c>
       <c r="AN58" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO58" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP58" t="n">
         <v>8.6</v>
@@ -11774,17 +11774,17 @@
         <v>30</v>
       </c>
       <c r="BE58" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF58" t="n">
         <v>19.5</v>
       </c>
       <c r="BG58" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -11836,31 +11836,31 @@
         <v>1.01</v>
       </c>
       <c r="M59" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N59" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O59" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P59" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q59" t="n">
         <v>2.38</v>
       </c>
       <c r="R59" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S59" t="n">
         <v>4.5</v>
       </c>
       <c r="T59" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U59" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V59" t="n">
         <v>1.43</v>
@@ -11872,7 +11872,7 @@
         <v>10</v>
       </c>
       <c r="Y59" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z59" t="n">
         <v>21</v>
@@ -11881,7 +11881,7 @@
         <v>60</v>
       </c>
       <c r="AB59" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC59" t="n">
         <v>7.2</v>
@@ -11932,13 +11932,13 @@
         <v>17.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT59" t="n">
         <v>8</v>
       </c>
       <c r="AU59" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV59" t="n">
         <v>12.5</v>
@@ -11956,29 +11956,29 @@
         <v>16.5</v>
       </c>
       <c r="BA59" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB59" t="n">
         <v>34</v>
       </c>
       <c r="BC59" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD59" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE59" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF59" t="n">
         <v>10</v>
       </c>
-      <c r="BE59" t="n">
+      <c r="BG59" t="n">
         <v>11</v>
       </c>
-      <c r="BF59" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG59" t="n">
-        <v>40</v>
-      </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -12009,10 +12009,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="G60" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H60" t="n">
         <v>4.1</v>
@@ -12024,7 +12024,7 @@
         <v>3.05</v>
       </c>
       <c r="K60" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="L60" t="n">
         <v>1.01</v>
@@ -12042,13 +12042,13 @@
         <v>1.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R60" t="n">
         <v>1.18</v>
       </c>
       <c r="S60" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="T60" t="n">
         <v>1.01</v>
@@ -12057,10 +12057,10 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W60" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X60" t="n">
         <v>1000</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -12206,7 +12206,7 @@
         <v>1.66</v>
       </c>
       <c r="G61" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H61" t="n">
         <v>6.2</v>
@@ -12224,7 +12224,7 @@
         <v>1.01</v>
       </c>
       <c r="M61" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N61" t="n">
         <v>3.15</v>
@@ -12254,7 +12254,7 @@
         <v>1.16</v>
       </c>
       <c r="W61" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X61" t="n">
         <v>970</v>
@@ -12269,10 +12269,10 @@
         <v>250</v>
       </c>
       <c r="AB61" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC61" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD61" t="n">
         <v>26</v>
@@ -12281,10 +12281,10 @@
         <v>140</v>
       </c>
       <c r="AF61" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AG61" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH61" t="n">
         <v>25</v>
@@ -12293,7 +12293,7 @@
         <v>140</v>
       </c>
       <c r="AJ61" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AK61" t="n">
         <v>21</v>
@@ -12314,13 +12314,13 @@
         <v>10</v>
       </c>
       <c r="AQ61" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AR61" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS61" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT61" t="n">
         <v>6.2</v>
@@ -12329,44 +12329,44 @@
         <v>7.4</v>
       </c>
       <c r="AV61" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW61" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX61" t="n">
         <v>8</v>
       </c>
       <c r="AY61" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ61" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BA61" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB61" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC61" t="n">
-        <v>6.2</v>
+        <v>17</v>
       </c>
       <c r="BD61" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE61" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF61" t="n">
         <v>11</v>
       </c>
       <c r="BG61" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12406,7 @@
         <v>2.88</v>
       </c>
       <c r="I62" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="J62" t="n">
         <v>2.92</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
         <v>4.1</v>
       </c>
       <c r="H64" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I64" t="n">
         <v>2.4</v>
@@ -12809,28 +12809,28 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="O64" t="n">
         <v>1.36</v>
       </c>
       <c r="P64" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="R64" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="S64" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T64" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U64" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V64" t="n">
         <v>1.71</v>
@@ -12842,7 +12842,7 @@
         <v>17</v>
       </c>
       <c r="Y64" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z64" t="n">
         <v>19.5</v>
@@ -12851,7 +12851,7 @@
         <v>42</v>
       </c>
       <c r="AB64" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC64" t="n">
         <v>11</v>
@@ -12896,7 +12896,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AR64" t="n">
         <v>8.4</v>
@@ -12905,10 +12905,10 @@
         <v>17.5</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AV64" t="n">
         <v>7</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -12979,58 +12979,58 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G65" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="H65" t="n">
         <v>2.48</v>
       </c>
       <c r="I65" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="J65" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K65" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N65" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P65" t="n">
         <v>1.93</v>
       </c>
-      <c r="O65" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P65" t="n">
-        <v>1.94</v>
-      </c>
       <c r="Q65" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R65" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S65" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="T65" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U65" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V65" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W65" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -13373,10 +13373,10 @@
         <v>1.43</v>
       </c>
       <c r="H67" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="J67" t="n">
         <v>4.5</v>
@@ -13451,7 +13451,7 @@
         <v>970</v>
       </c>
       <c r="AH67" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AI67" t="n">
         <v>300</v>
@@ -13478,25 +13478,25 @@
         <v>11</v>
       </c>
       <c r="AQ67" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR67" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS67" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT67" t="n">
         <v>5.4</v>
       </c>
       <c r="AU67" t="n">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="AV67" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AW67" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX67" t="n">
         <v>5.9</v>
@@ -13508,29 +13508,29 @@
         <v>7.6</v>
       </c>
       <c r="BA67" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB67" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC67" t="n">
         <v>6.4</v>
       </c>
       <c r="BD67" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE67" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF67" t="n">
         <v>6.4</v>
       </c>
       <c r="BG67" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -13564,7 +13564,7 @@
         <v>2.28</v>
       </c>
       <c r="G68" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H68" t="n">
         <v>3.3</v>
@@ -13579,7 +13579,7 @@
         <v>3.55</v>
       </c>
       <c r="L68" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M68" t="n">
         <v>1.09</v>
@@ -13588,7 +13588,7 @@
         <v>2.88</v>
       </c>
       <c r="O68" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P68" t="n">
         <v>1.64</v>
@@ -13600,7 +13600,7 @@
         <v>1.24</v>
       </c>
       <c r="S68" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T68" t="n">
         <v>1.89</v>
@@ -13612,10 +13612,10 @@
         <v>1.34</v>
       </c>
       <c r="W68" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X68" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y68" t="n">
         <v>13.5</v>
@@ -13705,26 +13705,26 @@
         <v>4.1</v>
       </c>
       <c r="BB68" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC68" t="n">
         <v>21</v>
       </c>
       <c r="BD68" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE68" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BE68" t="n">
-        <v>4.2</v>
       </c>
       <c r="BF68" t="n">
         <v>20</v>
       </c>
       <c r="BG68" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -13955,7 +13955,7 @@
         <v>7.8</v>
       </c>
       <c r="H70" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="I70" t="n">
         <v>1.63</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
         <v>5.9</v>
       </c>
       <c r="J71" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K71" t="n">
         <v>4.4</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -14337,10 +14337,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G72" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H72" t="n">
         <v>4.3</v>
@@ -14352,7 +14352,7 @@
         <v>3.55</v>
       </c>
       <c r="K72" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -14388,7 +14388,7 @@
         <v>1.25</v>
       </c>
       <c r="W72" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X72" t="n">
         <v>13.5</v>
@@ -14400,7 +14400,7 @@
         <v>36</v>
       </c>
       <c r="AA72" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB72" t="n">
         <v>8.4</v>
@@ -14412,7 +14412,7 @@
         <v>19</v>
       </c>
       <c r="AE72" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF72" t="n">
         <v>11.5</v>
@@ -14442,7 +14442,7 @@
         <v>15</v>
       </c>
       <c r="AO72" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP72" t="n">
         <v>11.5</v>
@@ -14451,7 +14451,7 @@
         <v>13.5</v>
       </c>
       <c r="AR72" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS72" t="n">
         <v>12</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -14531,22 +14531,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G73" t="n">
         <v>1.38</v>
       </c>
       <c r="H73" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="J73" t="n">
         <v>4.8</v>
       </c>
       <c r="K73" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14561,10 +14561,10 @@
         <v>1.44</v>
       </c>
       <c r="P73" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R73" t="n">
         <v>1.25</v>
@@ -14576,19 +14576,19 @@
         <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="V73" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W73" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="X73" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y73" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z73" t="n">
         <v>200</v>
@@ -14597,31 +14597,31 @@
         <v>1000</v>
       </c>
       <c r="AB73" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AC73" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD73" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AE73" t="n">
         <v>1000</v>
       </c>
       <c r="AF73" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AG73" t="n">
         <v>12.5</v>
       </c>
       <c r="AH73" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI73" t="n">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="AJ73" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AK73" t="n">
         <v>20</v>
@@ -14642,13 +14642,13 @@
         <v>10</v>
       </c>
       <c r="AQ73" t="n">
-        <v>6.2</v>
+        <v>26</v>
       </c>
       <c r="AR73" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AS73" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT73" t="n">
         <v>4.9</v>
@@ -14657,44 +14657,44 @@
         <v>11</v>
       </c>
       <c r="AV73" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AW73" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX73" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY73" t="n">
         <v>10</v>
       </c>
       <c r="AZ73" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BA73" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB73" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC73" t="n">
         <v>16.5</v>
       </c>
       <c r="BD73" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BE73" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF73" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG73" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
         <v>2.18</v>
       </c>
       <c r="G74" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H74" t="n">
         <v>3.15</v>
@@ -14737,13 +14737,13 @@
         <v>4.7</v>
       </c>
       <c r="J74" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K74" t="n">
         <v>3.5</v>
       </c>
       <c r="L74" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M74" t="n">
         <v>1.01</v>
@@ -14776,7 +14776,7 @@
         <v>1.27</v>
       </c>
       <c r="W74" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X74" t="n">
         <v>1000</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-27 05:19:45</t>
+          <t>2026-03-27 07:32:45</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-28.xlsx
@@ -763,19 +763,19 @@
         <v>4.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J2" t="n">
         <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.09</v>
@@ -784,13 +784,13 @@
         <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
         <v>1.27</v>
@@ -805,7 +805,7 @@
         <v>1.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
         <v>1.32</v>
@@ -868,59 +868,59 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>2.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU2" t="n">
         <v>4.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>16.5</v>
+        <v>2.84</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>2.58</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.85</v>
+        <v>2.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.96</v>
+        <v>2.7</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.99</v>
+        <v>2.76</v>
       </c>
       <c r="BC2" t="n">
         <v>7.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.97</v>
+        <v>2.74</v>
       </c>
       <c r="BE2" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.98</v>
+        <v>2.74</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
         <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
@@ -1032,7 +1032,7 @@
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AY3" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4" t="n">
         <v>3.85</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="M4" t="n">
         <v>1.07</v>
@@ -1184,34 +1184,34 @@
         <v>1.3</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U4" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="V4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
         <v>16.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
         <v>300</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>11.5</v>
@@ -1247,7 +1247,7 @@
         <v>210</v>
       </c>
       <c r="AN4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>230</v>
@@ -1256,7 +1256,7 @@
         <v>10</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>1.03</v>
@@ -1265,10 +1265,10 @@
         <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV4" t="n">
         <v>20</v>
@@ -1277,13 +1277,13 @@
         <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY4" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BA4" t="n">
         <v>1.03</v>
@@ -1295,20 +1295,20 @@
         <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE4" t="n">
         <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG4" t="n">
         <v>130</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>3.7</v>
       </c>
       <c r="H6" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="I6" t="n">
         <v>2.96</v>
@@ -1581,7 +1581,7 @@
         <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="W6" t="n">
         <v>1.37</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>2.66</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
         <v>3.45</v>
@@ -2139,16 +2139,16 @@
         <v>1.09</v>
       </c>
       <c r="N9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O9" t="n">
         <v>1.41</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
         <v>1.28</v>
@@ -2157,10 +2157,10 @@
         <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V9" t="n">
         <v>1.6</v>
@@ -2205,7 +2205,7 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="n">
         <v>48</v>
@@ -2223,7 +2223,7 @@
         <v>32</v>
       </c>
       <c r="AP9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ9" t="n">
         <v>8.6</v>
@@ -2232,7 +2232,7 @@
         <v>13.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
         <v>8.800000000000001</v>
@@ -2244,7 +2244,7 @@
         <v>11</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX9" t="n">
         <v>17.5</v>
@@ -2256,13 +2256,13 @@
         <v>15.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BC9" t="n">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="BD9" t="n">
         <v>38</v>
@@ -2274,11 +2274,11 @@
         <v>32</v>
       </c>
       <c r="BG9" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G11" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I11" t="n">
         <v>3.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K11" t="n">
         <v>3.55</v>
@@ -2551,10 +2551,10 @@
         <v>2.06</v>
       </c>
       <c r="V11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W11" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X11" t="n">
         <v>12.5</v>
@@ -2590,7 +2590,7 @@
         <v>19</v>
       </c>
       <c r="AI11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
         <v>32</v>
@@ -2632,7 +2632,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="AX11" t="n">
         <v>13</v>
@@ -2644,10 +2644,10 @@
         <v>16.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BC11" t="n">
         <v>23</v>
@@ -2656,7 +2656,7 @@
         <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BF11" t="n">
         <v>19.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>1.72</v>
       </c>
       <c r="I12" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -2739,13 +2739,13 @@
         <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="W12" t="n">
         <v>1.16</v>
@@ -2778,7 +2778,7 @@
         <v>55</v>
       </c>
       <c r="AG12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH12" t="n">
         <v>32</v>
@@ -2790,7 +2790,7 @@
         <v>280</v>
       </c>
       <c r="AK12" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AL12" t="n">
         <v>180</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>1.98</v>
       </c>
       <c r="G13" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
         <v>2.94</v>
@@ -2930,7 +2930,7 @@
         <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="T13" t="n">
         <v>1.92</v>
@@ -2939,10 +2939,10 @@
         <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3094,10 +3094,10 @@
         <v>2.84</v>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J14" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="K14" t="n">
         <v>3.35</v>
@@ -3112,13 +3112,13 @@
         <v>2.86</v>
       </c>
       <c r="O14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R14" t="n">
         <v>1.23</v>
@@ -3133,10 +3133,10 @@
         <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="X14" t="n">
         <v>11.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         <v>1.48</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q15" t="n">
         <v>2.44</v>
@@ -3318,7 +3318,7 @@
         <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="T15" t="n">
         <v>2</v>
@@ -3327,7 +3327,7 @@
         <v>1.83</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
         <v>1.62</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="G16" t="n">
         <v>5</v>
@@ -3482,19 +3482,19 @@
         <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J16" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="K16" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
         <v>3.2</v>
@@ -3518,7 +3518,7 @@
         <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V16" t="n">
         <v>1.72</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -3894,13 +3894,13 @@
         <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="R18" t="n">
         <v>1.18</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="T18" t="n">
         <v>1.11</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G19" t="n">
         <v>840</v>
       </c>
       <c r="H19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I19" t="n">
         <v>930</v>
@@ -4070,7 +4070,7 @@
         <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4094,7 +4094,7 @@
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I21" t="n">
         <v>2.5</v>
@@ -4482,7 +4482,7 @@
         <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
         <v>1.71</v>
@@ -4494,7 +4494,7 @@
         <v>1.67</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H22" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>3.55</v>
@@ -4661,34 +4661,34 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O22" t="n">
         <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
         <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4706,7 +4706,7 @@
         <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4715,7 +4715,7 @@
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG22" t="n">
         <v>1000</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ22" t="n">
         <v>4</v>
@@ -4754,10 +4754,10 @@
         <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU22" t="n">
         <v>7.2</v>
@@ -4769,28 +4769,28 @@
         <v>4.7</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AY22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA22" t="n">
         <v>4.7</v>
       </c>
       <c r="BB22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC22" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>4.1</v>
       </c>
       <c r="BD22" t="n">
         <v>4.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF22" t="n">
         <v>9</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
         <v>1.02</v>
       </c>
       <c r="K24" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
         <v>1.02</v>
       </c>
       <c r="K25" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>1.02</v>
       </c>
       <c r="G26" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
         <v>1.02</v>
       </c>
       <c r="I26" t="n">
-        <v>500</v>
+        <v>990</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,7 +5437,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.01</v>
@@ -5452,13 +5452,13 @@
         <v>1.02</v>
       </c>
       <c r="S26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5622,7 @@
         <v>1.02</v>
       </c>
       <c r="K27" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5640,13 +5640,13 @@
         <v>1.02</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R27" t="n">
         <v>1.02</v>
       </c>
       <c r="S27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
         <v>1.02</v>
       </c>
       <c r="K28" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5840,7 +5840,7 @@
         <v>1.02</v>
       </c>
       <c r="S28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
         <v>1.02</v>
       </c>
       <c r="K29" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
         <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L30" t="n">
         <v>1.33</v>
@@ -6219,7 +6219,7 @@
         <v>1.32</v>
       </c>
       <c r="P30" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
         <v>1.92</v>
@@ -6240,7 +6240,7 @@
         <v>1.38</v>
       </c>
       <c r="W30" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6327,7 +6327,7 @@
         <v>8.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="BA30" t="n">
         <v>5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -6497,13 +6497,13 @@
         <v>5.3</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="AS31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT31" t="n">
         <v>5</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>5.8</v>
       </c>
       <c r="AU31" t="n">
         <v>4.1</v>
@@ -6512,41 +6512,41 @@
         <v>7.6</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX31" t="n">
         <v>6</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB31" t="n">
         <v>4.1</v>
       </c>
       <c r="BC31" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF31" t="n">
         <v>4.1</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6786,7 @@
         <v>1.02</v>
       </c>
       <c r="K33" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="G34" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="H34" t="n">
-        <v>1.02</v>
+        <v>12</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K34" t="n">
-        <v>110</v>
+        <v>10.5</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,34 +6989,34 @@
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>1.71</v>
+        <v>7.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="R34" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="S34" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W34" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>2.66</v>
       </c>
       <c r="G35" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="H35" t="n">
         <v>2.56</v>
@@ -7171,7 +7171,7 @@
         <v>2.92</v>
       </c>
       <c r="J35" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K35" t="n">
         <v>3.85</v>
@@ -7198,19 +7198,19 @@
         <v>1.37</v>
       </c>
       <c r="S35" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="T35" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U35" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V35" t="n">
         <v>1.52</v>
       </c>
       <c r="W35" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="X35" t="n">
         <v>18</v>
@@ -7228,7 +7228,7 @@
         <v>14</v>
       </c>
       <c r="AC35" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD35" t="n">
         <v>14.5</v>
@@ -7276,7 +7276,7 @@
         <v>14</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT35" t="n">
         <v>9.4</v>
@@ -7288,7 +7288,7 @@
         <v>9.6</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX35" t="n">
         <v>15</v>
@@ -7300,19 +7300,19 @@
         <v>12.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BB35" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC35" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC35" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD35" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF35" t="n">
         <v>19</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>2.1</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I36" t="n">
         <v>5.6</v>
@@ -7380,13 +7380,13 @@
         <v>3.05</v>
       </c>
       <c r="O36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P36" t="n">
         <v>1.71</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="R36" t="n">
         <v>1.26</v>
@@ -7401,7 +7401,7 @@
         <v>1.88</v>
       </c>
       <c r="V36" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W36" t="n">
         <v>1.92</v>
@@ -7419,7 +7419,7 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC36" t="n">
         <v>9</v>
@@ -7467,10 +7467,10 @@
         <v>10.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT36" t="n">
         <v>6</v>
@@ -7482,7 +7482,7 @@
         <v>14</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX36" t="n">
         <v>9</v>
@@ -7494,7 +7494,7 @@
         <v>15.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB36" t="n">
         <v>18</v>
@@ -7503,20 +7503,20 @@
         <v>18</v>
       </c>
       <c r="BD36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE36" t="n">
         <v>5</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>5.3</v>
       </c>
       <c r="BF36" t="n">
         <v>14</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -7547,13 +7547,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G37" t="n">
         <v>1000</v>
       </c>
       <c r="H37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I37" t="n">
         <v>1000</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
         <v>21</v>
       </c>
       <c r="AP38" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>11</v>
@@ -7894,7 +7894,7 @@
         <v>7.6</v>
       </c>
       <c r="BE38" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BF38" t="n">
         <v>13.5</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G39" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I39" t="n">
         <v>2.62</v>
@@ -7950,10 +7950,10 @@
         <v>3.7</v>
       </c>
       <c r="K39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L39" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M39" t="n">
         <v>1.04</v>
@@ -7977,10 +7977,10 @@
         <v>2.42</v>
       </c>
       <c r="T39" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U39" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="V39" t="n">
         <v>1.61</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G40" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="H40" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I40" t="n">
         <v>2.78</v>
@@ -8144,7 +8144,7 @@
         <v>3.6</v>
       </c>
       <c r="K40" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8174,13 +8174,13 @@
         <v>1.59</v>
       </c>
       <c r="U40" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V40" t="n">
         <v>1.56</v>
       </c>
       <c r="W40" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8249,7 +8249,7 @@
         <v>25</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AU40" t="n">
         <v>6.6</v>
@@ -8261,13 +8261,13 @@
         <v>17</v>
       </c>
       <c r="AX40" t="n">
-        <v>16</v>
+        <v>4.1</v>
       </c>
       <c r="AY40" t="n">
         <v>3.85</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA40" t="n">
         <v>4.2</v>
@@ -8276,7 +8276,7 @@
         <v>26</v>
       </c>
       <c r="BC40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD40" t="n">
         <v>4.3</v>
@@ -8285,14 +8285,14 @@
         <v>3.6</v>
       </c>
       <c r="BF40" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BG40" t="n">
         <v>11.5</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G41" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H41" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="I41" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="J41" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K41" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L41" t="n">
         <v>1.32</v>
@@ -8347,34 +8347,34 @@
         <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O41" t="n">
         <v>1.23</v>
       </c>
       <c r="P41" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="Q41" t="n">
         <v>1.68</v>
       </c>
       <c r="R41" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S41" t="n">
         <v>2.72</v>
       </c>
       <c r="T41" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="U41" t="n">
         <v>2.38</v>
       </c>
       <c r="V41" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W41" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8392,101 +8392,101 @@
         <v>1000</v>
       </c>
       <c r="AC41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV41" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW41" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AY41" t="n">
         <v>9</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="BA41" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.6</v>
+        <v>23</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.9</v>
+        <v>3.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG41" t="n">
-        <v>4.4</v>
+        <v>19</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -8676,11 +8676,11 @@
         <v>10.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -8741,10 +8741,10 @@
         <v>1.25</v>
       </c>
       <c r="P43" t="n">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R43" t="n">
         <v>1.42</v>
@@ -8834,7 +8834,7 @@
         <v>3.3</v>
       </c>
       <c r="AU43" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="AV43" t="n">
         <v>3.3</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -8911,7 +8911,7 @@
         <v>2.3</v>
       </c>
       <c r="H44" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I44" t="n">
         <v>3.8</v>
@@ -8929,7 +8929,7 @@
         <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>1.25</v>
@@ -9025,7 +9025,7 @@
         <v>2.12</v>
       </c>
       <c r="AT44" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU44" t="n">
         <v>4.2</v>
@@ -9034,7 +9034,7 @@
         <v>10</v>
       </c>
       <c r="AW44" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="AX44" t="n">
         <v>4.2</v>
@@ -9046,29 +9046,29 @@
         <v>11.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BB44" t="n">
         <v>6.4</v>
       </c>
       <c r="BC44" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BF44" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="BG44" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -9105,10 +9105,10 @@
         <v>5.5</v>
       </c>
       <c r="H45" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="I45" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="J45" t="n">
         <v>3.65</v>
@@ -9129,7 +9129,7 @@
         <v>1.25</v>
       </c>
       <c r="P45" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q45" t="n">
         <v>1.68</v>
@@ -9147,7 +9147,7 @@
         <v>2.18</v>
       </c>
       <c r="V45" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="W45" t="n">
         <v>1.22</v>
@@ -9216,22 +9216,22 @@
         <v>9</v>
       </c>
       <c r="AS45" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT45" t="n">
         <v>13.5</v>
       </c>
       <c r="AU45" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AV45" t="n">
         <v>7.6</v>
       </c>
       <c r="AW45" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX45" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY45" t="n">
         <v>5.1</v>
@@ -9240,29 +9240,29 @@
         <v>4.8</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BB45" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="BC45" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="BE45" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF45" t="n">
         <v>5.9</v>
       </c>
       <c r="BG45" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="G46" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="H46" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="I46" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J46" t="n">
         <v>3.45</v>
@@ -9320,19 +9320,19 @@
         <v>4.2</v>
       </c>
       <c r="O46" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R46" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S46" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="T46" t="n">
         <v>1.61</v>
@@ -9341,10 +9341,10 @@
         <v>2.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W46" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9371,7 +9371,7 @@
         <v>1000</v>
       </c>
       <c r="AF46" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG46" t="n">
         <v>1000</v>
@@ -9398,65 +9398,65 @@
         <v>1000</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP46" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ46" t="n">
         <v>5.3</v>
       </c>
-      <c r="AQ46" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AR46" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AS46" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AT46" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AU46" t="n">
         <v>6.8</v>
       </c>
       <c r="AV46" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW46" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX46" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AY46" t="n">
-        <v>4.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ46" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BA46" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG46" t="n">
         <v>6</v>
       </c>
-      <c r="BB46" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>15</v>
-      </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>4.7</v>
       </c>
       <c r="G47" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H47" t="n">
         <v>1.67</v>
@@ -9502,7 +9502,7 @@
         <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.27</v>
@@ -9526,7 +9526,7 @@
         <v>1.53</v>
       </c>
       <c r="S47" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T47" t="n">
         <v>1.68</v>
@@ -9535,7 +9535,7 @@
         <v>2.22</v>
       </c>
       <c r="V47" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W47" t="n">
         <v>1.22</v>
@@ -9553,7 +9553,7 @@
         <v>21</v>
       </c>
       <c r="AB47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AC47" t="n">
         <v>10.5</v>
@@ -9619,7 +9619,7 @@
         <v>14</v>
       </c>
       <c r="AX47" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY47" t="n">
         <v>16.5</v>
@@ -9628,19 +9628,19 @@
         <v>15</v>
       </c>
       <c r="BA47" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB47" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE47" t="n">
         <v>7.4</v>
-      </c>
-      <c r="BC47" t="n">
-        <v>48</v>
-      </c>
-      <c r="BD47" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE47" t="n">
-        <v>7.2</v>
       </c>
       <c r="BF47" t="n">
         <v>7</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G48" t="n">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="H48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I48" t="n">
         <v>3.55</v>
       </c>
-      <c r="I48" t="n">
-        <v>4.1</v>
-      </c>
       <c r="J48" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K48" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9726,125 +9726,125 @@
         <v>1.62</v>
       </c>
       <c r="U48" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V48" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W48" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="X48" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y48" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z48" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA48" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB48" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG48" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD48" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AH48" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI48" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AJ48" t="n">
         <v>28</v>
       </c>
       <c r="AK48" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA48" t="n">
         <v>32</v>
       </c>
-      <c r="AM48" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>11</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>12</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>30</v>
-      </c>
       <c r="BB48" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC48" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BD48" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BE48" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF48" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG48" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -9878,13 +9878,13 @@
         <v>2.18</v>
       </c>
       <c r="G49" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H49" t="n">
         <v>3.2</v>
       </c>
       <c r="I49" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J49" t="n">
         <v>3.75</v>
@@ -9893,7 +9893,7 @@
         <v>4.1</v>
       </c>
       <c r="L49" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M49" t="n">
         <v>1.04</v>
@@ -9902,31 +9902,31 @@
         <v>4.6</v>
       </c>
       <c r="O49" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P49" t="n">
         <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R49" t="n">
         <v>1.51</v>
       </c>
       <c r="S49" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T49" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U49" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V49" t="n">
         <v>1.4</v>
       </c>
       <c r="W49" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X49" t="n">
         <v>25</v>
@@ -10016,7 +10016,7 @@
         <v>11.5</v>
       </c>
       <c r="BA49" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB49" t="n">
         <v>6.4</v>
@@ -10031,14 +10031,14 @@
         <v>6.8</v>
       </c>
       <c r="BF49" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG49" t="n">
         <v>18.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10084,7 @@
         <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L50" t="n">
         <v>1.01</v>
@@ -10102,7 +10102,7 @@
         <v>2.46</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R50" t="n">
         <v>1.58</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -10266,19 +10266,19 @@
         <v>1.33</v>
       </c>
       <c r="G51" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="H51" t="n">
         <v>8.6</v>
       </c>
       <c r="I51" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J51" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="K51" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L51" t="n">
         <v>1.21</v>
@@ -10308,13 +10308,13 @@
         <v>1.8</v>
       </c>
       <c r="U51" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V51" t="n">
         <v>1.1</v>
       </c>
       <c r="W51" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="X51" t="n">
         <v>32</v>
@@ -10371,13 +10371,13 @@
         <v>140</v>
       </c>
       <c r="AP51" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ51" t="n">
         <v>8</v>
       </c>
       <c r="AR51" t="n">
-        <v>9.199999999999999</v>
+        <v>55</v>
       </c>
       <c r="AS51" t="n">
         <v>10</v>
@@ -10401,7 +10401,7 @@
         <v>8</v>
       </c>
       <c r="AZ51" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="BA51" t="n">
         <v>9.4</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -10466,13 +10466,13 @@
         <v>2.54</v>
       </c>
       <c r="I52" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="J52" t="n">
         <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10502,7 +10502,7 @@
         <v>1.44</v>
       </c>
       <c r="U52" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V52" t="n">
         <v>1.56</v>
@@ -10511,7 +10511,7 @@
         <v>1.62</v>
       </c>
       <c r="X52" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="Y52" t="n">
         <v>21</v>
@@ -10565,28 +10565,28 @@
         <v>970</v>
       </c>
       <c r="AP52" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ52" t="n">
         <v>14.5</v>
       </c>
       <c r="AR52" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AS52" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT52" t="n">
         <v>13.5</v>
       </c>
       <c r="AU52" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AV52" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AW52" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AX52" t="n">
         <v>18</v>
@@ -10595,13 +10595,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ52" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA52" t="n">
         <v>20</v>
       </c>
       <c r="BB52" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BC52" t="n">
         <v>19</v>
@@ -10610,17 +10610,17 @@
         <v>21</v>
       </c>
       <c r="BE52" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BF52" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG52" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -10780,7 +10780,7 @@
         <v>10</v>
       </c>
       <c r="AW53" t="n">
-        <v>18</v>
+        <v>7.8</v>
       </c>
       <c r="AX53" t="n">
         <v>7</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10863,7 @@
         <v>3.8</v>
       </c>
       <c r="L54" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M54" t="n">
         <v>1.09</v>
@@ -10887,10 +10887,10 @@
         <v>3.8</v>
       </c>
       <c r="T54" t="n">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="U54" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V54" t="n">
         <v>1.43</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -11045,7 +11045,7 @@
         <v>6.2</v>
       </c>
       <c r="H55" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I55" t="n">
         <v>1.62</v>
@@ -11054,7 +11054,7 @@
         <v>4.7</v>
       </c>
       <c r="K55" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11063,7 +11063,7 @@
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O55" t="n">
         <v>1.19</v>
@@ -11075,16 +11075,16 @@
         <v>1.57</v>
       </c>
       <c r="R55" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S55" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T55" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="U55" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V55" t="n">
         <v>2.6</v>
@@ -11117,7 +11117,7 @@
         <v>16</v>
       </c>
       <c r="AF55" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AG55" t="n">
         <v>23</v>
@@ -11147,7 +11147,7 @@
         <v>7</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ55" t="n">
         <v>9.800000000000001</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -11233,19 +11233,19 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G56" t="n">
         <v>2.32</v>
       </c>
       <c r="H56" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="I56" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J56" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K56" t="n">
         <v>3.3</v>
@@ -11257,28 +11257,28 @@
         <v>1.12</v>
       </c>
       <c r="N56" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O56" t="n">
         <v>1.56</v>
       </c>
       <c r="P56" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R56" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S56" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T56" t="n">
         <v>2.2</v>
       </c>
       <c r="U56" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="V56" t="n">
         <v>1.34</v>
@@ -11362,7 +11362,7 @@
         <v>15</v>
       </c>
       <c r="AW56" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="AX56" t="n">
         <v>11.5</v>
@@ -11377,10 +11377,10 @@
         <v>14.5</v>
       </c>
       <c r="BB56" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC56" t="n">
         <v>28</v>
-      </c>
-      <c r="BC56" t="n">
-        <v>11.5</v>
       </c>
       <c r="BD56" t="n">
         <v>50</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -11427,61 +11427,61 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G57" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H57" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J57" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K57" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L57" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M57" t="n">
         <v>1.11</v>
       </c>
       <c r="N57" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O57" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P57" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q57" t="n">
         <v>2.48</v>
       </c>
       <c r="R57" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T57" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="U57" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V57" t="n">
         <v>1.21</v>
       </c>
       <c r="W57" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="X57" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y57" t="n">
         <v>14</v>
@@ -11535,28 +11535,28 @@
         <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ57" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS57" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT57" t="n">
         <v>6</v>
       </c>
       <c r="AU57" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV57" t="n">
         <v>18.5</v>
       </c>
       <c r="AW57" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX57" t="n">
         <v>8.6</v>
@@ -11568,7 +11568,7 @@
         <v>21</v>
       </c>
       <c r="BA57" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB57" t="n">
         <v>17</v>
@@ -11580,17 +11580,17 @@
         <v>44</v>
       </c>
       <c r="BE57" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF57" t="n">
         <v>15.5</v>
       </c>
       <c r="BG57" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -11729,52 +11729,52 @@
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF58" t="n">
         <v>1.01</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -11815,10 +11815,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G59" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H59" t="n">
         <v>5.1</v>
@@ -11839,13 +11839,13 @@
         <v>1.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O59" t="n">
         <v>1.46</v>
       </c>
       <c r="P59" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q59" t="n">
         <v>2.3</v>
@@ -11854,19 +11854,19 @@
         <v>1.22</v>
       </c>
       <c r="S59" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T59" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U59" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V59" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W59" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X59" t="n">
         <v>12.5</v>
@@ -11911,7 +11911,7 @@
         <v>26</v>
       </c>
       <c r="AL59" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM59" t="n">
         <v>1000</v>
@@ -11944,7 +11944,7 @@
         <v>18.5</v>
       </c>
       <c r="AW59" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX59" t="n">
         <v>8.6</v>
@@ -11956,7 +11956,7 @@
         <v>20</v>
       </c>
       <c r="BA59" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB59" t="n">
         <v>18</v>
@@ -11968,7 +11968,7 @@
         <v>6.4</v>
       </c>
       <c r="BE59" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF59" t="n">
         <v>16</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
         <v>2.96</v>
       </c>
       <c r="J61" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="K61" t="n">
         <v>3.45</v>
@@ -12245,7 +12245,7 @@
         <v>4.6</v>
       </c>
       <c r="T61" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U61" t="n">
         <v>1.87</v>
@@ -12317,10 +12317,10 @@
         <v>7</v>
       </c>
       <c r="AR61" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS61" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="AT61" t="n">
         <v>7.6</v>
@@ -12329,44 +12329,44 @@
         <v>5.8</v>
       </c>
       <c r="AV61" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW61" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AX61" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AY61" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AZ61" t="n">
-        <v>5.9</v>
+        <v>15</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.9</v>
+        <v>2.94</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.9</v>
+        <v>7.6</v>
       </c>
       <c r="BC61" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="BF61" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="BG61" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -12600,7 +12600,7 @@
         <v>3.25</v>
       </c>
       <c r="I63" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J63" t="n">
         <v>2.9</v>
@@ -12654,7 +12654,7 @@
         <v>23</v>
       </c>
       <c r="AA63" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB63" t="n">
         <v>8.4</v>
@@ -12666,7 +12666,7 @@
         <v>16.5</v>
       </c>
       <c r="AE63" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF63" t="n">
         <v>16.5</v>
@@ -12678,7 +12678,7 @@
         <v>23</v>
       </c>
       <c r="AI63" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ63" t="n">
         <v>46</v>
@@ -12687,7 +12687,7 @@
         <v>40</v>
       </c>
       <c r="AL63" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM63" t="n">
         <v>1000</v>
@@ -12708,7 +12708,7 @@
         <v>16</v>
       </c>
       <c r="AS63" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="AT63" t="n">
         <v>6</v>
@@ -12720,7 +12720,7 @@
         <v>11</v>
       </c>
       <c r="AW63" t="n">
-        <v>7.6</v>
+        <v>36</v>
       </c>
       <c r="AX63" t="n">
         <v>11.5</v>
@@ -12732,29 +12732,29 @@
         <v>15.5</v>
       </c>
       <c r="BA63" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="BB63" t="n">
         <v>7.4</v>
       </c>
       <c r="BC63" t="n">
-        <v>7.2</v>
+        <v>26</v>
       </c>
       <c r="BD63" t="n">
         <v>7.8</v>
       </c>
       <c r="BE63" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF63" t="n">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BG63" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1.04</v>
+        <v>2.52</v>
       </c>
       <c r="G64" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="H64" t="n">
-        <v>1.04</v>
+        <v>2.48</v>
       </c>
       <c r="I64" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="J64" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="K64" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12809,34 +12809,34 @@
         <v>1.01</v>
       </c>
       <c r="N64" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="O64" t="n">
         <v>1.01</v>
       </c>
       <c r="P64" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R64" t="n">
         <v>1.12</v>
       </c>
       <c r="S64" t="n">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="T64" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U64" t="n">
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W64" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X64" t="n">
         <v>1000</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -12979,46 +12979,46 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G65" t="n">
-        <v>1000</v>
+        <v>2.22</v>
       </c>
       <c r="H65" t="n">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="I65" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J65" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="K65" t="n">
         <v>1000</v>
       </c>
       <c r="L65" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M65" t="n">
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="O65" t="n">
         <v>1.01</v>
       </c>
       <c r="P65" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="R65" t="n">
         <v>1.12</v>
       </c>
       <c r="S65" t="n">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="T65" t="n">
         <v>1.01</v>
@@ -13027,10 +13027,10 @@
         <v>1.01</v>
       </c>
       <c r="V65" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W65" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -13173,22 +13173,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="G66" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="H66" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I66" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="J66" t="n">
-        <v>1.03</v>
+        <v>2.68</v>
       </c>
       <c r="K66" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L66" t="n">
         <v>1.01</v>
@@ -13197,22 +13197,22 @@
         <v>1.01</v>
       </c>
       <c r="N66" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="O66" t="n">
         <v>1.01</v>
       </c>
       <c r="P66" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R66" t="n">
         <v>1.12</v>
       </c>
       <c r="S66" t="n">
-        <v>1.02</v>
+        <v>2.42</v>
       </c>
       <c r="T66" t="n">
         <v>1.01</v>
@@ -13221,10 +13221,10 @@
         <v>1.01</v>
       </c>
       <c r="V66" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W66" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X66" t="n">
         <v>1000</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -13367,10 +13367,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G67" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H67" t="n">
         <v>3.95</v>
@@ -13379,7 +13379,7 @@
         <v>4.2</v>
       </c>
       <c r="J67" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K67" t="n">
         <v>3.6</v>
@@ -13400,31 +13400,31 @@
         <v>1.9</v>
       </c>
       <c r="Q67" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R67" t="n">
         <v>1.33</v>
       </c>
       <c r="S67" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T67" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U67" t="n">
         <v>2.08</v>
       </c>
       <c r="V67" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W67" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X67" t="n">
         <v>13.5</v>
       </c>
       <c r="Y67" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z67" t="n">
         <v>28</v>
@@ -13433,10 +13433,10 @@
         <v>85</v>
       </c>
       <c r="AB67" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC67" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD67" t="n">
         <v>16</v>
@@ -13445,7 +13445,7 @@
         <v>55</v>
       </c>
       <c r="AF67" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG67" t="n">
         <v>10.5</v>
@@ -13454,13 +13454,13 @@
         <v>18</v>
       </c>
       <c r="AI67" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ67" t="n">
         <v>25</v>
       </c>
       <c r="AK67" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL67" t="n">
         <v>40</v>
@@ -13478,7 +13478,7 @@
         <v>12</v>
       </c>
       <c r="AQ67" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR67" t="n">
         <v>25</v>
@@ -13496,41 +13496,41 @@
         <v>15</v>
       </c>
       <c r="AW67" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AX67" t="n">
         <v>12</v>
       </c>
       <c r="AY67" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ67" t="n">
         <v>15.5</v>
       </c>
       <c r="BA67" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="BB67" t="n">
         <v>19.5</v>
       </c>
       <c r="BC67" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD67" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="BE67" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BF67" t="n">
         <v>15</v>
       </c>
       <c r="BG67" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -13564,10 +13564,10 @@
         <v>2.24</v>
       </c>
       <c r="G68" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H68" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I68" t="n">
         <v>3.05</v>
@@ -13576,7 +13576,7 @@
         <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L68" t="n">
         <v>1.19</v>
@@ -13585,7 +13585,7 @@
         <v>1.02</v>
       </c>
       <c r="N68" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="O68" t="n">
         <v>1.12</v>
@@ -13606,13 +13606,13 @@
         <v>1.39</v>
       </c>
       <c r="U68" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V68" t="n">
         <v>1.48</v>
       </c>
       <c r="W68" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="X68" t="n">
         <v>48</v>
@@ -13669,7 +13669,7 @@
         <v>14</v>
       </c>
       <c r="AP68" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ68" t="n">
         <v>4.6</v>
@@ -13684,7 +13684,7 @@
         <v>4.6</v>
       </c>
       <c r="AU68" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV68" t="n">
         <v>11.5</v>
@@ -13693,7 +13693,7 @@
         <v>4.7</v>
       </c>
       <c r="AX68" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY68" t="n">
         <v>10</v>
@@ -13708,23 +13708,23 @@
         <v>4.9</v>
       </c>
       <c r="BC68" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD68" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE68" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF68" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG68" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
         <v>1.01</v>
       </c>
       <c r="N69" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O69" t="n">
         <v>1.39</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -13967,7 +13967,7 @@
         <v>3.2</v>
       </c>
       <c r="L70" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="M70" t="n">
         <v>1.13</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -14251,52 +14251,52 @@
         <v>1000</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE71" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF71" t="n">
         <v>1.01</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -15501,46 +15501,46 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1.04</v>
+        <v>2.42</v>
       </c>
       <c r="G78" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="H78" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="I78" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J78" t="n">
-        <v>1.03</v>
+        <v>2.3</v>
       </c>
       <c r="K78" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L78" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="M78" t="n">
         <v>1.01</v>
       </c>
       <c r="N78" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O78" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="P78" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="R78" t="n">
         <v>1.12</v>
       </c>
       <c r="S78" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="T78" t="n">
         <v>1.01</v>
@@ -15549,10 +15549,10 @@
         <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W78" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X78" t="n">
         <v>1000</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -15913,7 +15913,7 @@
         <v>1.01</v>
       </c>
       <c r="N80" t="n">
-        <v>2.74</v>
+        <v>1.86</v>
       </c>
       <c r="O80" t="n">
         <v>1.31</v>
@@ -15922,16 +15922,16 @@
         <v>1.86</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="R80" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S80" t="n">
         <v>2.96</v>
       </c>
       <c r="T80" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="U80" t="n">
         <v>1.96</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -16083,10 +16083,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G81" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H81" t="n">
         <v>3.3</v>
@@ -16095,10 +16095,10 @@
         <v>5</v>
       </c>
       <c r="J81" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K81" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L81" t="n">
         <v>1.01</v>
@@ -16110,7 +16110,7 @@
         <v>2.06</v>
       </c>
       <c r="O81" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P81" t="n">
         <v>1.41</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -16277,19 +16277,19 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="G82" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H82" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I82" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J82" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K82" t="n">
         <v>3.8</v>
@@ -16304,13 +16304,13 @@
         <v>1.76</v>
       </c>
       <c r="O82" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="P82" t="n">
         <v>1.76</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R82" t="n">
         <v>1.2</v>
@@ -16325,28 +16325,28 @@
         <v>1.01</v>
       </c>
       <c r="V82" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W82" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="X82" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y82" t="n">
         <v>13</v>
       </c>
       <c r="Z82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA82" t="n">
         <v>48</v>
       </c>
       <c r="AB82" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC82" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD82" t="n">
         <v>14.5</v>
@@ -16355,10 +16355,10 @@
         <v>36</v>
       </c>
       <c r="AF82" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG82" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH82" t="n">
         <v>20</v>
@@ -16373,7 +16373,7 @@
         <v>38</v>
       </c>
       <c r="AL82" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM82" t="n">
         <v>1000</v>
@@ -16382,13 +16382,13 @@
         <v>34</v>
       </c>
       <c r="AO82" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP82" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR82" t="n">
         <v>14</v>
@@ -16397,7 +16397,7 @@
         <v>1.03</v>
       </c>
       <c r="AT82" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU82" t="n">
         <v>6.2</v>
@@ -16409,10 +16409,10 @@
         <v>1.03</v>
       </c>
       <c r="AX82" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY82" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ82" t="n">
         <v>13</v>
@@ -16436,11 +16436,11 @@
         <v>21</v>
       </c>
       <c r="BG82" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16504,7 @@
         <v>1.89</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="R83" t="n">
         <v>1.34</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -16665,7 +16665,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G84" t="n">
         <v>2.26</v>
@@ -16677,7 +16677,7 @@
         <v>3.55</v>
       </c>
       <c r="J84" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K84" t="n">
         <v>4.2</v>
@@ -16704,7 +16704,7 @@
         <v>1.6</v>
       </c>
       <c r="S84" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T84" t="n">
         <v>1.53</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -16877,19 +16877,19 @@
         <v>3.75</v>
       </c>
       <c r="L85" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M85" t="n">
         <v>1.05</v>
       </c>
       <c r="N85" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O85" t="n">
         <v>1.26</v>
       </c>
       <c r="P85" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q85" t="n">
         <v>1.78</v>
@@ -16904,10 +16904,10 @@
         <v>1.65</v>
       </c>
       <c r="U85" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V85" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W85" t="n">
         <v>1.48</v>
@@ -16958,7 +16958,7 @@
         <v>38</v>
       </c>
       <c r="AM85" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN85" t="n">
         <v>24</v>
@@ -16991,10 +16991,10 @@
         <v>22</v>
       </c>
       <c r="AX85" t="n">
-        <v>18.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY85" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ85" t="n">
         <v>14</v>
@@ -17015,14 +17015,14 @@
         <v>12</v>
       </c>
       <c r="BF85" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG85" t="n">
         <v>15.5</v>
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G86" t="n">
         <v>2.68</v>
@@ -17161,7 +17161,7 @@
         <v>50</v>
       </c>
       <c r="AP86" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ86" t="n">
         <v>9.4</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -17444,13 +17444,13 @@
         <v>2.42</v>
       </c>
       <c r="G88" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H88" t="n">
         <v>2.52</v>
       </c>
       <c r="I88" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J88" t="n">
         <v>2.6</v>
@@ -17459,16 +17459,16 @@
         <v>5.3</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P88" t="n">
         <v>1.4</v>
@@ -17477,134 +17477,134 @@
         <v>2.18</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S88" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V88" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W88" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="X88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO88" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE88" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG88" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -17659,7 +17659,7 @@
         <v>1.09</v>
       </c>
       <c r="N89" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O89" t="n">
         <v>1.39</v>
@@ -17701,7 +17701,7 @@
         <v>260</v>
       </c>
       <c r="AB89" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AC89" t="n">
         <v>10.5</v>
@@ -17731,7 +17731,7 @@
         <v>25</v>
       </c>
       <c r="AL89" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM89" t="n">
         <v>210</v>
@@ -17743,16 +17743,16 @@
         <v>220</v>
       </c>
       <c r="AP89" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AQ89" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AR89" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS89" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT89" t="n">
         <v>6.2</v>
@@ -17761,10 +17761,10 @@
         <v>7.6</v>
       </c>
       <c r="AV89" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AW89" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AX89" t="n">
         <v>8.199999999999999</v>
@@ -17773,32 +17773,32 @@
         <v>9</v>
       </c>
       <c r="AZ89" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA89" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB89" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC89" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA89" t="n">
+      <c r="BD89" t="n">
         <v>4.7</v>
       </c>
-      <c r="BB89" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC89" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD89" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BE89" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF89" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BG89" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -17832,25 +17832,25 @@
         <v>2.06</v>
       </c>
       <c r="G90" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H90" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I90" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J90" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K90" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L90" t="n">
         <v>1.01</v>
       </c>
       <c r="M90" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N90" t="n">
         <v>3.8</v>
@@ -17859,10 +17859,10 @@
         <v>1.3</v>
       </c>
       <c r="P90" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R90" t="n">
         <v>1.37</v>
@@ -17880,10 +17880,10 @@
         <v>1.31</v>
       </c>
       <c r="W90" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="X90" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y90" t="n">
         <v>17.5</v>
@@ -17898,7 +17898,7 @@
         <v>11.5</v>
       </c>
       <c r="AC90" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD90" t="n">
         <v>18.5</v>
@@ -17913,7 +17913,7 @@
         <v>12.5</v>
       </c>
       <c r="AH90" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI90" t="n">
         <v>65</v>
@@ -17928,7 +17928,7 @@
         <v>42</v>
       </c>
       <c r="AM90" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN90" t="n">
         <v>18</v>
@@ -17940,13 +17940,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ90" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AR90" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS90" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT90" t="n">
         <v>7.8</v>
@@ -17958,7 +17958,7 @@
         <v>12</v>
       </c>
       <c r="AW90" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX90" t="n">
         <v>10.5</v>
@@ -17970,29 +17970,29 @@
         <v>4.1</v>
       </c>
       <c r="BA90" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB90" t="n">
         <v>6.4</v>
       </c>
       <c r="BC90" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD90" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE90" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF90" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG90" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -18217,7 +18217,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G92" t="n">
         <v>970</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -18414,16 +18414,16 @@
         <v>1.6</v>
       </c>
       <c r="G93" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="H93" t="n">
         <v>2.5</v>
       </c>
       <c r="I93" t="n">
-        <v>500</v>
+        <v>310</v>
       </c>
       <c r="J93" t="n">
-        <v>2.44</v>
+        <v>1.09</v>
       </c>
       <c r="K93" t="n">
         <v>110</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -18713,52 +18713,52 @@
         <v>1000</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE94" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF94" t="n">
         <v>1.01</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -18916,7 +18916,7 @@
         <v>12</v>
       </c>
       <c r="AS95" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT95" t="n">
         <v>10</v>
@@ -18940,19 +18940,19 @@
         <v>16.5</v>
       </c>
       <c r="BA95" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BB95" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD95" t="n">
         <v>5</v>
       </c>
-      <c r="BC95" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD95" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE95" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BF95" t="n">
         <v>4.9</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -19035,7 +19035,7 @@
         <v>1.02</v>
       </c>
       <c r="T96" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U96" t="n">
         <v>1.01</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -19187,7 +19187,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G97" t="n">
         <v>3</v>
@@ -19202,7 +19202,7 @@
         <v>3.55</v>
       </c>
       <c r="K97" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L97" t="n">
         <v>1.01</v>
@@ -19217,10 +19217,10 @@
         <v>1.31</v>
       </c>
       <c r="P97" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R97" t="n">
         <v>1.37</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -19420,7 +19420,7 @@
         <v>1.3</v>
       </c>
       <c r="S98" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T98" t="n">
         <v>1.98</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -19877,52 +19877,52 @@
         <v>1000</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF100" t="n">
         <v>1.01</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -19963,16 +19963,16 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G101" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="H101" t="n">
         <v>3.3</v>
       </c>
       <c r="I101" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="J101" t="n">
         <v>3.05</v>
@@ -20002,7 +20002,7 @@
         <v>1.24</v>
       </c>
       <c r="S101" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T101" t="n">
         <v>1.89</v>
@@ -20011,13 +20011,13 @@
         <v>1.88</v>
       </c>
       <c r="V101" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W101" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="X101" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y101" t="n">
         <v>13.5</v>
@@ -20080,7 +20080,7 @@
         <v>17.5</v>
       </c>
       <c r="AS101" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT101" t="n">
         <v>6.2</v>
@@ -20092,7 +20092,7 @@
         <v>11</v>
       </c>
       <c r="AW101" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AX101" t="n">
         <v>10.5</v>
@@ -20104,29 +20104,29 @@
         <v>14.5</v>
       </c>
       <c r="BA101" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB101" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC101" t="n">
         <v>21</v>
       </c>
       <c r="BD101" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE101" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BE101" t="n">
-        <v>4.3</v>
       </c>
       <c r="BF101" t="n">
         <v>20</v>
       </c>
       <c r="BG101" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -20563,7 +20563,7 @@
         <v>4.6</v>
       </c>
       <c r="L104" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="M104" t="n">
         <v>1.06</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -21136,7 +21136,7 @@
         <v>15</v>
       </c>
       <c r="I107" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="J107" t="n">
         <v>4.9</v>
@@ -21160,7 +21160,7 @@
         <v>1.74</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R107" t="n">
         <v>1.27</v>
@@ -21181,13 +21181,13 @@
         <v>3.7</v>
       </c>
       <c r="X107" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y107" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z107" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AA107" t="n">
         <v>1000</v>
@@ -21238,37 +21238,37 @@
         <v>9.4</v>
       </c>
       <c r="AQ107" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR107" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS107" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT107" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU107" t="n">
         <v>10</v>
       </c>
       <c r="AV107" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ107" t="n">
         <v>7.4</v>
       </c>
-      <c r="AW107" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX107" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY107" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ107" t="n">
-        <v>7</v>
-      </c>
       <c r="BA107" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB107" t="n">
         <v>8.6</v>
@@ -21277,20 +21277,20 @@
         <v>15.5</v>
       </c>
       <c r="BD107" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE107" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF107" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG107" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
@@ -21369,7 +21369,7 @@
         <v>1.86</v>
       </c>
       <c r="V108" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W108" t="n">
         <v>1.71</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-27 14:19:53</t>
+          <t>2026-03-27 16:37:04</t>
         </is>
       </c>
     </row>
